--- a/reports/Speculative decoding paper table.xlsx
+++ b/reports/Speculative decoding paper table.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Separate drafter runs gamma sequential passes and keeps its own KV cache; drafter must share the target tokenizer; rejected tokens waste target FLOPs (more total arithmetic), which hurts once compute-bound</t>
+          <t>Separate drafter runs gamma sequential passes and keeps its own KV cache; drafter must share the target tokenizer; rejected tokens waste target FLOPs (more total arithmetic, stated), which hurts once compute-bound</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Separate drafter (T5-small 77M to T5-large for T5-XXL) + its KV cache (unv.)</t>
+          <t>Separate drafter (T5-small 77M / base 250M / large 800M for T5-XXL 11B) + its KV cache</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; acceptance rate alpha per pair/task (e.g. ~0.75 EnDe T5-small, unv.)</t>
+          <t>not reported as tau; alpha 0.75-0.82 (T=0) / 0.62-0.71 (T=1) EnDe T5-XXL by drafter; CNN/DM 0.53-0.74; LaMDA 137B 0.57-0.75</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2-3x vs T5X on T5-XXL 11B, TPU-v4, bs1 (unv.); ~3.4x EnDe T=0 with T5-small (unv.)</t>
+          <t>T5-XXL, 1 TPU-v4, bs1: EnDe 3.4x T=0 / 2.6x T=1 (T5-small, gamma 7); CNN/DM 3.1x / 2.3x (T5-small, gamma 5)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Drafter is a separate 4B model trained for the target (same tokenizer), with its own weights and KV; drafting is sequential so drafter latency grows with K; speedup plateaus or regresses as K grows (stated)</t>
+          <t>Drafter is a separate 4B model (8 layers, d=6144) trained for the target with the same tokenizer, with its own weights and KV; drafting is sequential so drafter latency grows with K; efficiency per step drops as K grows (stated)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4B drafter (~8 GB bf16, est.) + its KV cache</t>
+          <t>4B drafter (~8 GB bf16, est.) + its KV cache; served on its own 16 TPU v4</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (within hardware numerics); XSum ROUGE-2 0.156 vs 0.157 greedy; HumanEval 47.0% vs 45.1% nucleus</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2-2.5x on Chinchilla 70B, distributed TPU setup (abstract); per-task numbers not captured</t>
+          <t>Chinchilla 70B, 16 TPU v4, bs1, K=4: XSum 2.01x greedy, 1.92x nucleus; HumanEval 2.46x nucleus (14.1 -&gt; 5.73 ms/token)</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; block efficiency figures only</t>
+          <t>block efficiency (T5-Small -&gt; T5-XL, greedy, gamma 7): XSum 2.68 -&gt; 3.31; GSM8K 3.27 -&gt; 4.14; CNN/DM 3.85 -&gt; 4.83</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>+10-45% over standard SD; lossy SD 6-10x latency cut; TPUv4, bs1</t>
+          <t>+10-45% over standard SD; e.g. CNN/DM greedy 2.07x -&gt; 2.53x vs AR (T5-Small/T5-XL, TPUv4, bs1); lossy SD 6-10x latency cut</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; token acceptance rate +0.1 to +0.65</t>
+          <t>not reported as tau; token acceptance rate +0.1 to +0.65 (e.g. Spider 0.44 -&gt; 0.76 per overview)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1.22-3.06x latency reduction (README/abstract); hardware not captured</t>
+          <t>1.42-2.17x latency reduction (ICML/arXiv v4 abstract); hardware not captured</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Drafter must be pretrained from scratch with target tokenizer (32 A100 pretraining) plus target-generated distillation data; separate model + KV; fine-tuned drafter can lose to base drafter on OOD tasks (stated)</t>
+          <t>Drafter must be pretrained from scratch with target tokenizer (600B tokens, 32 A100) plus target-generated distillation data; separate model + KV; fine-tuned drafter loses to base drafter on OOD tasks (WMT18 DeEn, stated)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+6-27% tokens/s over DistillSpec (A100, greedy); e.g. MBPP 0.69 -&gt; 0.57 s/sentence</t>
+          <t>Pythia-31M-&gt;1.4B, A100, vLLM: MBPP 181.7 vs 149.2 tok/s (+22%), CNN/DM +14%, GSM8K +6% over DistillSpec</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>tau 6.45 vs EAGLE-2 3.94 (Vicuna-7B, T=0); 5.22 vs 4.06 (Qwen2.5-7B, T=0)</t>
+          <t>mean tau 6.32 (MT-Bench 6.45) vs EAGLE-2 3.94 (Vicuna-7B, T=0); Qwen2.5-7B 5.28 vs 4.05 (T=0)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>~2x throughput over EAGLE-2 on Qwen2.5-72B, 4 GPUs, bs64 (2150 vs 980 tok/s)</t>
+          <t>Qwen2.5-72B, 4x H800: bs1 250 vs 200 tok/s EAGLE-2 (AR 60); bs64 2150 vs 980 tok/s (AR 1763)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>T=0 tau: Vicuna-7B 6.45; Llama2-Chat-70B 5.64 (EAGLE-2 4.26); Llama3-Instruct-8B 5.25 (EAGLE-2 4.19)</t>
+          <t>mean tau T=0: Vicuna-7B 6.32; Llama2-Chat-70B 5.60 (EAGLE-2 4.17); Llama3-Instruct-8B 5.36 (EAGLE-2 4.18); T=1: L2-70B 5.54, L3-8B 4.97</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1202,22 +1202,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>not reported; ~0.15B per head at 7B (d x d ResBlock + d x 32k head), ~0.74B for 5 heads (est.)</t>
+          <t>not reported; each head = d x d ResBlock + d x V head, ~0.15B per head at 7B, ~0.74B for 5 heads (est.)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>lossless for Medusa-1 greedy; typical acceptance lossy: MT-Bench score delta -0.14 to +0.05</t>
+          <t>lossless for Medusa-1 greedy; Medusa-2 / typical acceptance lossy: MT-Bench delta -0.14 (V13B) to +0.05 (V33B), Zephyr -0.07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>acceleration rate 3.47 (Vicuna-7B, Medusa-2); 3.51 (13B); 3.01 (33B)</t>
+          <t>acceleration rate 3.47 (Vicuna-7B), 3.51 (13B), 3.01 (33B), 3.14 (Zephyr-7B), Medusa-2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Medusa-1 2.18x, Medusa-2 2.83x (Vicuna-7B, A100, bs1, MT-Bench)</t>
+          <t>Medusa-1 2.18x, Medusa-2 2.83x (Vicuna-7B, A100-80GB, bs1, MT-Bench); Zephyr-7B M2 2.66x</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Heads now run sequentially (one call per draft position), so drafting latency grows with depth; Hydra++ extra decoder layer adds its own KV cache; retrained per target</t>
+          <t>Heads run sequentially (one call per draft position; Hydra++ heads 0.6-1.4 ms each vs Medusa 0.3 ms), so drafting latency grows with depth; Hydra++ prefix attention layer adds its own KV cache; retrained per target</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Hydra++ 2.70x vs AR, 1.27x vs Medusa (Vicuna-7B, A100-40GB, bs1); 1.63x at bs8</t>
+          <t>Hydra++ 2.70x vs AR, 1.27x vs Medusa (Vicuna-7B, A100-40GB, bs1, MT-Bench); SpecBench avg 2.17x vs Medusa 1.75x; gap to Medusa shrinks at bs8 (fig.)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench; summarization and RAG tasks (names not captured)</t>
+          <t>MT-Bench; SpecBench (MT chat, translation, summarization, QA, math, RAG)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0.24B / 0.37B / 0.56B / 0.99B drafter for 7B/13B/33B/70B + 1-layer KV</t>
+          <t>0.24B / 0.37B / 0.56B / 0.99B drafter for 7B/13B/33B/70B (0.28B Mixtral) + 1-layer KV</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>tau 3.98 (Vicuna-13B, T=0, MT-Bench); 3.81 (LLaMA2-Chat-70B, T=0)</t>
+          <t>tau 3.98 (Vicuna-13B, T=0, MT-Bench), 3.20 at T=1; 3.81 (LLaMA2-Chat-70B, T=0)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3.03x (Vicuna-13B, bs1, T=0, MT-Bench); ~2x throughput at max batch</t>
+          <t>~2.8-3.0x MT-Bench T=0 bs1 (figure); HumanEval 3.33-3.76x; throughput 1.97x (Vicuna-7B, bs8, RTX 3090), 1.99x (L2-70B, bs5, 4x A100-40G)</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench T=0: Vicuna-7B 2.90x/tau 3.94, 13B 3.03x/3.98, 33B 2.97x/3.68; LLaMA2-Chat-70B 2.87x/3.81 (T=1 2.92x)</t>
+          <t>MT-Bench T=0 tau: V7B 3.94, V13B 3.98, V33B 3.68, L2-7B 3.62, L2-13B 3.90, L2-70B 3.81; HumanEval L2-70B 3.52x/4.42, L2-13B 3.76x/4.52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>same as EAGLE (0.24B for 7B) + 1-layer KV</t>
+          <t>same as EAGLE (reuses EAGLE drafter, 0.24B for 7B) + 1-layer KV</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1458,17 +1458,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>tau 4.83 (Vicuna-13B, T=0); 4.53 (LLaMA3-Instruct-8B, T=0); dataset column ambiguous in extraction</t>
+          <t>tau 4.83 MT-Bench, mean 4.65 (Vicuna-13B, T=0); mean 4.40 at T=1</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4.26x (Vicuna-13B, T=0, bs1); 3.80x at T=1</t>
+          <t>4.26x MT-Bench, 4.04x mean (Vicuna-13B, T=0, bs1); 3.80x mean at T=1; hardware not stated</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>T=0: Vicuna-13B 4.26x/tau 4.83; LLaMA2-Chat-70B 3.51x/4.48; LLaMA3-8B 3.46x/4.53; LLaMA3-70B 3.29x/4.16</t>
+          <t>T=0 MT-Bench: Vicuna-13B 4.26x/tau 4.83; L2-Chat-70B 3.51x/4.48; L3-8B 3.46x/4.53; L3-70B 3.29x/4.16; mean: L2-7B 3.43x/4.64, L2-13B 4.10x/4.68</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>not captured from EAGLE-3 itself; GTO re-run: tau 6.07 (LLaMA-3.1-8B, T=0), 6.80 (Vicuna-13B)</t>
+          <t>tau 6.65 (Vicuna-13B), 6.13 (LLaMA-3.1-8B), 5.63 (L3.3-70B), T=0; mean 5.99 T=0, 4.90 T=1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench, HumanEval, GSM8K, Alpaca, CNN/DM (unv.)</t>
+          <t>MT-Bench, HumanEval, GSM8K, Alpaca, CNN/DM</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Multi-step (3-step) alignment multiplies training cost vs EAGLE; needs target top-K logits during training; inherits EAGLE-2 per-target drafter and target-feature dependency</t>
+          <t>Multi-step (n=3) alignment costs n times EAGLE training (stated); needs target top-K logits during training; inherits EAGLE-2 per-target drafter and target-feature dependency</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4.05x (LLaMA3-Instruct-70B, H800, bs1, T=0)</t>
+          <t>4.05x (LLaMA3-Instruct-70B, H800, bs1, T=0, mean of 3 sets); T=1 3.85x</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1704,22 +1704,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>tau 5.44 (LLaMA3-Instruct-8B, T=0); 4.82 at T=1</t>
+          <t>tau 5.38 mean / 4.85 MT-Bench (LLaMA3-Instruct-8B, T=0); 5.20 mean at T=1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3.28x (LLaMA3-8B, A100 80G, bs1, T=0); README claims up to 4.2x</t>
+          <t>3.35x mean (LLaMA3-8B, A100 80G, bs1, T=0); vLLM chain-2: 1.52x bs2 -&gt; 1.25x bs16; README claims up to 4.2x</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>T=0: L3-8B 3.28x/tau 5.44; Vicuna-7B 4.03x/5.47; L2-Chat-7B 3.12x/5.11; L3-70B 3.99x/5.17 (EAGLE-2 4.01x/5.21)</t>
+          <t>T=0 mean: L2-7B 3.28x/tau 5.44; L2-13B 3.74x/5.70; L3-8B 3.35x/5.38; Vicuna-7B 4.23x/5.76 (HASS 4.03x/5.47); L3-70B 3.52x/4.66 (NeurIPS ver., 2 GPUs)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench, HumanEval, GSM8K</t>
+          <t>MT-Bench, HumanEval, GSM8K (also Qwen2-7B, Mixtral-8x7B in NeurIPS ver.)</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>not reported; ~2 transformer-layer equivalent (LSTM + attention + MLP), ~0.4B for 7B (est.) + KV</t>
+          <t>not reported as count; drafter 'comparable to two Transformer layers' (2 LSTM + attention + MLP), ~0.4B for 7B (est.) + KV</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>not captured</t>
+          <t>tau 3.34 / 3.88 / 3.70 (Vicuna-7B, MT-Bench/HumanEval/GSM8K, T=0)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2.91-3.51x on Vicuna and LLaMA2-Chat (hardware/bs not captured)</t>
+          <t>2.91-3.51x (H800, bs1, T=0 only); 1.01-1.24x over EAGLE</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B/13B, LLaMA2-Chat-7B/13B: 2.91-3.51x (per-model split not captured)</t>
+          <t>T=0 MT-Bench: Vicuna-7B 3.10x/3.34; V13B 2.97x/3.37; L2-Chat-7B 2.94x/2.82; L2-13B 3.11x/2.95 (HumanEval up to 3.51x)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1858,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>not reported (lightweight RNN drafter + per-beam state)</t>
+          <t>not reported (one-layer RNN + few MLP layers drafter, + per-beam state)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>lossless at T=0; T&gt;0 implementation may not match distribution (README)</t>
+          <t>lossless (stated); README notes T&gt;0 implementation may not match distribution</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2.80x (Vicuna-7B/13B, H100, PyTorch, bs1, greedy); MLX M2 Ultra 13B 1.94x (abstract: up to 2.3x)</t>
+          <t>2.80x (Vicuna-7B/13B, H100, PyTorch, bs1, greedy); MLX up to 2.3x M2 Ultra, 1.37x M1 Max; bs80 BW2 ~1636 tok/s total (H100, 7B)</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench: Vicuna-7B 2.80x/tau 4.20; 13B 2.80x/4.21; 33B 2.61x/3.87 (EAGLE 2.69/2.74/2.80x)</t>
+          <t>MT-Bench: Vicuna-7B 2.80x/tau 4.20; 13B 2.80x/4.21; 33B 2.61x/3.87 (EAGLE 2.69/2.74/2.80x); AlpacaEval 7B 2.69x/4.06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3.73x (LLaMA-3.1-8B, A100 80GB, bs1, T=0); +7.7% over EAGLE-3</t>
+          <t>3.73x (LLaMA-3.1-8B, A100 80GB, bs1, T=0) vs EAGLE-3 3.46x; T=1 2.89x</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2.62x MT-Bench, 3.35x HumanEval (LLaMA-3.1-8B EAGLE-3, vLLM 0.11, bs1, T=0)</t>
+          <t>2.62x MT-Bench, 3.35x HumanEval (LLaMA-3.1-8B EAGLE-3, vLLM 0.11, bs1, T=0); hardware not stated</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3.1-8B EAGLE-3: tau 3.84 (T=0), speed 2.62x MT-Bench; LLaMA-3.3-70B also tested (numbers not captured)</t>
+          <t>LLaMA-3.1-8B EAGLE-3: tau 3.84 (T=0), 2.62x MT-Bench; MLP speculator HumanEval tau 2.42 -&gt; 2.83; LLaMA-3.3-70B EAGLE-3 mean tau 4.81 T=0 (+0.5%), 4.66 T=1 (+3.5%)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Training needs the target in the loop for rollouts (RL-style verl stack, teacher inference memory); per-target retraining; main recipe is on a DFlash block drafter, so inherits its target-feature dependency</t>
+          <t>Training needs the target in the loop for rollouts (verl RL stack, ~120 H200 GPU-h for Qwen3-4B); per-target retraining; main recipe is on a DFlash block drafter, so inherits its target-feature dependency</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>not reported (DFlash b16 or EAGLE-3 drafter, same as base drafter)</t>
+          <t>not reported as count; 5-layer drafter for 4B/8B targets (8 layers for 30B), same as base drafter</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>mean 4.86x (Qwen3-4B, T=0 thinking), 4.89x (Qwen3-8B); hardware/bs not captured</t>
+          <t>mean 4.86x (Qwen3-4B, T=0 thinking), 4.89x (Qwen3-8B); H200, bs1</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Each training step runs a simulated verification (target forward), raising training cost; verification head is training-only; drafter still per-target</t>
+          <t>Supervision comes from simulated verification against the target's outputs, so the drafter is tied to that target and acceptance rule and retrained per target; inherits base drafter's target-feature dependency</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4.39x vs 4.07x (Qwen3-4B EAGLE-3, A100 80GB, bf16, HF, T=0)</t>
+          <t>4.39x vs 4.07x (Qwen3-4B EAGLE-3, A100 80GB, bf16, HF Transformers, T=0); DFlash 4.81x vs 4.54x</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3.1-8B: EAGLE-3 tau +2.5%, speed +3.8%; DFlash tau +3.8%, speed +3.4%</t>
+          <t>LLaMA-3.1-8B T=0: EAGLE-3 tau 5.66 -&gt; 5.81, 3.84x -&gt; 3.97x; DFlash tau 5.39 -&gt; 5.59, 4.19x -&gt; 4.34x</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/naver-ai/VAT (per paper; README not fetched)</t>
+          <t>https://github.com/naver-ai/VAT</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Ens-EAGLE keeps N=O(log T) drafter copies with different learning rates (memory xN); online updates use serving GPUs and drafter drifts; Online-LR variant is step-level and lossy</t>
+          <t>Ens-EAGLE keeps N drafter copies (N=3 in experiments) with different learning rates (memory xN); online updates need training compute and the drafter drifts during serving; Online-LR variant is step-level and lossy</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2268,27 +2268,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Ens: N=O(log T) drafter copies + optimizer state (not quantified); Opt-Hydra: Hydra heads + momentum state</t>
+          <t>Ens: 3 drafter copies + optimizer state (not quantified); Opt-Hydra: Hydra heads + momentum state</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>lossless (token-level variants); Online-LR lossy (MMLU acc 84.52% reported)</t>
+          <t>lossless (token-level variants); Online-LR lossy (Qwen3-8B MMLU 84.52% vs target 83.81%)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>tau 2.70 (Opt-Hydra, Vicuna-7B, Alpaca-finance); 2.73 (Vicuna-13B); 2.01 (Ens-EAGLE, GSM8K)</t>
+          <t>tau 2.70 (Opt-Hydra, Vicuna-7B, Alpaca-finance); 2.94 (Llama-2-7B-Chat, GSM8K); 2.01 (Ens-EAGLE, Vicuna-7B, GSM8K)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1.55x (Opt-Hydra, Vicuna-7B); 1.84x (Vicuna-13B); 4x A800 80GB</t>
+          <t>vs vanilla SD (not AR): Opt-Hydra 1.18-1.55x (Vicuna-7B), 1.61-2.03x (Llama-2-7B-Chat); 4x A800 80GB</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B: Opt-Hydra 1.55x/tau 2.70, Ens-EAGLE 1.41x/2.01, Ens-EAGLE-3 1.26x/2.16; Vicuna-13B Opt-Hydra 1.84x/2.73</t>
+          <t>vs vanilla SD: Vicuna-7B Opt-Hydra 1.55x/2.70, Ens-EAGLE 1.41x/2.01, Ens-EAGLE-3 1.27x/2.07; Llama-2-7B-Chat Opt-Hydra 2.03x/3.28 (Spider), Ens-EAGLE 1.61x/1.82</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>venue? (not stated)</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>~462 MB drafter, 127 MB trainable private part</t>
+          <t>~462 MB drafter params (full retrain), 127 MB trainable private part (27.5%)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>tau 4.79 vs 4.37 (Qwen2.5-Math-7B, T=0); 5.18 vs 4.59 (Coder-7B)</t>
+          <t>tau 5.19 vs 4.69 full FT (Qwen2.5-Math-7B, T=0); 5.18 vs 4.59 (Coder-7B); 4.21 vs 3.89 (Meditron3-Qwen2.5-7B)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3.06x vs ~2.88x (Math-7B, T=0, notes); PDF extract 3.27x, README 3.45x (inconsistent); 4x H200</t>
+          <t>3.27x vs 3.07x full FT (Math-7B, T=0); Coder 3.11x vs 2.76x; 4x H200 stated (other extract gave 3.06x; numbers conflict)</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Draft still runs ~50% of target depth per token, capping speedup; skip set searched offline per model (2.5-6 h BO) and static, so it degrades under task shift</t>
+          <t>Draft still runs ~50% of target depth per token, capping speedup; skip set searched offline per model (BO, 1000 iters, ~2.5 h 13B, ~6 h 70B) and static, so it degrades under task shift</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (ROUGE-2 0.108 vs 0.106 LLaMA-2-13B CNN/DM; Pass@1 0.317 vs 0.311 CodeLLaMA-13B)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>acceptance 0.85-0.92 (LLaMA-2, greedy); tau not reported</t>
+          <t>acceptance ~0.92 (LLaMA-2-13B CNN/DM, greedy), 0.85-0.92 across LLaMA-2; tau not reported</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1.22-1.99x (A100, HF, bs1 implied); best 1.99x LLaMA-2-70B CNN/DM</t>
+          <t>1.22-1.99x (A100 40/80GB, HF transformers 4.33, bs1, greedy; T=0.2/0.6 sampling also tested); best 1.99x LLaMA-2-70B CNN/DM</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>CNN/DM, XSum, HumanEval</t>
+          <t>CNN/DM, XSum, HumanEval (GSM8K, MT-Bench in later version)</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2514,32 +2514,32 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>none extra (single model, shared KV and exit head)</t>
+          <t>none extra (single model, shared exit LM head; draft KV and hidden states reused by verify)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>lossless vs the LayerSkip-trained model (which differs from original checkpoint)</t>
+          <t>lossless vs the LayerSkip-trained model; trained model has minimal last-layer accuracy drop vs original (continual pretraining)</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>not reported in abstract (acceptance tracked in paper)</t>
+          <t>token acceptance 68.9% Llama2-7B / 74.5% 13B CNN/DM (E=8, d=12, continual PT); 77.8% 7B from scratch; 45% Llama1-7B HumanEval; tau not reported</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>up to 2.16x CNN/DM, 1.82x coding, 2.0x TOPv2 (hardware not recorded)</t>
+          <t>up to 2.16x CNN/DM (Llama2-7B, scratch PT), 1.82x HumanEval (A100), 2.0x TOPv2; H100, greedy, max 512 tokens, bs1</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Llama2-7B/13B, Llama 1.5B, Llama1-7B code (v1); later versions add Llama3 (unv.); up to 2.16x</t>
+          <t>Llama2-7B 1.86x / 13B 1.81x CNN/DM, 7B 1.54x XSum (continual PT); Llama2-7B 2.16x, 1.5B 1.76x CNN/DM (scratch); Llama1-7B 1.82x HumanEval; Llama 1.5B 2.0x TOPv2</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>CNN/DM, HumanEval, TOPv2, MMLU, NaturalQuestions</t>
+          <t>CNN/DM, XSum, HumanEval, TOPv2 (+ MMLU, NaturalQuestions etc. for last-layer accuracy)</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67M adapter (Vicuna-7B) + its 1-layer KV</t>
+          <t>67M adapter (Vicuna-7B; 88.7% fewer than Medusa 591M) + its 1-layer KV</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>compression rate 1.41-2.22 by Spec-Bench subtask (Vicuna-7B, per fetched table)</t>
+          <t>compression rate 1.41-2.22 by Spec-Bench subtask (Vicuna-7B)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>up to 1.68x Spec-Bench; avg 1.50x Vicuna-7B, 1.44x Vicuna-13B (V100, bs1 implied)</t>
+          <t>avg 1.50x Vicuna-7B (1.24x translation to 1.68x MT-Bench), 1.44x Vicuna-13B (V100; bs and temperature not stated; exit l=2/3, eta 0.6, gamma 6)</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B avg 1.50x (up to 1.68x), Vicuna-13B 1.44x</t>
+          <t>Vicuna-7B avg 1.50x (up to 1.68x MT-Bench, 1.61x math), Vicuna-13B avg 1.44x (up to 1.66x MT-Bench)</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>acceptance 98-100% greedy (LLaMA-2); tau not recorded</t>
+          <t>mean generated length M 4.34 CNN/DM, 3.13 GSM8K, 8.21 TinyStories (LLaMA-2-13B, greedy); 3.85/2.99/6.17 (LLaMA-2-70B); 4.75 CodeLLaMA-13B HumanEval</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>tau 1.28-6.22 (LLaMA-3-8B, T=0), 2.57-5.81 (LLaMA-3-70B, T=0); T=1: 0.98-4.26 (8B), 1.53-5.38 (70B), by Spec-Bench task</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0.52-2.26% memory overhead (LayerSkip 0.50-1.42%)</t>
+          <t>0.52-2.26% memory overhead (avg 1.54%)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2.16-2.62x vs AR (A100/H100, bs1, greedy and T=0.6)</t>
+          <t>1.98-2.84x vs AR by model and task (A100 40GB / H100 80GB, bs1, T=0.6 sampling, greedy for pass@1)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3-8B 2.62x; LLaMA-2-7B 2.50x; LLaMA-2-70B 2.84x (as summarized); CodeLLaMA-7B 2.26x; also Llama-3.2-1B, 13B, CodeLlama-34B</t>
+          <t>LLaMA-2-7B 2.12-2.75x, 13B 1.98-2.29x, 70B 2.12-2.84x by task; LLaMA-3-8B 2.62x; Llama-3.2-1B 2.36x; CodeLLaMA-7B/34B 2.26x/2.12x HumanEval</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Lossy early exit, output can differ from the full model; predictors trained per model and need an EAGLE draft model for features</t>
+          <t>Lossy early exit, output can differ from the full model; predictors trained per model and need an EAGLE draft model for features; predictors add ~5.6% latency</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2.25x cloud (A100 80GB vs HF), 2.43x PC (RTX 4060 laptop vs llama.cpp)</t>
+          <t>2.25x cloud (Llama2-7B, A100 80GB vs HF, combined with other opts), 2.43x PC (RTX 4060 laptop vs llama.cpp); SpecEE alone 1.23-1.43x vs HF; 256 output tokens, bs not stated</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Llama2-7B 2.25x cloud / 2.43x PC; Llama2-13B/70B 1.14x/1.12x over HF baseline component</t>
+          <t>Llama2-7B 2.25x cloud / 2.43x PC; Llama2-13B 1.43x, 70B 1.23x vs HF (A100); with EAGLE 1.05x/1.06x over EAGLE (7B/13B)</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3098,32 +3098,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>acceptance &gt;90% (91.16% LWM-Text-Chat-128K at 128K)</t>
+          <t>acceptance 89.9-94.3%: 91.16% Llama-2-7B-32K (Multi-LexSum 32K), 94.31% LWM-Text-Chat-128K (Multi-LexSum 128K)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>up to 2.49x (Llama-2-7B-32K-Instruct, 32K ctx, bs1, A6000)</t>
+          <t>up to 2.49x (LWM-Text-Chat-128K, 128K ctx, bs1, 2x A6000); 1.35x at 4K to 2.08x at 32K (Llama-2-7B-32K-Instruct)</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Llama-2-7B-32K-Instruct up to 2.49x; LWM-Text-Chat-128K (Llama-2-based)</t>
+          <t>Llama-2-7B-32K-Instruct 1.35-2.08x (4K-32K); LWM-Text-Chat-128K (Llama-2-based) 1.78-2.49x (16K-128K)</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>PG-19, Multi-LexSum, LWM long-context, 4K-128K</t>
+          <t>PG-19, Multi-LexSum, InfiniteBench Sum; contexts 4K-128K</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>none found (no link in paper)</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3175,22 +3175,22 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>lossless vs W4A16 (W4A4 alone loses e.g. 25-51% on GSM8K/MATH)</t>
+          <t>lossless vs W4A16 (W4A4 alone loses 25-51% relative, e.g. GSM8K 73.4 to 54.2, Llama-3-8B Atom)</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>not recorded (gamma=3)</t>
+          <t>not reported as tau (gamma=3; &gt;80% W4A4/W4A16 token agreement)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>avg 1.38x, up to 1.64x throughput vs W4A16 (Llama-2-7B, bs32, L20 48GB)</t>
+          <t>avg 1.38x, up to 1.64x throughput vs W4A16 (Llama-2-7B, bs32; 4x L20 48GB, gamma 3, group size 128)</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Llama-2-7B up to 1.64x vs W4A16; Llama 3B/8B/13B tested</t>
+          <t>Llama-2-7B avg 1.58x (up to 1.64x), Llama-2-13B 1.47x, Llama-3.2-3B 1.25x vs W4A16; Llama-3-8B quality tests</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>acceptance ~0.92 (T=0), &gt;0.9 at T=1</t>
+          <t>acceptance &gt;0.9 across temperatures (Llama2-7B-128K, retrieval-cache draft)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3349,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>up to 2x LLaMA-2-7B-32K (32K, bs32), 1.84x LLaMA-3.1-8B (100K, bs32), 8x A100, greedy</t>
+          <t>up to 2x LLaMA-2-7B-32K (32K, bs32), 1.84x LLaMA-3.1-8B (100K, bs32) on 8x A100; 1.84x LLaMA-2-7B (8K, bs64) on 4x H100; greedy, 64 output tokens</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-2-7B-32K up to 2x; LLaMA-3.1-8B 1.84x; TinyLlama-1.1B draft variant</t>
+          <t>LLaMA-2-7B-32K up to 2x; LLaMA-3.1-8B 1.84x (100K), 1.43x (64K); TinyLlama-1.1B draft variant</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>lossless (greedy)</t>
+          <t>lossless (identical BLEU to greedy)</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>up to 38% faster than AR; ~2x with parallel resources (MT models)</t>
+          <t>PGJ up to 38% faster on CPU (Opus); HGJ 1-8% faster on GPU (MBart50); ~2x bound with parallel resources</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>machine translation benchmarks (not recorded)</t>
+          <t>WMT14, WMT16, WMT17, IWSLT15, IITB, FLORES</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Spends 56-120x extra FLOPs per step, so it slows in compute-bound settings (large batch); Jacobi guesses from an untrained model have low hit rate</t>
+          <t>Spends 56-120x extra FLOPs per step (W=15,N=5 at 7B), so it slows in compute-bound settings (large batch) and weak GPUs (~30% on RTX 3090); Jacobi guesses from an untrained model have low hit rate</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>step compression ~1.5-2.0</t>
+          <t>step compression ~1.6-2.05 (LLaMA-2-7B MT-Bench ~2.0; summarization 1.64-1.77)</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Modifies target weights, so output is not guaranteed equal to the original model; needs per-domain trajectory generation and training (2-30 A100 h)</t>
+          <t>Modifies target weights, so output is not equal to the original model; needs per-domain trajectory generation and training (2-30 h on 8x A100)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3585,22 +3585,22 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>lossless vs CLLM; vs original: near-no accuracy loss reported</t>
+          <t>lossy vs original fine-tuned target: GSM8K 59.1 to 56.4, Spider 70.0 to 69.3, CSN 60.4 to 59.2, MT-Bench 6.5 to 6.4</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>not recorded (fast-forwarded tokens per iteration reported)</t>
+          <t>not reported as tau; fast-forwarded tokens per iteration 2.0-6.8x vs base model</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2.4-3.4x Jacobi, 2.5-3.6x with lookahead (A100, bs1)</t>
+          <t>Jacobi 2.4-3.4x, lookahead 2.5-3.6x (A100 40GB, bs1); e.g. GSM8K 43.5 to 132.4 tok/s</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-2-7B-based targets: 3.0x GSM8K, 2.4x ShareGPT/MT-Bench (Jacobi)</t>
+          <t>LLaMA2-7B-based targets: GSM8K 3.0x Jacobi / 2.9x lookahead; ShareGPT/MT-Bench 2.4x / 2.5x</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>mean generated length 1.77 Vicuna-7B/13B MT-Bench greedy (1.72 nucleus); 2.65/2.45 CodeLlama-7B/13B HumanEval greedy</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B 1.69x, Vicuna-13B 1.77x (MT-Bench greedy); CodeLlama-7B 2.36x, 13B 2.27x (HumanEval)</t>
+          <t>Vicuna-7B 1.69x, 13B 1.77x MT-Bench greedy (1.62x/1.71x nucleus); CodeLlama-7B 2.36x, 13B 2.27x HumanEval greedy</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (HF transformers: works with greedy and sampling)</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>avg ~2.4x on summarization and context QA (Mistral-7B-Instruct, A100 40GB); smaller on MT-Bench</t>
+          <t>avg ~2.4x on summarization (CNN/DM) and context QA (HAGRID) (Mistral-7B-Instruct-v0.1, A100 40GB, greedy, max_ngram 3, 10 draft tokens); little gain on MT-Bench turn 1</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>suffix trees in CPU RAM (~6.15 GB per 572M cached tokens)</t>
+          <t>suffix trees in CPU RAM (~6.15 GB per 572M cached tokens); ~20 us per draft token</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6.3 AgenticSQL, 7.8 SWE-Bench, 1.75 Spec-Bench (Llama-3.1-8B-Instruct)</t>
+          <t>6.3 AgenticSQL, 7.8 SWE-Bench, 1.75 Spec-Bench (Llama-3.1-8B-Instruct, greedy); hybrid with EAGLE-3 4.68 Spec-Bench</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5.3x AgenticSQL, 2.5x SWE-Bench, hybrid 2.5x Spec-Bench (H100, bs1, vLLM)</t>
+          <t>5.3x AgenticSQL, 2.5x SWE-Bench, 1.66x Spec-Bench alone, hybrid 2.46x Spec-Bench (H100, bs1, greedy); vLLM run with OpenHands-LM-32B, 8 concurrent, TP4</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>MAT 3.03 (+Token Recycling), 3.77 (+EAGLE), 4.61 (+EAGLE-2) Spec-Bench; HumanEval 2.94/4.03/4.79 (Vicuna-7B, greedy)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>https://github.com/hyx1999/SAM-Decoding</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>MAT 2.70 (Vicuna-7B), 2.72 (13B), 2.63 (33B), Spec-Bench, greedy</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>n-1 extra transformer-layer heads (7B, n=4: ~0.6B, est.)</t>
+          <t>n-1 extra heads, one transformer layer each, shared unembedding (7B, n=4: ~0.6B, est.)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MBPP, HumanEval, APPS (unv.); NLP benchmarks</t>
+          <t>MBPP, HumanEval, APPS, CodeContests; ARC-C, COPA, HellaSwag, NQ, PIQA, SIQA, TriviaQA; CNN/DM, XSum and 5 other summarization sets; GSM8K</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Sequential depth-1 MTP module trained with the model; reused as a 1-token speculative drafter</t>
+          <t>Sequential depth-1 (D=1) MTP module (1 transformer block, shared embedding and output head) trained with the model; reused as a 1-token speculative drafter</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1 MTP module ~14B params on 671B model (unv.) + its KV</t>
+          <t>1 MTP module, 14B params (685B total = 671B main + 14B MTP) + its KV</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2nd-token acceptance 85-90% (unv.)</t>
+          <t>2nd-token acceptance 85-90% across generation topics</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>~1.8x TPS (unv.)</t>
+          <t>1.8x TPS (hardware, batch not stated)</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>various generation topics (not specified)</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1 MTP head (already in MiMo) + its KV; compressed draft vocab</t>
+          <t>1 MTP head (already in MiMo), 210.8M params fine-tuned (&lt;3% of backbone) + its KV; draft vocab 16K zh / 32K en</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>7 benchmarks, general NLP, math, code (names not recorded)</t>
+          <t>MT-Bench, LiveCodeBench-v6, MATH-500, Natural Questions (QA, RAG), CNN/DM, C-Eval</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>gated LoRA + 2-layer sampler (size not reported; small, est.)</t>
+          <t>rank-128 gated LoRA + 2-layer MLP sampler (counts not reported; small vs 8B, est.)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>up to ~5x tokens/step math and code, ~2.5x chat (Tulu3-8B, k=8)</t>
+          <t>tokens/step (k=8): 5.22 math, 5.35 code, 2.39-2.52 chat, 1.91-2.38 knowledge, 2.79-3.72 safety (Tulu3-8B)</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>math, code, chat, knowledge tasks of Tulu3 eval (names not recorded)</t>
+          <t>GSM8K, HumanEval, AlpacaEval, IFEval, MMLU, PopQA, TruthfulQA, safety (XSTest, HarmBench, etc.)</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>each head predicts its offset independently, so later heads ignore earlier choices; heads share the base trunk, so proposal quality is capped by one hidden state</t>
+          <t>each head predicts its offset independently, so later heads ignore earlier choices; heads share one trunk hidden state; high acceptance needs fine-tuning the trunk, which changes the base model being decoded</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4482,22 +4482,22 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) k-1 extra output heads on the base model, no extra KV</t>
+          <t>one extra FFN layer (hidden k x d_hidden, out k x d_model) on a transformer_base model; no extra KV</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>lossless (exact-match variant); lossy variants trade quality for up to 7x fewer iterations</t>
+          <t>lossless vs the (possibly fine-tuned) scoring model; dev BLEU 26.00 base vs 26.11 at k=8 (distill+FT); top-k approx lossy: 25.04 BLEU at k=10 top-2</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; up to 2x fewer decoding iterations lossless (MT)</t>
+          <t>mean accepted block (WMT dev, greedy): 1.76 regular k=8; 4.69 distill+FT k=8, 4.95 k=10; super-res 6.79 at k=10 (FT+approx)</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>up to 4x wall-clock (MT and image super-resolution Transformers, greedy)</t>
+          <t>MT up to 3.3x wall-clock (k=8, block 4.7); test k=2 28.95 BLEU 1.72x, k=8 27.88 BLEU 3.31x; super-res 4.0x (k=6); greedy, hardware/bs not extracted</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>WMT14 En-De MT (unv.), image super-resolution (unv.)</t>
+          <t>WMT 2014 En-De (newstest2013 dev, newstest2014 test), CelebA image super-resolution (8x8 to 32x32)</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR 2026</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>separate small LM: Llama3.2-1B (for LLaMA3), Qwen2.5-0.5B, R1-Distill-Qwen-1.5B, plus its KV</t>
+          <t>separate small LM: Llama3.2-1B (LLaMA3 targets), Qwen2.5-0.5B, R1-Distill-Qwen-1.5B, plus its KV</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>not reported as tau; LLaMA3.1-8B acceptance 1-alpha 0.93 / 4-alpha 0.90 HumanEval, 0.88/0.85 GSM8K (EAGLE-3 0.87/0.85); K_infer 12</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>LLaMA3.1-8B avg 3.57x / 274.4 tok/s, HumanEval 4.08x / 311.5 tok/s; Qwen2.5-7B 4.87x (A100-40GB, bs1, T=0, Transformers+); abstract v4: 3.67x / 264.88 tok/s (versions conflict)</t>
+          <t>vLLM, A100-40GB, bs1: LLaMA3.1-8B avg 3.00x / 219.15 tok/s; Qwen2.5-7B avg 3.18x, HE 3.76x; abstract 3.67x / 264.88 tok/s (earlier version: Transformers+ 3.57x)</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>LLaMA3.1-8B: HumanEval 4.08x, MATH500 3.35x, GSM8K 3.30x, avg 3.57x (Llama3.2-1B drafter)</t>
+          <t>vLLM A100 bs1: LLaMA3.1-8B HE 3.63x (264.88 tok/s), GSM8K 3.20x, SpecBench 2.17x, avg 3.00x; LLaMA3.3-70B HE 4.11x, GSM8K 3.94x, avg 3.49x (84.29 tok/s)</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>HumanEval, GSM8K, MATH500</t>
+          <t>HumanEval, GSM8K, SpecBench, MATH500 (appendix)</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/AMD-AIG-AIMA/PARD</t>
+          <t>https://github.com/AMD-AGI/PARD</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Dream-7B drafter (~15 GB bf16, est.) plus its context processing</t>
+          <t>Dream-7B drafter (~15 GB bf16, est.) plus its context processing; no extra training</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>MAT 6.99 across tasks (Qwen2.5-32B, T=0)</t>
+          <t>MAT mean 6.99 (Qwen2.5-32B, T=0): MT 7.02, Trans 7.35, Sum 6.25, QA 7.49, Math 7.61, RAG 8.04</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>up to 3x, mean 3.08x (Qwen2.5-32B, A100-80GB, T=0)</t>
+          <t>mean 3.08x, Math 4.02x, Sum 2.41x, RAG 2.38x (Qwen2.5-32B, 1x A100-80GB, bs1, T=0); path search ~1.1% overhead; draft len 20-30</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>self-selection needs several drafter samples per round (extra drafter compute); block positions sampled from marginals, so drafts can be incoherent</t>
+          <t>self-selection needs several drafter samples per round (extra drafter compute); block positions sampled from marginals, so drafts can be incoherent; full 7B diffusion drafter tied to one tokenizer family</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>not reported (diffusion LM drafter, size not extracted)</t>
+          <t>7B diffusion drafter (DiffuCoder-7B for Qwen, DiffuLLaMA-7B for Llama-2) plus its context processing (~14 GB bf16, est.)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; later positions get 3.2x higher acceptance than AR drafter</t>
+          <t>tokens/draft: Qwen2.5-14B Math500 6.20 (T=0); Qwen2.5-72B Math500 7.00 (T=1); EAGLE-2 4.25/4.63</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>up to 5.5x avg over AR, +55% tok/s over prior baselines (Qwen2.5-14B/72B, Llama 13B/70B; hardware and T in appendix, not extracted)</t>
+          <t>up to 5.5x avg over AR, +55% tok/s over baselines; Qwen2.5-72B Math500 5.01x (T=1), Qwen2.5-14B 3.65x (T=0) (A100-80GB)</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Llama 13B and 70B targets used; per-model numbers not extracted</t>
+          <t>LLaMA-2-70B-Chat HumanEval 5.28x, 7.40 tok/draft (T=1); LLaMA-2-13B-Chat Math500 3.61x, 6.31 (T=0); EAGLE-2 3.91x / 3.48x</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Math500, Alpaca, others not extracted</t>
+          <t>Math500, HumanEval, GPQA, GSM8K, LiveCodeBench, MT-Bench</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>dLLM block positions independent given context; separate dLLM drafter retrained per target family</t>
+          <t>dLLM block positions independent given context; separate dLLM drafter retrained per target family (~240 GPU-h for Qwen3-8B); dLLM KV caching lacks support in vLLM/SGLang, hurting batched serving</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>not reported (dLLM drafter, size not stated)</t>
+          <t>~0.5B (~470M) diffusion drafter (from open-dCoder or Qwen2.5-0.5B) plus its KV</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -4820,12 +4820,12 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>~5 avg, max 32 (Qwen3-30B-A3B, T=0)</t>
+          <t>T=0 mean tau 4.61 (Qwen3-4B), 4.61 (8B), 4.82 (14B), 5.03 (30B-A3B); HumanEval 30B-A3B 6.58; max accepted 32 vs EAGLE-3 8</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-4B ~2.8-3.0x, 8B ~3.0x, 14B 3.1-3.7x, 30B-A3B up to 5.54x HumanEval (A100, T=0)</t>
+          <t>T=0, A100-80GB: 30B-A3B HumanEval 5.54x, MBPP 4.00x; 8B 2.35-3.30x; 14B 2.43-3.59x; bs16 HumanEval 175.66 vs AR 49.76 tok/s (no KV cache)</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -4835,17 +4835,17 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>HumanEval, MBPP, CodeAlpaca (Python), LiveCodeBench</t>
+          <t>HumanEval, MBPP, CodeAlpacaPy, LiveCodeBench, GSM8K, Math500, Minerva Math</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/czc726/DEER</t>
+          <t>https://czc726.github.io/DEER/ (code announced)</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>parallel positions share one learned hidden state, so later positions do not see earlier drafted tokens; drafter tied to target features (retrained per target); EAGLE drafter KV grows with context</t>
+          <t>parallel positions use a shared hidden state and mask embedding, so later positions do not see earlier drafted tokens; drafter tied to target features (retrained per target); 4-layer drafter is costlier per pass than EAGLE-3 (slowdown at K=3 on MoE)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4892,42 +4892,42 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) EAGLE-3-size single-layer drafter plus its KV</t>
+          <t>4-layer drafter, 2-5% of target params (paper), plus its KV</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (standard rejection sampling in vLLM)</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>AL K=5: GPT-OSS-120B 2.9-3.5, GPT-OSS-20B 3.4-4.0, Qwen3-Coder-30B 3.0-4.5 (AR EAGLE-3 2.7-4.4); T not stated</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1.10-1.36x over AR EAGLE-3 (GPT-OSS 120B/20B, Qwen3-Coder-30B, vLLM; hardware/bs/T not extracted)</t>
+          <t>vs AR EAGLE-3, vLLM, 1x H200, C=2: GPT-OSS-20B 1.27-1.36x (1205 tok/s HumanEval, K=7); 120B 1.04-1.10x; Qwen3-Coder-30B 1.04-1.11x; no vanilla AR baseline</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ablations only, LLaMA 3.1 8B: 4-layer AL 3.92 HumanEval, 3.04 MT-Bench; 1-layer 2.69 / 2.41</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>not extracted</t>
+          <t>HumanEval, MT-Bench, GSM8K (test); training on UltraChat, GSM8K train, OpenCodeInstruct</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>in vLLM; no standalone repo found</t>
+          <t>https://github.com/vllm-project/speculators (training); vLLM inference; no released checkpoints</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>positions conditionally independent within a block (product of marginals); needs fresh target features every round, so draft and verify serialize (ours: drafter ~16% of a round); block 16 caps accepted length at 16 per round</t>
+          <t>positions conditionally independent within a block (product of marginals); needs fresh target features every round, so draft and verify serialize (ours: drafter ~16% of a round); block 16 caps accepted length; drafter retrained per target</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4974,32 +4974,32 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) ~1B drafter for Qwen3-8B (5 target-width layers + fc, shared embed/head) ~2 GB bf16; drafter KV ~5/36 of target KV, grows with context</t>
+          <t>1B drafter for Qwen3-8B and for LLaMA-3.1-8B (HF cards, ~2 GB bf16); drafter KV ~5/36 of target KV (est.), grows with context</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>lossless (not audited in bf16)</t>
+          <t>lossless</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>tau 6.49 T=0, 5.48 T=1 (Qwen3-8B avg); 8.01 SGLang Math500 (ours: tau 5.85, Qwen3-8B, A100, HF)</t>
+          <t>tau 6.49 T=0, 5.48 T=1 (Qwen3-8B avg, HF); MATH-500 7.87 T=0; SGLang Math500 8.01 (ours: tau 5.85, Qwen3-8B, A100, HF)</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 4.86x T=0, 4.03x T=1 (H200, bs1, HF); SGLang B200 Math500 5.1x c=1 to 2.8x c=32 (ours: HF 4.37x; vLLM 4.84x, 2.69 ms/tok, A100 bs1)</t>
+          <t>Qwen3-8B 4.86x T=0, 4.03x T=1 (H200, bs1, HF); SGLang B200 Math500 5.1x (1175 tok/s) c=1 to 2.8x (16076 tok/s) c=32 (ours: HF 4.37x; vLLM 4.84x, A100 bs1)</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3.1-8B-Instruct, block 10, SGLang B200: GSM8K 2.4x at c=1 to 1.6x at c=32 (EAGLE-3 0.6x at c=32)</t>
+          <t>LLaMA-3.1-8B-Instruct, block 10, SGLang B200, T=0: GSM8K 2.4x c=1 to 1.6x c=32, tau 4.32; HumanEval 2.8x, tau 4.91; Alpaca 2.2x, tau 3.73 (EAGLE-3(60) 0.6x at c=32)</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>GSM8K, MATH-500, AIME25, HumanEval, MBPP, LiveCodeBench, MT-Bench, Alpaca; GPQA (thinking); LongBench subsets</t>
+          <t>GSM8K, MATH-500, AIME24, AIME25, HumanEval, MBPP, LiveCodeBench, SWE-Bench, MT-Bench, Alpaca; thinking mode; LLaMA drafter trained on UltraChat+ShareGPT</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5036,62 +5036,62 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>blog/code only</t>
+          <t>blog (Inco AI, 2026-08-18) + HF models</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>DFlash plus grouped causal convolution per layer and a candidate selector (first-order Markov rerank of top-k)</t>
+          <t>DFlash plus two-tap dynamic depthwise conv around attention/FFN sublayers and a path selector scoring adjacent token pairs over top-16 candidates per position</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>rerank is only first-order (predecessor/successor), so longer-range dependencies stay independent; still needs fresh target features each round</t>
+          <t>conv sees only the previous position and selector scores only adjacent pairs, so longer-range in-block dependencies stay independent; still needs fresh target features each round; drafter retrained per target</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>adds left-to-right information inside the block at small cost</t>
+          <t>adds left-to-right info inside the block for ~1.3% extra latency; selector picks a coherent path instead of per-position argmax</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) DFlash-size drafter plus conv and codebook params</t>
+          <t>2B drafter for Qwen3.8-27B (HF card); conv +16.5M params (3%), selector +2.0M; plus drafter KV (est.)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>lossless (assumed, standard verify)</t>
+          <t>lossless (rejection sampling, T=1)</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>T=1 thinking: Qwen3.5-4B mean 5.97 vs DFlash 4.92; Qwen3.8-27B 4.80 (GSM8K 5.46, MT-Bench 4.10) vs MTP 4.28; Muse Glimmer 5.70 vs DFlash 4.44</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>Qwen3.8-27B 2.7-3.4x bs1, GSM8K 236.1 tok/s 3.43x (1x H200, SGLang FA3, c=1, T=1, block 8); Muse Glimmer 3.1-4.6x (block 16)</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>README lists Llama-3.1-8B as supported; no numbers found</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>GSM8K, MATH-500, HumanEval, MBPP, MT-Bench</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/z-lab/dflash</t>
+          <t>https://github.com/z-lab/dflash; HF incoai/Qwen3.8-27B-DFlash2, incoai/Muse-Glimmer-30B-DFlash2; SGLang, vLLM, llama.cpp, Ollama</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5148,12 +5148,12 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B MATH-500 tau 10.73 vs DFlash 7.79 (T=0) (ours: DDTree-128 tau 8.1, Qwen3-8B, A100)</t>
+          <t>Qwen3-8B MATH-500 tau 10.73 vs DFlash 7.79 (T=0), 9.54 vs 6.46 (T=1); Qwen3-4B 10.71 (ours: DDTree-128 tau 8.1, Qwen3-8B, A100)</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B MATH-500 7.52x vs DFlash 5.56x (H200, bs1, T=0, HF/SDPA; budget picked per cell) (ours: DDTree-128 HF 5.90x, A100)</t>
+          <t>Qwen3-8B MATH-500 7.52x vs DFlash 5.56x T=0, 6.59x vs 4.56x T=1 (H200, HF/SDPA, budget picked per cell from 16-1024) (ours: DDTree-128 HF 5.90x, A100)</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>surrogate is a product of marginals, ignores dependencies; budget controller needs hardware-calibrated latency profiles; inherits DFlash block cap and fresh-feature dependency</t>
+          <t>surrogate is a product of marginals, ignores dependencies; budget controller needs per-(GPU, target) latency calibration and assumes bs1 cost profile; inherits DFlash block cap and fresh-feature dependency</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>no extra params beyond DFlash; tree verify tokens per round; controller overhead negligible</t>
+          <t>no extra params beyond DFlash; tree verify tokens per round; controller overhead negligible (heap ops)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B tau 8.48 (T=0, A100); range 4.64-10.60</t>
+          <t>T=0 A100 avg tau: Qwen3-8B 8.48 (EAGLE-3 2.32), Qwen3-4B 8.56; range 4.64 (MT-Bench) to 10.60 (MATH500)</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 6.61x over AR, DFlash 4.56x (A100, bs1, T=0); avg 1.39x over DFlash, 2.45x over EAGLE-3</t>
+          <t>T=0, A100, bs1: Qwen3-8B 6.61x avg (EAGLE-3 2.70x; DFlash GSM8K 4.56x); Qwen3-4B 6.93x; claims 1.39x over DFlash, 2.45x over EAGLE-3; also H100, RTX PRO 6000, A6000</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-8B-Instruct: 4.46x, tau 6.00 vs DFlash 2.53x (A100, T=0)</t>
+          <t>Llama-3.1-8B-Instruct (DFlash block 10) evaluated on four GPUs; numbers only in Fig. 4, not extracted (earlier 4.46x/tau 6.00 unconfirmed)</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/kaist-ai-osi-lab/BASTION</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>~3.1-10.4 by dataset (Qwen3-4B/8B, T=0); Qwen3-4B MATH-500 10.37 vs DDTree-oracle 10.35</t>
+          <t>T=0: Qwen3-4B MATH-500 tau 10.37 vs DDTree-oracle 10.35, DFlash 7.71; Qwen3-8B DFlash 7.91; ~8.9-10.4 on math/code sets</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-4B MATH-500 4.53 ms/tok (= DDTree oracle) vs DFlash 5.93 ms/tok (A800, T=0)</t>
+          <t>Qwen3-4B MATH-500 4.53 ms/tok (= DDTree-oracle, mean budget 221 vs oracle 256) vs DFlash 5.93, AR 30.65; Qwen3-8B 4.60 vs DFlash 5.83, AR 30.95 (A800, T=0)</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/ZhangShuai1230/CaDDTree</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>arXiv (AAAI template, unconfirmed)</t>
+          <t>arXiv (AAAI template)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -5384,22 +5384,22 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) small (two linear projections + depth embeddings) on top of DFlash</t>
+          <t>not reported; (est.) small (two linear projections + depth embeddings over frozen target embeddings) on top of DFlash; scorer 0.3 ms/round</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (standard target verification; not stated explicitly)</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B GSM8K MAT 8.06 vs DDTree 8.18, DFlash 5.82</t>
+          <t>Qwen3-8B MAT: GSM8K 8.06 vs DDTree 8.18, DFlash 5.82; Math500 9.36 vs 9.38, 7.02; Alpaca 4.26 vs 4.46, 2.83</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2.13-6.36x over AR; Qwen3-8B up to 6.17x (A100-80GB, bs1)</t>
+          <t>2.13-6.36x over AR (A100-80GB, bs1, T not stated); Qwen3-8B Math500 6.17x vs DDTree 4.93x, DFlash 4.84x; Qwen3-4B 6.36x; Qwen3-Coder-30B 4.74x</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>none found</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>GRU runs sequentially over block positions, so a sequential step grows with block length; correction only helps when early positions are accepted; inherits fresh-feature dependency</t>
+          <t>Domino head updates its causal state token by token, so a sequential step grows with block length (1.20 ms/round after Triton+CUDA graphs); correction only pays off once early positions are accepted; inherits fresh-feature dependency</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>+56M params (+5.3%) on DFlash drafter (GRU 1024-d, rank 256)</t>
+          <t>+56M params (+5.3%) on DFlash drafter (GRU 1024-d, rank-256 correction); no extra KV reported</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B tau 7.08 vs DFlash 6.11 (T=0)</t>
+          <t>Qwen3-8B tau 7.17 vs DFlash 6.06 (T=0), 5.91 vs 5.18 (T=1); Qwen3-4B 7.08 vs 6.06 (T=0), 6.00 vs 5.33 (T=1)</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 5.49x vs DFlash 4.70x (A100, T=0, HF); up to 5.8x throughput in SGLang</t>
+          <t>Qwen3-8B 5.49x vs DFlash 4.66x (T=0), 4.46x vs 3.96x (T=1) (A100-80GB, Transformers); SGLang Qwen3-8B GSM8K 5.1x at c=2, 3.0x at c=16; up to 5.8x</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>only first-order conditioning (previous token); large trees conflict with production attention kernels (dense SDPA mask); inherits block cap</t>
+          <t>only first-order conditioning (previous token); trained teacher-forced, so conditioning on its own drafted tokens at inference gives exposure bias; large trees conflict with production attention kernels; inherits block cap</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B B=64: 6.73 vs DDTree 6.15, DFlash 4.71 (T=0); 5.95 vs 5.39 (T=1)</t>
+          <t>Qwen3-8B B=64 T=1: 7.62 vs DDTree 6.76; T=0 B=64 ~8.84 vs DDTree ~7.8 (table parse ambiguous); +12.4% mean tau over DDTree</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>+9.1% over DDTree at B=64 (GH200, bs1, SDPA)</t>
+          <t>Qwen3-8B B=64 T=1: 5.50x vs DDTree 5.04x; +9.1% over DDTree at B=64 (GH200, bs1, PyTorch SDPA, bf16)</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MATH-500, GSM8K, HumanEval, MBPP, MT-Bench</t>
+          <t>MATH-500, GSM8K, HumanEval, MBPP, MT-Bench; targets Qwen3-4B/8B, Qwen3-Coder-30B-A3B</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>two drafters run per round (second waits on the first); verify width grows with K branches; extra stages give diminishing returns (third stage -4% speed)</t>
+          <t>two drafters run per round (VP-drafter waits on drafter-1 confidences); verify width grows with K branches; more stages do not pay off (3rd stage: tau 7.62-&gt;8.24 but 5.35x-&gt;5.13x)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) two DFlash-size drafters (~2x drafter weights and draft KV)</t>
+          <t>not reported; VP-drafter shares DFlash architecture, so ~2x drafter weights and draft KV (est.)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 7.05 vs DFlash 5.31 (T=0); 5.45 vs 4.33 (T=1)</t>
+          <t>Qwen3-8B 7.05 vs DFlash 5.31 (T=0), 5.45 vs 4.33 (T=1); GPT-OSS-20B 8.02 vs 4.13 (T=0), 2.35 vs 1.99 (T=1); gamma 16, K=4</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 4.98x vs 4.16x (T=0), 4.01x vs 3.43x (T=1); GPT-OSS-20B 6.15x vs 3.53x (H200, HF)</t>
+          <t>Qwen3-8B 4.98x vs 4.16x (T=0), 4.01x vs 3.43x (T=1); GPT-OSS-20B 6.15x vs 3.53x (T=0), 1.84x vs 1.71x (T=1) (H200, HF Transformers, FA2)</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>not extracted (abstract only); (likely) tree verify cost grows with branches x batch</t>
+          <t>draft head is a 5-layer decoder with its own KV fed by fused target features, so it is trained per target and needs fresh features each round; 256-node tree verify cost grows with batch, gains shrink at large batch</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>not reported; (est.) ~1B draft head (5 layers, 4096 hidden, 12288 MLP for Qwen3-8B) + its KV cache</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>Qwen3-8B budget 256: MATH-500 10.76 (T=0), 9.01 (T=1); MT-Bench 5.94 (T=0); Qwen3-30B-A3B MATH-500 10.28 vs DDTree 9.71</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>up to 9.64x MATH-500, 4.58x chat (H100, Qwen3 dense and MoE; bs/T not extracted)</t>
+          <t>Qwen3-8B budget 256 T=0: MATH-500 9.64x (DDTree 8.78x), MT-Bench 4.58x (H100); vLLM MATH-500 budget 128: 4.33x bs1, 3.26x bs8, 2.80x bs16</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>MATH-500, code, chat (names not extracted)</t>
+          <t>GSM8K, MATH-500, AIME25, HumanEval, MBPP, LiveCodeBench, MT-Bench</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>sequential module runs once per draft position; scheduler depends on throughput profiling; drafter KV over full prefix grows with context (~2.5 GiB at 128K, derived from LongSpark's 406x)</t>
+          <t>sequential head samples left to right per position (+0.2-1.3% round latency); fixed upfront gamma-token draft cost is wasted on low-acceptance queries; drafter KV over full prefix grows with context (2.5 GiB at 128K per LongSpark)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>not reported; DFlash backbone + rank-256 head + linear confidence head; drafter state ~2.5 GiB at 128K (est.)</t>
+          <t>not reported; 5-layer DFlash-style backbone + rank-256 Markov/RNN head + linear confidence head; drafter state 2.5 GiB at 128K (LongSpark measurement)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>tau +16.3/18.4/18.3% vs DFlash on Qwen3-4B/8B/14B (absolute not extracted)</t>
+          <t>Qwen3-8B macro tau 4.87 vs DFlash 4.12, EAGLE-3 3.91 (T=1); +16.3/18.4/18.3% vs DFlash on Qwen3-4B/8B/14B</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek-V4 production: 60-85% per-user speedup at matched throughput</t>
+          <t>DeepSeek-V4-Flash 60-85%, V4-Pro 57-78% higher per-user speed vs MTP-1 at matched throughput (production); Qwen3 wall-clock not extracted</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>math, code, chat (names not extracted)</t>
+          <t>GSM8K, MATH500, AIME25, MBPP, HumanEval, LiveCodeBench, MT-Bench, Alpaca, Arena-Hard</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Jacobi iterations add K refiner passes to every round; refiner conditions on drafter candidates, so it cannot recover tokens outside them</t>
+          <t>Jacobi refinement adds K=4-7 batched refiner passes every round (K tuned per benchmark); refiner reranks drafter candidates, so it cannot recover tokens outside them</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) small, rank-256 refiner on DFlash</t>
+          <t>not reported; rank-256 refiner (~16x lighter than full-width) on block-16 DFlash</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>+18-56% vs DFlash at T=0, +19-58% at T=1 (Qwen3-8B)</t>
+          <t>Qwen3-8B avg tau 8.02 (T=0), 6.97 (T=1) (README); +18-56% (T=0), +19-58% (T=1) vs DFlash</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>~1.3x (up to 1.7x) over DFlash T=0, ~1.46x T=1 (Qwen3-8B, H200)</t>
+          <t>6.2x (T=0), 5.3x (T=1) over AR; ~1.29x / 1.46x over DFlash, up to 1.7x (Qwen3-8B, H200, bs1, PyTorch, 2048 tokens)</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>7 math, code and chat benchmarks (not enumerated)</t>
+          <t>GSM8K, MATH-500, AIME25, HumanEval, MBPP, LiveCodeBench, MT-Bench</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>only K=4 latent components, so dependence is coarse; trained with a biased surrogate objective and greedy-branch proposals that do not match stochastic inference</t>
+          <t>latent category sampled once per block from only K=4 components, so dependence is coarse; trained with a biased surrogate objective and proposals that do not match stochastic inference</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>&gt;12% macro tau gain over DFlash, Qwen3-8B high-entropy (T 0.7-1.5, top-p 0.8/0.95)</t>
+          <t>&gt;12% macro tau gain over DFlash, Qwen3-8B high-entropy (T/top-p 0.7/0.8, 1.0/0.95, 1.5/0.95); absolute values not extracted</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>none found</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>one correction-head pass per tree depth, so sequential steps grow with depth; tree verify cost grows with nodes x batch</t>
+          <t>one correction-head pass per tree depth, so sequential steps grow with depth; fixed-width depth-wise schedule only approximates best-first search; tree verify cost grows with nodes x batch</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>not reported; DFlash drafter + AR correction heads</t>
+          <t>not reported; DFlash drafter + pretrained AR correction module (Domino/DSpark-style)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>up to 12.97; Qwen3-8B avg 9.81 (T=0, extractor, check)</t>
+          <t>Qwen3-8B T=0 avg 9.81 vs DFlash 6.09, DDTree 7.59, Domino 7.11; max 12.97 (GSM8K)</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>up to 9.73x; Qwen3-8B avg 6.99x (T=0; GPU not given)</t>
+          <t>Qwen3-8B T=0 avg 6.99x vs DFlash 4.43x, DDTree 5.63x, Domino 5.19x; up to 9.73x (GSM8K) (GPU/batch not extracted)</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/VILA-Lab/DARTree</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>arXiv; COLM'26 workshop (per README)</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>DFlash baseline tau 7.09 at c=1 (Qwen3-8B); AdaFlash not extracted</t>
+          <t>AdaFlash not extracted; DFlash baseline tau 7.09-7.11 at c=1-128 (Qwen3-8B)</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>up to 5.3x over AR; +66% throughput over prior SOTA at c=128 (SGLang); DFlash 0.90x at c=128</t>
+          <t>up to ~5.3x over AR; up to ~66% higher avg throughput than prior SOTA at high concurrency (SGLang); DFlash drops 4.38x (c=1) to 0.90x (c=128) on Qwen3-8B</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>MathQA, GSM8K, OpenCodeInstruct, CodeAlpaca, ShareGPT, Blend, 2 long reasoning sets</t>
+          <t>MathQA, GSM8K, OpenCodeInstruct, CodeAlpaca, ShareGPT, Blend (+2, 8 total); targets Qwen3-8B, Qwen3-Coder-30B-A3B + 1</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/ZinYY/AdaFlash</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>block fixed at 16 (accepted length capped); still needs fresh target features each round; training mismatch when combined with Domino</t>
+          <t>relay must be trained on its own rejected rollouts (teacher-forced relay training drops tau to 2.22 with Domino); block fixed at 16; still needs fresh target features each round</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>not reported; small MLP relay on DFlash</t>
+          <t>not reported; small MLP relay on DFlash (0.51 ms, 1.2% latency)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 4.15 vs DFlash 3.66 (T=0), 3.45 vs 3.10 (T=1)</t>
+          <t>Qwen3-8B 4.15 vs DFlash 3.66 (T=0), 3.45 vs 3.10 (T=1); Qwen3-4B 4.20 vs 3.71 (T=0); with Domino 4.50 vs 4.02 (Qwen3-1.7B)</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2.65x at c=1 down to 1.35x at c=32 (Qwen3-8B, SGLang, A800)</t>
+          <t>Qwen3-8B GSM8K: 3.08x vs DFlash 2.83x at c=1, 1.89x vs 1.71x at c=16, 1.35x vs 1.16x at c=32 (A800, SGLang)</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/pekpuch/dflow</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>no new params (fine-tuned DSpark checkpoint); extra drafting GPU; ~8x per-round draft activations (est.)</t>
+          <t>no new params (backbone fine-tuned from DSpark ckpt); one dedicated drafting GPU; 8 anchors per round (d=7) so ~8x draft activations (est.)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>not extracted (+30.7% tau from multi-anchor fine-tuning)</t>
+          <t>not extracted (backbone fine-tuning raises avg tau +30.7%)</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>3.21x Qwen3-8B, 3.52x 14B; +11.1%/5.1% vs DSpark (H800, bs1-16, greedy)</t>
+          <t>avg 3.21x Qwen3-8B, 3.52x Qwen3-14B, max 4.53x; +11.1%/5.1% vs DSpark (H800, bs1-16, greedy)</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>drafter state 6.3 MiB at 128K (406x smaller than DSpark); one extra drafter GPU</t>
+          <t>drafter state 6.3 MiB at 128K vs DSpark 2.5 GiB (406x smaller); one dedicated drafter GPU; params not reported</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>1.88-2.13x over AR at 1K-128K; 128K TPOT 74.3 vs 97.2 ms DSpark; +6-12% vs DSpark at c=128</t>
+          <t>avg 1.88x/1.99x/2.13x over AR (Qwen3-4B/8B/14B); 128K TPOT 74.3 vs DSpark 97.2 ms; +12.0/7.8/6.0% vs DSpark at c=128 (target TP4 + 1 drafter GPU, SGLang)</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>not reported; separate small drafter (PARD-style, size not extracted) plus its KV</t>
+          <t>not reported; separate small AR draft model (sizes not named) plus its KV</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -6460,17 +6460,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 6.98; LLaMA3.1-8B 9.19 (T=0, K=16)</t>
+          <t>Qwen3-8B avg 6.98 (DFlash 5.58); LLaMA3.1-8B avg 6.95 (T=0, K=16, target-dependent)</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 5.81x vs DFlash 4.61x, PARD 4.39x, EAGLE-3 1.93x (A100-40GB, vLLM, T=0)</t>
+          <t>Qwen3-8B avg 5.81x vs DFlash 4.61x, PARD 4.39x, EAGLE-3 1.93x (A100-40GB, vLLM, T=0); target-independent 4.82x/4.79x/4.68x on Qwen3-8B/14B/32B</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>LLaMA3.1-8B 6.94x / tau 9.19 (vLLM, T=0); notes also cite 5.19x (conflict, check table)</t>
+          <t>LLaMA3.1-8B avg 5.19x / tau 6.95 vs PARD 4.00x, EAGLE-3 2.76x; 6.94x / tau 9.19 is HumanEval only (abstract 'up to') (vLLM, A100-40GB, T=0, K=16)</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>LoRA adapter only; reuses target weights (draft pass costs a full forward)</t>
+          <t>LoRA r=16, 10.1M params (1.67% of 0.6B); reuses target weights, draft pass is a full forward (50.3 ms vs verify 50.6 ms)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>tau 2.88 (Qwen3-0.6B, T=0)</t>
+          <t>2.88 vs FastMTP 1.51 (Qwen3-0.6B, T=0, D=16)</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>34.05 tok/s vs FastMTP 188.01 tok/s (Qwen3-0.6B, bf16, T=0, 256 tokens)</t>
+          <t>34.05 tok/s vs FastMTP 188.01, greedy AR 431.36 (slower than AR) (Qwen3-0.6B, SGLang, T=0, 256 tokens)</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -6557,17 +6557,17 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>TULU-3 (training); eval set not extracted</t>
+          <t>TULU-3 50k (training); eval prompt set not named</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none found</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6614,22 +6614,22 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>separate Transformer-base-size drafter; paper reports ~245-555 MB extra at test time</t>
+          <t>Spec-Drafter (12+2 layers) weights; extra peak GPU memory ~245-288 MB (WMT14 En-De, P100, bs 1-32)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>lossy, no drop measured: BLEU 28.93 vs 28.73 AR greedy (WMT14 En-De); ROUGE +0.03 (CNN/DM, BART-base)</t>
+          <t>lossy by rule, no measured drop: BLEU 28.93 vs 28.89 AR (WMT14 En-De, Transformer-base); En-Ro 35.45 vs 34.96; CNN/DM ROUGE-1 43.11 vs 43.08 (BART-base)</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>8.23 tokens/iter (k=25) vs 2.32 for blockwise decoding</t>
+          <t>8.23 tokens/iter (k=25, WMT14 En-De, greedy)</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>5.1-5.5x (Transformer-base, P100, bs1); 3.0-3.3x (12+2 target); 5.1x (BART-base)</t>
+          <t>Transformer-base: 5.1x En-De, 5.5x De-En, 4.6x En-Ro, 4.8x Ro-En; 12+2 target: 2.5-3.3x; BART-base CNN/DM 5.1x (P100, bs1, fairseq)</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>lossy: tokens the large model would not pick are kept; fallback and rollback thresholds must be tuned; small and large models must be aligned (README advises fine-tuning the small model)</t>
+          <t>lossy: tokens the large model would not pick are kept; fallback/rollback thresholds tuned per task; best results need the small model fine-tuned on large-model outputs (alignment); rollback discards small-model work</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>not reported; small model (T5/mT5-small class) + its KV (est.)</t>
+          <t>small model (paper: 25M vs 409M/402M large, ~1/20) + its KV; ~5x fewer memory ops than vanilla</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>lossy: 'minimal' quality degradation at up to 2.12x; exact BLEU/ROUGE drop not seen</t>
+          <t>lossy: matched-quality IWSLT 40.24 vs 40.32 BLEU, WMT 31.26 vs 31.38, XSum 35.05 vs 35.08 R-L, CNN/DM 41.52 vs 41.54; max-speed setting ~1 pt drop (CNN/DM 40.96)</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>up to 2.12x (T4 GPU)</t>
+          <t>aligned, matched quality: 1.62x IWSLT, 1.47x WMT, 1.50x XSum, 1.85x CNN/DM; ~1 pt drop: up to 2.12x (T4, bs1, greedy); unaligned 1.43-1.71x</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>none (T5/mT5 encoder-decoders)</t>
+          <t>none (mT5/T5 encoder-decoders only)</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6778,32 +6778,32 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Medusa heads: ResBlock + own vocab projection each, ~0.15B per head on 7B, ~0.7B for 5 heads (est.); no extra KV</t>
+          <t>per head W1 (d x d) + W2 (d x V): ~0.15B/head on 7B, ~0.74B for 5 heads (est., not reported); no extra KV</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>lossy at T&gt;0: MT-Bench quality roughly unchanged (unv.)</t>
+          <t>lossy at T&gt;0: Fig. 5 (Medusa-2 Vicuna-7B, T=0.7, MT-Bench writing/roleplay) shows GPT-4 score similar to random sampling; exact drop not tabulated</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>not reported for typical acceptance alone</t>
+          <t>acceleration rate (Medusa-2): 3.47 Vicuna-7B, 3.51 Vicuna-13B, 3.01 Vicuna-33B, 3.14 Zephyr-7B; typical-acceptance alone only in Fig. 5</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>~2x wall-time (Vicuna-7B/13B/33B, A100, bs1, MT-Bench, Medusa-1); +10% over greedy on creative tasks with typical acceptance; Medusa-2 2.3-3.6x (unv.)</t>
+          <t>Medusa-1 2.18x (Vicuna-7B), 2.33x (13B); Medusa-2 2.83x (7B/13B), 2.35x (33B), 2.66x (Zephyr-7B) (A100, bs1, MT-Bench); typical acceptance: higher accel. than RS at T=0.7</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B/13B/33B ~2x (Medusa-1); Medusa-2 2.3-3.6x (unv.)</t>
+          <t>Vicuna-7B 2.18x/2.83x, Vicuna-13B 2.33x/2.83x (Medusa-1/-2), Vicuna-33B 2.35x (Medusa-2); MT-Bench score change -0.14 to +0.05</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench</t>
+          <t>MT-Bench, AlpacaEval; training on ShareGPT/UltraChat</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6860,42 +6860,42 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>none beyond the drafter (est.); per-step sort over the vocabulary</t>
+          <t>none beyond the drafter (est.); O(n) data structure, O(sort(n)) build per step (n = vocab or top-k)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>lossy with bounded per-token divergence; measured drop not reported in material seen</t>
+          <t>lossy with bounded per-token f-divergence; theory paper, no measured drop (toy simulation only); claims proxy can beat target</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>not reported (theory paper)</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>not reported (full text not read)</t>
+          <t>not reported (theory paper, no benchmarks)</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>none seen</t>
+          <t>none (no experiments)</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>none (toy simulation only)</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/vivien000/mentored_decoding</t>
+          <t>none found in paper</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>lossy: no guarantee of target distribution; judge needs hand-labeled error annotations and new domains need new labels (OOD drop); needs a strong drafter (Medusa/EAGLE heads unsuitable) and a large target</t>
+          <t>lossy: no guarantee of target distribution; judge trained on ~500 hand-annotated examples and OOD domains drop; needs a long-drafting drafter (Medusa/EAGLE-2 draft &lt;=6 tokens) and a large target</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>judge head 16,384 params (405B) / 8,192 (70B), negligible; plus separate Llama-3.1-8B drafter + its KV</t>
+          <t>judge head ~16.4k params (linear on target last-layer embeddings), negligible; plus separate Llama-3.1-8B drafter + its KV</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>lossy: GSM8K ~90% and HumanEval 86.6% ~ target 405B; OOD (code removed from judge data) HumanEval 86.6% -&gt; 80.4%</t>
+          <t>lossy: target accuracy 'almost exactly preserved' (GSM8K ~91%, HumanEval 86.6% on 405B, figure); OOD (no code in judge data) HumanEval 86.6% -&gt; 80.4%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>8B/405B: 9.7x HF, 3.9x gpt-fast, 129.3 tok/s; 8B/70B: 2x HF, 3x gpt-fast, 141.8 tok/s (H100, 8-bit, bs1)</t>
+          <t>8B/405B: 9.7x HF, 3.9x gpt-fast, 129.3 tok/s (8xH100); 8B/70B: 2x HF, 3x gpt-fast, 141.8 tok/s (2xH100); gpt-fast 8-bit, bs1</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>lossy: target distribution not preserved; labels need verifiable tasks (final-answer change) and classifier degrades OOD, so mining is redone per domain; offline mining needs many sequential target passes</t>
+          <t>lossy: target distribution not preserved; labels need verifiable tasks and classifier is task-specific (GSM8K&lt;-&gt;LCB transfer much worse); mining needs many sequential target passes (~706 s/sample for 8B/70B)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -7024,27 +7024,27 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>logistic regression on concatenated hidden states (~6k params, est.) + Llama-3.2-1B drafter + KV</t>
+          <t>logistic regression on concat draft+target hidden states (6144-d for 1B/8B, ~6k params, est.) + Llama drafter + KV</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>lossy: ≤1% accuracy drop on GSM8K at ~1.5x more accepted tokens; ~1% drop on LiveCodeBench at ~2x</t>
+          <t>lossy: GSM8K 8B/70B 92.0 -&gt; 89.9% at 1.49x, 91.9% at 1.11x; 1B/8B 83.1 -&gt; 80.2% at 1.14x; LiveCodeBench ~2% Pass@1 drop at &gt;22 tokens/cycle</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>15+ (GSM8K), 20+ (LiveCodeBench) per cycle, window W=64 (Llama 1B/8B, greedy on GSM8K)</t>
+          <t>&gt;40 tokens/forward (8B/70B, GSM8K), &gt;22 (8B/70B, LiveCodeBench); 1B/8B ~1.5x more than SD at &lt;=1% drop (greedy)</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>~2x over standard SD (GSM8K/LiveCodeBench); hardware and batch not specified</t>
+          <t>vs SD in vLLM (A100-80GB, bs1, bf16): 8B/70B GSM8K 72.3 -&gt; 107.4 tok/s (1.49x); 1B/8B 147.7 -&gt; 169.2 tok/s (1.14x)</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.2-1B -&gt; Llama-3.1-8B: up to 1.5x more accepted tokens at ≤1% GSM8K drop</t>
+          <t>Llama-3.1-8B -&gt; 70B: 1.49x over SD at -2.1 pts GSM8K; Llama-3.2-1B -&gt; 3.1-8B: 1.14x at -2.9 pts</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>lossy: target distribution not preserved; label threshold τ calibrated on annotated math examples; label creation needs pre-generated target responses and extra scoring passes</t>
+          <t>lossy: target distribution not preserved; label threshold calibrated on GSM8K (AutoJudge labels); labeling needs target responses plus suffix rescoring passes (N=20 tokens) per mismatch</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -7106,27 +7106,27 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>logistic regression on target hidden states (~4k params, est.) + 1B/0.5B drafter + KV</t>
+          <t>logistic regression on target hidden states (~4k params for 8B, est.) + 1B/8B/0.5B drafter + KV; judge 0.26% of verify time</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>lossy: -1.0% average task accuracy (vs -2.7% for AutoJudge)</t>
+          <t>lossy (Llama 8B/1B, T=0): GSM8K 80.5 vs 80.7 SD, MMLU 62.7 vs 65.0, MATH-500 42.2 vs 45.4, CNN/DM 63.9 vs 64.6, LCB 10.0 vs 8.6</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>+2.06 accepted tokens/cycle over standard SD (vs +1.96 AutoJudge)</t>
+          <t>Llama 8B/1B: GSM8K 11.29 vs 9.14 SD, MMLU 6.38 vs 4.36, CNN/DM 6.05 vs 4.35, MATH-500 12.78 vs 9.98</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>not reported as wall-clock in material seen (V100, T=0)</t>
+          <t>A100, T=0: 8B/1B GSM8K 137.4 vs 111.2 tok/s SD (+23.5%), MMLU 89.5 vs 61.1 (+46.3%); 70B/8B (4xA100) +22.4% GSM8K, +22.7% MMLU</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.2-1B -&gt; Llama-3.1-8B (included in averages above)</t>
+          <t>Llama-3.1-8B/3.2-1B and Llama-3.1-70B/8B: +22-46% tok/s over SD (above)</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7188,22 +7188,22 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>none beyond the drafter (Llama-3.1-8B + KV for 70B target)</t>
+          <t>none beyond the drafter (Llama-3.1-8B, Gemma2-2B or Qwen2.5-7B + KV)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>lossy: ~2% absolute accuracy drop at &gt;5 tok/s over SD (GSM8K, CSQA); ~0% on HumanEval</t>
+          <t>lossy: Llama 8B/70B GSM8K 93.1 vs 95.1% SD at 22.0 tok/s; CSQA 82.1 vs 84.1; HumanEval 77.4 = SD; low threshold matches SD accuracy</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>CSQA 1.96 -&gt; 3.32 at SD-matched accuracy (Llama 8B/70B)</t>
+          <t>Llama 8B/70B: GSM8K 9.7 SD -&gt; 11.8-13.5; CSQA 1.96 -&gt; 3.32-8.14; HumanEval 7.6 -&gt; 8.5-8.9</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Llama 8B/70B, 2xA100, bs1: GSM8K 16.8 (SD) -&gt; 19.5 (matched acc.) / 22.0 tok/s; HumanEval 20.5 -&gt; 22.3 / 23.6</t>
+          <t>Llama 8B/70B, 2xA100, bs1: GSM8K 16.8 SD -&gt; 19.5-22.0 tok/s (AR 8.5); HumanEval 20.5 -&gt; 22.3-23.6; CSQA 13.5 -&gt; 14.4-19.5; Gemma2/Qwen2.5 on 2xA6000</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>GSM8K, CSQA, HumanEval</t>
+          <t>GSM8K, CSQA, HumanEval, MMLU; pairs Llama-3.1 8B/70B, Gemma2 2B/27B, Qwen2.5 7B/32B</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>AISTATS 2026 or NeurIPS 2025 (conflict)</t>
+          <t>AISTATS 2026 (earlier NeurIPS 2025 Efficient Reasoning workshop)</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -7270,32 +7270,32 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>small FFN weight network (size not reported) + Llama-3.2-1B drafter + KV</t>
+          <t>weight net: 1 FC layer + sigmoid on concat draft+target hidden states (params not reported, small vs drafter, est.) + 1B drafter + KV</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>lossy: 'comparable quality' (ROUGE, accuracy, perplexity); exact drop not seen</t>
+          <t>lossy, no drop seen (Llama 8B/1B, T=1): GSM8K 67% = AR; MBPP 53% = AR; CNN/DM R-2 12.11 vs 9.86 AR; XSum R-2 7.23 vs 7.03</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>not reported in material seen (figures only)</t>
+          <t>acceptance rate (N=5, T=1), Llama 8B/1B: GSM8K 72.6% vs 44.6% SD, CNN/DM 70.0 vs 21.6, XSum 70.5 vs 20.4, MBPP 85.0 vs 26.3</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>not reported in material seen (T=0, 128 tokens on CNN/DM)</t>
+          <t>wall-clock only as normalized time in figures (8xA100-40GB); no speedup numbers tabulated</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.2-1B -&gt; Llama-3.1-8B (main pair); numbers not seen</t>
+          <t>Llama-3.1-8B/3.2-1B: acceptance 70-85% vs 20-45% SD at AR-level quality (T=1, N=5)</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>GSM8K, CNN/DM, XSum, MBPP</t>
+          <t>GSM8K, CNN/DM, XSum, MBPP; pairs Llama-3.1-8B/3.2-1B, Qwen3-8B/0.6B, Gemma-3-12B/4B</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7357,22 +7357,22 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>lossy: &gt;99% accuracy retention (GSM8K, HumanEval, MBPP)</t>
+          <t>lossy: &gt;99% accuracy recovery; e.g. GSM8K 94.69 vs 95.45% (Llama-3.1-70B)</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>~11-12 (70B), ~15-18 (405B) vs 1-4 standard SD</t>
+          <t>tau 12.67 in-dist / 11.35 OOD (70B, T=0); 17.14 / 17.13 (405B) vs ~2-3 standard SD</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>70B: in-dist 2.88x T=0 / 2.59x T=1, OOD 2.53x / 2.56x; 405B: 4.80x / 5.21x (MI355X, bs1); README avg 2.81x / 5.07x</t>
+          <t>T=0: 70B 2.88x in-dist / 2.53x OOD; 405B 5.34x / 4.80x; T=1: 70B 2.59x / 2.56x, 405B 5.31x / 5.21x (MI355X, 1 GPU 70B, 4 GPUs 405B, bs1)</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B 2.5-2.9x; Llama-3.1-405B 4.8-5.2x; OOD 1.62x over EAGLE-3 (Llama-3.3-70B)</t>
+          <t>Llama-3.1-70B 2.5-2.9x, tau ~11-13; Llama-3.1-405B 4.8-5.3x, tau ~17; OOD 1.62x over EAGLE-3</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,11 @@
           <t>single harness and taxonomy for lossy rules; names failure modes</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>EAGLE-3 draft head + its KV (est.); lossy rules themselves add no memory</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
           <t>truncation (SpecCascade) gap to true truncation sampling grows with difficulty: 0.38 pp (GSM8K) to 6.67 pp (AIME)</t>
@@ -7440,17 +7444,17 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>reported as block efficiency; numbers not seen</t>
+          <t>block efficiency in App. C; numbers not extracted</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>reported as decoding speed; numbers not seen</t>
+          <t>tokens/s in App. C; numbers not extracted (A100, bs1, T=0 per App. G)</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Llama-based models (versions not seen)</t>
+          <t>EAGLE-3 on Llama-3.1-8B-Instruct (plus Qwen) per App. G; numbers not extracted</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -7512,27 +7516,27 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>small model + its KV (T5-small 77M; Gemma 2B/9B for 27B)</t>
+          <t>small model + its KV (T5-small 77M for T5-large 800M / T5-XL 3B; Gemma 2B drafter for 9B/27B)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>lossy by design: matches large-model quality at 1.85x (WMT), 1.89x (CNN/DM), 1.18x (XSum); can exceed it</t>
+          <t>lossy by design: matches large-model quality at the speedups below; can exceed it</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>not reported in material seen</t>
+          <t>not reported (rejection rates only)</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>1.85x WMT, 1.89x CNN/DM, 1.18x XSum latency reduction at large-model quality (T5, T=1, γ=5, bs1)</t>
+          <t>at large-model quality, SpecCascade [Token]: small-&gt;large 1.85x WMT, 1.89x CNN/DM, 1.18x XSum; small-&gt;XL 2.50x, 1.89x, 1.40x (T5, T=1, gamma=5, bs1)</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>none (T5, Gemma)</t>
+          <t>none (T5, Gemma 2B/9B/27B)</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -7547,7 +7551,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7603,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>lossy (gain): +1.1 avg accuracy vs target over 6 benchmarks; GPQA-Diamond 38.4 vs 32.8</t>
+          <t>lossy (gain): Qwen2.5-Math 1.5B/7B: avg 66.1 vs 65.3 target (6 tasks); GPQA up to 38.4 vs 32.8; 7B/72B: MATH500 88.0 vs 85.6</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -7609,17 +7613,17 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>up to 4.4x fewer FLOPs vs target-only; wall-clock not reported (A100, vLLM)</t>
+          <t>up to 4.4x fewer FLOPs vs target-only (7B/72B, MATH500); wall-clock not reported (A100, vLLM, T=0.7)</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-8B target with ~1B Llama draft tested; numbers not seen</t>
+          <t>Llama-3.2-1B/3.1-8B, PRM 7B: avg 41.9 vs 41.4 target, 41.1 SD (MATH500 50.4 vs 49.4, GSM8K 85.4 vs 83.9)</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>MATH500, GSM8K, GPQA-Diamond, Olympiad-level math</t>
+          <t>MATH500, GSM8K, GaoKao-2023-En, OlympiadBench, GPQA-Diamond, MMLU-STEM</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -7629,7 +7633,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7685,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>lossy (gain, v1): +1.0 MATH500, +3.1 AIME, +9.9 GPQA vs QwQ-32B</t>
+          <t>lossy (gain): QwQ-32B +1.3-3.6 AIME, +4.0-9.0 MATH500, +0.4-1.7 GPQA; Skywork-OR1-32B +1.4-5.0 (pass@1, k=16)</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7691,12 +7695,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>v1: 2.5x MATH500, 1.9x AIME, 1.5x GPQA (QwQ-32B, 2xA6000, vLLM 0.8.2, T=0.6); +19.4-44.2% latency cut over SD alone</t>
+          <t>QwQ-32B: 2.5x MATH500, 1.5x AIME, 1.4x GPQA; Skywork-OR1-32B: 3.0x, 1.6x, 1.7x (2xA6000, vLLM 0.8.2, T=0.6); +SD: 19.4-58.0% lower latency than SD alone</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>R1-Distill-Llama-70B as base (§5.4); numbers not seen</t>
+          <t>R1-Distill-Llama-70B as base (App. A.1); numbers not extracted</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7748,7 +7752,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>lossy vs large model: output mostly small-model text; cue words are model-family heuristics; both models must share a family/tokenizer</t>
+          <t>lossy vs large model: output mostly small-model text; cue words are hand-picked heuristics; each switch hands text across, so the other model must prefill the new tokens (est.)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7763,22 +7767,22 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>lossy vs 32B (accuracy vs 32B alone not seen); small model gains: MATH500 83.2 -&gt; 89.4, GPQA 33.8 -&gt; 41.9</t>
+          <t>lossy vs 32B alone: MATH500 89.4 vs 93.8, GPQA 41.9 vs 61.6, AIME 32.2 vs 60.0, AMC23 80.0 vs 95.0 (1.5B+32B); vs 1.5B alone +5 to +8 pts</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>not applicable</t>
+          <t>not applicable (~18-21% of output tokens from the large model)</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>est. 96.6 vs 32.2 tok/s for 32B alone (FLOP-based estimate, A100-class, not measured)</t>
+          <t>FLOP-based estimate, not measured: 96.6 vs 32.2 tok/s for 32B alone (MATH500, A100-class)</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>LLaMA3-8B small + Qwen-32B large: +3.4% accuracy, +44.4% est. speed vs small alone</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7793,7 +7797,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7834,7 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>lossy: output is a draft CoT, not the target's; LoRA tuning of both models (math only); 'all wrong' detected only 52% of the time, wasted drafts when rejected</t>
+          <t>lossy: output is a draft CoT, not the target's; LoRA tuning of both models on GSM8K data; 'all drafts wrong' detected only 52% of the time, and rejected rounds waste 5 drafts</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7845,7 +7849,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>lossy: 'near-target' accuracy, exact drop not seen; CollegeMath above target</t>
+          <t>lossy: Qwen-32B -0.4 to -1.0 pts (CollegeMath +0.4); Llama-70B -1.4 to -2.4 pts (GSM8K 86.8 vs 88.2, MATH 90.4 vs 92.0)</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7855,12 +7859,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>2.26-2.92x (R1-Distill-Qwen-32B, A100-40GB); 1.26-1.96x (R1-Distill-Llama-70B, H800)</t>
+          <t>R1-Distill-Qwen 1.5B/32B: 1.90-2.92x (A100-40GB); R1-Distill-Llama 8B/70B: 1.26-1.96x (H800)</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>R1-Distill-Llama-8B -&gt; R1-Distill-Llama-70B: 1.26-1.96x</t>
+          <t>R1-Distill-Llama-8B -&gt; 70B: 1.26-1.96x at -1.4 to -2.4 pts</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7875,7 +7879,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -7932,12 +7936,12 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>step acceptance 0.35-0.63</t>
+          <t>step acceptance 0.35-0.63 (R1-Distill), 0.30-0.53 (Qwen3)</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>LR+SD 1.49-2.11x, LR alone 1.04-1.71x, n-gram SD 1.32-1.53x (32B targets, 8xH100, vLLM 0.8.3, T=0.6)</t>
+          <t>LR+SD 1.51-2.11x (R1-Distill-32B), 1.32-1.68x (Qwen3-32B); LR alone 1.04-1.71x; SD alone 1.25-1.53x (8xH100, vLLM 0.8.3, T=0.6)</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -7957,7 +7961,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8013,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>lossy (gain): +3.6% accuracy vs standard SD (target-only MATH500 83.0)</t>
+          <t>lossy (gain): Qwen2.5-Math 7B/1.5B MATH500 85.4 vs 83.0 target, GSM8K 95.8 vs 94.7; 'accuracy +3.6%' vs SD/RSD</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -8019,17 +8023,17 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>~11% lower latency vs standard SD (hardware not seen)</t>
+          <t>~11% lower latency vs RSD (A100, vLLM); per-method latency only in figure</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Llama-3 8B/1B: MATH500 51.6 vs 48.2 target, GSM8K 85.1 vs 83.9, Olympiad 17.2 vs 14.5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>MATH500, GSM8K, GaoKao-2023-En, OlympiadBench</t>
+          <t>MATH500, GSM8K, GaoKao-2023-En, OlympiadBench; Qwen2.5-Math, Qwen2.5, Llama-3 pairs</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -8039,7 +8043,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8090,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>not reported; K=8 draft sequences x L=8 tokens of draft KV plus 64 verify positions (est.)</t>
+          <t>not reported; K=8 draft sequences x L=8 tokens of draft KV plus up to 64 verify positions in the target pass (est.)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -8096,12 +8100,12 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>block efficiency 4.0 vs 2.9 for SD (PaLM-2 Gecko/Bison, K=8, L=8, T=1)</t>
+          <t>block efficiency 4.0 vs 2.9 SD (K=8 vs 1, L=8) and 3.1 vs 2.4 (L=4) (PaLM-2 Gecko-&gt;Bison, LM1B, T=1); 3.27 vs 2.33 (6M/97M LM1B models)</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>2.13x vs AR, 1.37x vs SD (PaLM-2 Gecko-&gt;Bison, K=8, L=8, T=1; hardware not stated)</t>
+          <t>2.13x vs AR, 1.37x vs SD (K=8, L=8); 2.08x vs 1.67x SD at L=4 (PaLM-2 Gecko-&gt;Bison, T=1); hardware not stated</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -8111,7 +8115,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>LM1B (plus small FLAX LM1B ablations)</t>
+          <t>LM1B (1000 prompts, 3 seeds; plus 6M/97M LM1B transformers)</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -8121,7 +8125,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8178,17 +8182,17 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>acceptance rate 90.7% greedy draft vs 89.9% optimal w/o replacement (OPT-125M/6.7B, Alpaca, T=0.7); existing verifiers 0.1-3.3 pts below optimum</t>
+          <t>single-step acceptance, Alpaca, T=0.7, w/o replacement: optimal 89.9% vs RRS 88.9%, greedy 90.7% (OPT-125M/6.7B); 76.5/75.7/78.4% (LLaMA-68M/7B); 71.5/70.9/72.6% (EAGLE/Vicuna-7B)</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>1.17x (multi-step MT-Bench, T=0.1, 4 drafts x 3 steps; baseline per paper table, check); RTX A6000</t>
+          <t>multi-step MT-Bench Vicuna-7B+EAGLE, T=0.1: greedy draft 1.17x (4 drafts x 3 steps), 1.13x vs RRS 1.04x (2 x 4); RTX A6000; reference baseline of the x not stated in extract</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-68M/LLaMA-7B and Eagle-0.24B/Vicuna-7B pairs used; per-model numbers not extracted</t>
+          <t>LLaMA-68M/LLaMA-7B: optimal 73.0% w/ repl. (K-SEQ 71.9%, RRS 71.6%), 76.5% w/o repl.; EAGLE-0.24B/Vicuna-7B: 64.4% / 71.5%; Vicuna-7B multi-step up to 1.17x</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -8203,7 +8207,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8244,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>token-level selection only, no tree-wide joint acceptance; each draft needs its own draft pass/model; gain only at T&gt;0</t>
+          <t>token-level selection only, no tree-wide joint acceptance; practical scheme needs a truncated LP (s=5) and truncated alphabet (40 tokens), so it only approximates the optimum; gain only at T&gt;0</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -8250,7 +8254,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>not reported; one extra draft sequence (and KV) per draft (est.)</t>
+          <t>not reported; K=2 draft sequences of 5 tokens (+ draft KV) from OPT-125M (est.)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -8260,22 +8264,22 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>not read (abstract: improved block efficiency over baselines)</t>
+          <t>not reported numerically (block efficiency in Fig. 3 plots only; OPT-125M-&gt;OPT-13B, K=2, 5 tokens/call, target T=1, top-p 0.95)</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>not read (abstract: improved token rates over baselines)</t>
+          <t>token-rate % gain over SpecInfer and single-draft SD shown in plots only; 1x A100-80GB</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>not read</t>
+          <t>none (OPT-125M/OPT-13B only)</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>not read</t>
+          <t>XSum, Databricks-Dolly-15k, WMT18</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -8285,7 +8289,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8326,7 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>solver costs up to ~100 ms/token, far above a 20-50 ms decode step; optimal only for i.i.d. drafts; truncation set can be too large, forcing early termination (small deviation from target)</t>
+          <t>solver runs per token (5-47 ms/token on Llama-3), comparable to a decode step; success rate falls to 15% at k=1000, n=2, forcing early termination/fallback; optimal only for i.i.d. drafts</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -8337,27 +8341,27 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>lossless in exact solve; truncated solve gives 'negligible deviation' from target</t>
+          <t>lossless in exact solve; early-terminated solve deviates at most 15*tau in L1 from target (tau=1e-3 setting)</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>~90% per-token acceptance (Llama-3 70B/8B, Gemma-2 27B/2B, n&lt;=10, T=1); +1.03%/+0.47% acceptance vs other solvers at 100 ms budget</t>
+          <t>Llama-3 70B/8B: 90.04% vs 89.01% max-flow at 100 ms/token, 85.65% vs 83.94% at 10 ms; Gemma-2 27B/2B: 86.60% vs 85.83%; T not extracted</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>nearly 2x wall time in multi-step SpecTr setting; per-token overhead &lt;100 ms; hardware not extracted</t>
+          <t>solver 5.27-47.46 ms/token (Llama-3); ~2x wall-clock vs SpecTr baseline in multi-step setting (App. R); hardware in App. M not extracted</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Llama-3-70B target / Llama-3-8B draft: ~90% acceptance, +1.03% over other solvers under 100 ms/token</t>
+          <t>Llama-3-70B target / Llama-3-8B draft: 90.04% acceptance vs 89.01% max-flow solver (100 ms/token budget)</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>40 random prompts per dataset (dataset names not extracted)</t>
+          <t>40 random prompts per dataset (names in App. M, not extracted)</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -8424,12 +8428,12 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>+8.30% block efficiency avg (7.00-10.06%) vs token-wise (PaLM-2-S + XXS, gamma=8, sampling)</t>
+          <t>+8.30% block efficiency avg (7.00-10.06% across 8 datasets) vs token-wise (PaLM-2-S + PaLM-2-XXS, gamma=8, sampling)</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>+6.49% wall-clock avg (5.36-8.14%) vs token-wise SD (PaLM-2-S, gamma=8); hardware not stated</t>
+          <t>+6.49% wall-clock avg (5.36-8.14%) vs token-wise SD (PaLM-2-S + XXS, gamma=8, T&gt;0); hardware not stated</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -8449,7 +8453,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8506,22 +8510,22 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>not reported numerically in extract (figures only)</t>
+          <t>not reported numerically (block efficiency in Figs. 4-5 only)</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>RSD-S beats SD and SpecTr on block efficiency and token rate in most budgets (A100); exact values in figures</t>
+          <t>RSD-S beats SD and SpecTr on block efficiency, MBSU and token rate at fixed draft length (A100; values in figures only)</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Llama 2 / Llama 2-Chat 7B,13B,70B targets: RSD-S strictly outperforms SD and SpecTr at fixed draft length (values in figures)</t>
+          <t>Llama 2 / Llama 2-Chat 7B, 13B, 70B targets (also OPT 13B/30B/66B): RSD-S strictly outperforms SD and SpecTr at fixed draft length (figures only)</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>WMT18 De-En, XSum, Databricks-Dolly-15k</t>
+          <t>WMT18 De-En (T=0.3), XSum (T=0.3), Databricks-Dolly-15k (T=1, top-p 0.95)</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
@@ -8531,7 +8535,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8572,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>bottom-up traversal over the whole tree adds overhead that eats part of the gain; gain shrinks as T falls and is zero at T=0</t>
+          <t>bottom-up traversal over the whole tree adds overhead that eats part of the gain; gain shrinks as T falls (1.0% at T=0.2 vs 2.8% at T=1) and is zero at T=0</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -8588,17 +8592,17 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>tau 4.09 vs 3.95 token-level (Llama3.1-8B / 3.2-1B, chain d5, MT, T=1); 2.59 vs 2.47 (Llama2-7B / 68M, binary tree, T=1)</t>
+          <t>tau 4.09 vs 3.95 token-level (Llama3.1-8B / 3.2-1B, chain d5); 4.76 vs 4.64 binary tree; 4.67 vs 4.53 EAGLE sparse tree; 2.59 vs 2.47 (Llama2-7B / 68M, binary d5)</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>58.5 tok/s sparse tree vs 34.5 AR (~1.7x) on Llama3.1-8B; +1.7-2.5% tok/s vs token-level (RTX A6000, bs1, T=1, PyTorch)</t>
+          <t>58.5 tok/s EAGLE sparse tree vs 57.3 token-level vs 34.5 AR (~1.7x) on Llama3.1-8B; +1.7-2.5% tok/s vs token-level; RTX A6000, bs1</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>Llama3.1-8B: tau 4.09, 52.5-58.5 tok/s vs 34.5 AR; Llama2-7B: 72.5 tok/s vs 37.3 AR</t>
+          <t>Llama3.1-8B: tau 4.09-4.76, 52.5-58.5 tok/s vs 34.5 AR; Llama2-7B/68M: tau 2.16 chain, 2.59 binary (+4.7-5.5%), AR 37.3 tok/s</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -8613,7 +8617,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8670,32 +8674,32 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>tau 3.29 vs 3.06 RRSw (Vicuna-7B + EAGLE, binary d5, T=1); 2.95 vs 2.72 (Llama3.1-8B, T=1)</t>
+          <t>tau 3.29 vs 3.06 RRSw, 3.13 traversal (Vicuna-7B + EAGLE, binary 2x5, T=1); 2.95 vs 2.72 (Llama3.1-8B, T=1); equal to traversal at T=0.3</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>72.2 tok/s vs 35.9 AR (~2.0x), ~7% over RRSw (Vicuna-7B, RTX A6000, bs1, T=1)</t>
+          <t>72.2 tok/s vs 67.5 RRSw vs 35.9 AR (~2.0x) (Vicuna-7B + EAGLE, RTX A6000 48G, bs1, T=1)</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B tau 3.29 (+7.5%); Llama3.1-8B tau 2.95 (+8.5%); also Vicuna-13B/33B, Llama2-7B+68M</t>
+          <t>Vicuna-7B tau 3.29 (+7.5%); Vicuna-13B 3.35, 45.3 tok/s (AR 22.3); Vicuna-33B 3.21, 21.4 tok/s (AR 9.2); Llama3.1-8B 2.95, 51.1 tok/s (AR 34.5); Llama2-7B+68M 2.65, 62.5 tok/s</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Spec-Bench (MT-Bench, WMT14 De-En, CNN/DM, Natural Questions, GSM8K, DPR)</t>
+          <t>Spec-Bench (6 domains, 80 samples each)</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>none found</t>
+          <t>none found (built on EAGLE repo)</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8726,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR 2026</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -8732,7 +8736,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>no gain at T=0; with EAGLE-3 top-K drafting draft probs are near one-hot, so the joint-probability gain is muddied (authors flag stochasticity/precision); needs full draft+target probs for all gamma positions</t>
+          <t>no gain at T=0; needs full draft and target probability vectors for all gamma positions; gain shrinks for the largest target (+3.3% BE on Qwen2.5-72B GSM8K)</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8742,7 +8746,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>none beyond drafter; verify &lt;1% of decode time; stores gamma x V probs (est.)</t>
+          <t>none beyond drafter; stores gamma x V probabilities (est.); verify &lt;1% of decode time (stated)</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -8752,17 +8756,17 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>BE 6.30 / 6.47 / 6.65 vs 5.99 / 6.14 / 6.44 token-wise (Qwen2.5-0.5B -&gt; 14B/32B/72B, GSM8K, gamma=10, T=1)</t>
+          <t>BE 6.30 / 6.47 / 6.65 vs 5.99 / 6.14 / 6.44 token-wise (Qwen2.5-0.5B -&gt; 14B/32B/72B, GSM8K, gamma=10, T=1); HumanEval 5.29-5.49; CNN/DM 2.45-2.59</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>+6.7% avg speed vs token-wise; 91.05 tok/s (+10.7%) Qwen2.5-14B GSM8K (1x H20, T=1); EAGLE-3 80.49 vs 71.59 tok/s</t>
+          <t>+6.7% avg speed vs token-wise; 91.05 vs 82.28 tok/s Qwen2.5-14B GSM8K (1x H20, T=1); EAGLE-3 integration 80.49 vs 71.59 tok/s (+12.4%)</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B/8B: +8.8% BE, +9.2% speed (8x H20); EAGLE-3 Llama3.1-8B: &gt;12% speed</t>
+          <t>Llama-3.1-70B/8B: BE 7.43 vs 6.83 (+8.8%), 9.18 vs 8.41 tok/s (+9.2%) (H20)</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -8777,7 +8781,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8813,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Generic tree construction principle (title only)</t>
+          <t>Generic tree construction principle aimed at maximizing speedup (title only; OpenReview page blocked by bot check)</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -8906,7 +8910,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>SSMs LLaMA-68M / OPT-125M (+ their KV) and target KV for tree nodes</t>
+          <t>SSMs LLaMA-68M / OPT-125M add &lt;1% memory; token-tree overhead negligible vs KV cache (stated)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -8916,32 +8920,32 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2.18-3.91 tokens/step greedy, 1.64-2.38 stochastic (tree width 1-5)</t>
+          <t>verified tokens/step greedy 2.18-2.95 (width 1) to 3.07-3.69 (width 5); stochastic 2.21-2.38 (width 5) (LLaMA-7B + LLaMA-68M, range over datasets)</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>1.5-2.5x single-node, 2.4-2.8x multi-node vs incremental; 2.6-3.5x offloading vs FlexGen (A10 24GB, bs 1-16)</t>
+          <t>1.5-2.5x single-node (LLaMA-7B 1 GPU, OPT-30B 4 GPUs), 2.4-2.8x multi-node (LLaMA-65B, 2 nodes) vs vLLM/HF TGI/FasterTransformer; 2.6-3.5x offloading vs FlexGen (OPT-13B/30B); A10 24GB, bs1-16</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-7B and LLaMA-65B targets with LLaMA-68M SSM (within the 1.5-2.8x distributed range)</t>
+          <t>LLaMA-7B + LLaMA-68M: 1.5-2.5x single GPU; LLaMA-65B multi-node: 2.4-2.8x</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Instruction Prompts, ChatGPT Prompts, WebQA, Alpaca, PIQA</t>
+          <t>Alpaca, ChatGPT Prompts, WebQA, Chatbot Instruction Prompts (CIP), PIQA</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/flexflow/flexflow-serve</t>
+          <t>https://github.com/flexflow/FlexFlow (paper link; now flexflow-serve)</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8992,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>68M drafter + KV; up to 128-node (768 offloaded) verify tree per step</t>
+          <t>JF68M drafter + KV, 128-node verify tree (A100); offload: Llama2-7B/Llama3-8B drafter + 768-node tree</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -8998,17 +9002,17 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>5.08 tokens/step (Llama2-7B + 68M, C4, T=0); 3.92 at T=0.6; 11.68 (Llama3-70B offload, T=0)</t>
+          <t>5.08 tokens/step (Llama2-7B + JF68M, C4, T=0, tree 128); 3.92 at T=0.6; 4.98 MT-Bench T=0; offload 10.30 (Llama2-70B/7B), 11.68 (Llama3-70B/8B, T=0)</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>4.04x (Llama2-7B, A100, bs1, T=0); 3.73x Llama2-13B; 9.5x Llama3-70B offloaded on L40 (0.60 s/token)</t>
+          <t>4.04x (Llama2-7B, A100, bs1, T=0, C4) vs SpecInfer 3.45x; up to 3.73x Llama2-13B, 2.27x Vicuna-33B; offload on L40: 9.5x Llama3-70B (0.60 s/token), 8.6x Llama2-70B (0.66 s/token)</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>Llama2-7B 4.04x (T=0), 3.18x (T=0.6); Llama2-13B 3.73x; Vicuna-33B; Llama3-70B offload 9.5x</t>
+          <t>Llama2-7B 4.04x (T=0), 3.18x (T=0.6); Llama2-13B up to 3.73x; Vicuna-33B 2.27x; offload Llama2-70B 8.6x, Llama3-70B 9.5x</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -9023,7 +9027,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9064,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>deeper trees mean more sequential drafter passes; draft probability is used as acceptance proxy, which weakens under sampling; per-step tree rebuild gives dynamic shapes</t>
+          <t>deeper trees mean more sequential drafter passes, so a strong large drafter can raise MAL yet give ~1x (Llama-2-7B + 1B draft: MAL 4.88, 1.01x); draft probability as acceptance proxy weakens under sampling; per-step tree rebuild gives dynamic shapes</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -9070,7 +9074,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>drafter (68M-7B, or EAGLE head) + its KV; 25-60 node verify tree</t>
+          <t>drafter (68M, 1B, 7B or EAGLE head) + its KV; 25-60 node verify tree</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -9080,22 +9084,22 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>MAL 4.06 (Llama-2-70B + EAGLE, MT-Bench, T=0); 7.74 with Llama-2-7B draft; 4.55 GSM8K</t>
+          <t>MAL 4.06 (Llama-2-70B + EAGLE, MT-Bench, T=0); 7.74 with Llama-2-7B draft (50 nodes); ~10 with 500 nodes; 4.09 at T=1</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>3.21x (Llama-2-70B + EAGLE, GSM8K, 4x A100-40GB, T=0); 3.01x at T=1</t>
+          <t>3.05x (Llama-2-70B + EAGLE, MT-Bench, 4x A100-PCIE-40GB, T=0), ~3.2x GSM8K; 3.01x at T=1; Llama-2-7B + EAGLE 2.56x (RTX 4090)</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>Llama-2-7B/13B/70B and Vicuna-33B; best 3.21x Llama-2-70B + EAGLE</t>
+          <t>Llama-2-7B: 1.69x (68M), 2.56x (EAGLE); Llama-2-13B 1.80x (68M, L20); Llama-2-70B 1.85x (7B draft), 3.05x (EAGLE); Vicuna-33B 2.24x (EAGLE)</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench, GSM8K (C4 for Sequoia trees)</t>
+          <t>MT-Bench, GSM8K</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
@@ -9105,7 +9109,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9156,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>EAGLE head ~0.24B for Vicuna-7B (per Hu et al.) + its KV; ~1 decoder layer for larger targets (est.)</t>
+          <t>EAGLE head ~0.24B for Vicuna-7B (per Hu et al.) + its KV; draft tree 60 tokens (7B/8B), 50 (13B), 48 (70B) verified per step</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -9162,17 +9166,17 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>tau 4.98 (Vicuna-7B, MT-bench, T=0); 4.83 Vicuna-13B; 4.28 Vicuna-7B at T=1</t>
+          <t>tau 4.98 (Vicuna-7B, MT-bench, T=0); 4.83 Vicuna-13B; 4.28 Vicuna-7B at T=1; up to 5.52 (LLaMA2-Chat-13B, HumanEval, T=0)</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>3.62x Vicuna-7B, 4.26x Vicuna-13B (MT-bench, T=0, bs1); 3.05x Vicuna-7B at T=1</t>
+          <t>3.62x Vicuna-7B, 4.26x Vicuna-13B (MT-bench, T=0); 3.05x Vicuna-7B at T=1; up to 5.00x LLaMA2-Chat-13B HumanEval; hardware not stated in extract</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B 3.62x/tau 4.98; LLaMA2-Chat-7B 3.43x/tau 4.70; LLaMA2-Chat-13B 4.21x; also LLaMA2-70B, LLaMA3-8B/70B</t>
+          <t>Vicuna-7B 3.62x/tau 4.98; LLaMA2-Chat-7B 3.43x/4.70; LLaMA2-Chat-13B 4.21x/4.75; LLaMA2-Chat-70B 3.51x/4.48; LLaMA3-8B 3.46x/4.53; LLaMA3-70B 3.29x/4.16 (MT-bench, T=0)</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -9187,7 +9191,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9228,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>pays off only with long shared prefixes or large trees; requires a custom attention kernel inside the serving engine</t>
+          <t>pays off only with large token trees or long shared prefixes (stated); gain small where attention is a minor share of latency (~30% in multi-step reasoning: 1.03-1.10x); requires a custom Triton attention kernel in the engine</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -9234,7 +9238,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>none extra (kernel metadata only)</t>
+          <t>none extra (kernel metadata only; paged and unpaged KV supported)</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -9249,17 +9253,17 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>up to 2.23x end-to-end, 3.59x attention latency vs SOTA attention kernels (tree-based workloads incl. SD)</t>
+          <t>SD trees 32/64/128/256 nodes: 1.43x/1.70x/2.22x/2.52x e2e vs Radix Attention, 3.82x attention (Llama3-8B, A100-80GB, v2); latest abstract: up to 2.23x e2e / 3.59x attention</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Llama-3-8B / Llama-3.1-8B used in examples; per-model numbers not extracted</t>
+          <t>Llama3-8B: SD workload 1.43-2.52x e2e vs Radix Attention (A100-80GB, v2); few-shot 1.24-1.33x</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>APPS (SD trees, 64 tokens), few-shot prompting and multi-step reasoning tree workloads</t>
+          <t>few-shot prompting (4k prompt), multi-step reasoning (sorting, doc merging, keyword counting, set intersection), speculative decoding token trees</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
@@ -9269,7 +9273,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9320,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>68M/160M drafter + KV and tree (not reported)</t>
+          <t>not reported; Llama-68M/160M drafter + KV and verify tree (est.)</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -9331,12 +9335,12 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>up to 3.98x (A100-80GB), 2.76x on A40 vs SpecInfer/Sequoia/vLLM-Spec; bs1</t>
+          <t>up to 3.98x (A100-80GB), 2.76x (A40) vs SpecInfer baseline; 1.49x over Sequoia; bs1 (single request), T=0; PyTorch TorchInductor + CUDA Graphs</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Llama-2-7B/13B targets with Llama-68M/160M drafters: up to 3.98x</t>
+          <t>Llama-2-7B + Llama-68M and Llama-2-13B + Llama-160M: up to 3.98x (A100)</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -9351,7 +9355,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9392,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>needs drafter on separate GPU(s) or they contend on one GPU; post-verify drafts are wasted on rejection and target runs 1.29-1.42x more forward passes</t>
+          <t>needs drafter on separate GPU(s) or they contend for one GPU (stated); post-verify drafts are wasted on rejection, so draft and target run +29-42% more forward passes than SD</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -9398,7 +9402,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>full separate drafter (e.g. 7B for 70B) + its KV on extra GPU</t>
+          <t>full separate drafter (e.g. 7B for 70B) + its KV on its own GPU (draft 1 GPU, 70B target 3 GPUs)</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -9408,17 +9412,17 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>MAT 26.53 (CodeLlama 7B/70B, HumanEval); 39.90 DeepSeek 6.7B/33B (PEARL's MAT definition)</t>
+          <t>MAT (PEARL's definition) 26.53 vs 8.32 SD (CodeLlama 7B/70B, HumanEval); 27.95 (7B/34B); 39.90 vs 5.69 (DeepSeek 6.7B/33B)</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>4.43x (CodeLlama 7B-&gt;70B, HumanEval, A100-80G, bs1, bf16); README headline 3.87x HumanEval on H100</t>
+          <t>4.43x vs AR, 1.46x vs SD (CodeLlama 7B-&gt;70B, HumanEval, A100-SXM4-80G, bs1, bf16)</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Llama 2 7B/70B: 3.82x GSM8K, 2.64x MT-Bench, 3.95x MGSM; Llama 3.1 8B/70B: 3.95x MGSM, 3.59x MT-Bench</t>
+          <t>Llama2 7B/70B: 3.29x HumanEval, 3.82x GSM8K, 2.64x MT-Bench avg; Llama3.1 8B/70B: 3.87x HumanEval</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -9433,7 +9437,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9464,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>ICLR 2026</t>
+          <t>arXiv 2026 (v3 May 2026; earlier ICLR 2026 note not confirmed)</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -9470,7 +9474,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>needs a dedicated draft GPU; speculations for missed outcomes are wasted compute; hit rate drops with batch size and temperature</t>
+          <t>needs a dedicated draft GPU; speculations for missed outcomes are wasted compute; cache misses rise with batch size (at bs16 a fast backup speculator beats the neural one)</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -9480,7 +9484,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>1B drafter on separate H100 + speculation cache 'hundreds of MB'</t>
+          <t>1B drafter on separate H100 + speculation cache O(BFK(K+1)(V+1)) bits, 'hundreds of MB' (stated)</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -9490,17 +9494,17 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau</t>
+          <t>not reported as tau (cache hit rate ~80-90% at fan-out 128, T=0)</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>4.8x avg vs AR (Llama-3.1-70B on 4x H100 + 1B draft on 1x H100, bs1, T=0); 255.8 vs 161.8 SD vs 54.7 AR tok/s; ~30% over best SD baseline</t>
+          <t>4.68x avg vs AR, 1.58x vs SD (Llama-3.1-70B on 4x H100 + 1B draft on 1x H100, bs1, T=0): 255.8 vs 161.8 SD vs 54.7 AR tok/s; Qwen3-32B 2.29x</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B + Llama-3.2-1B: 5.3x HumanEval, 5.6x GSM8K, 4.8x avg vs AR</t>
+          <t>Llama-3.1-70B + Llama-3.2-1B: 5.17x HumanEval, 5.50x GSM8K, 4.10x Alpaca, 3.93x UltraFeedback, 4.68x avg vs AR</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -9515,7 +9519,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9556,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>3 models resident with 3 KV caches; theory conditions hard to meet beyond 3 models (stated); extra verification stage to schedule</t>
+          <t>3 models resident with 3 KV caches whose footprint grows with length, lowering gains on summarization/RAG (stated); conditions for &gt;3 models hard to meet with off-the-shelf models (stated)</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -9562,7 +9566,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>full 4-bit quantized copy of target + EAGLE head + their KV (est.)</t>
+          <t>not reported; full 4-bit (group 128) copy of target + EAGLE-2 head + their KV (est.)</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -9572,32 +9576,32 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>9.1-10 tokens avg (secondary review)</t>
+          <t>9.88 (Vicuna-7B), 9.84 (LLaMA2-7B), 9.44 (LLaMA3-8B), 9.32 (Qwen2-7B) tokens per target pass, Spec-Bench overall; 7.48 LLaMA2-70B; T not stated</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>up to 4.43x Vicuna-7B; hardware/T not extracted</t>
+          <t>3.48x Vicuna-7B overall (up to 4.43x Math); 3.66x LLaMA2-7B; A800-80G; T not stated</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>LLaMA2-Chat-7B 3.31-4.01x; LLaMA3-8B up to 3.87x; Vicuna-7B up to 4.43x; Vicuna-13B 2.69x; LLaMA-70B 2.92x</t>
+          <t>LLaMA2-7B 3.31-4.10x (3.66x overall); LLaMA3-8B 2.71-3.87x (3.31x); Vicuna-7B 3.48x; Vicuna-13B 2.69x; LLaMA2-70B 2.92x</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Spec-Bench tasks (MT-Bench, translation, summarization, QA, math, RAG)</t>
+          <t>Spec-Bench (MT, translation, summarization, QA, math, RAG)</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>promised, not found</t>
+          <t>release promised, not found</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9638,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>unpad-realign-repad overhead grows superlinearly (~40% of compute at bs8, 46.7% at bs16); static batching only, no continuous batching</t>
+          <t>unpad-realign-repad overhead grows superlinearly (39.4% of compute at bs8, 46.7% at bs16); beyond bs8 cross-batch grouping fails more often and falls back to realignment; static batching only</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -9644,12 +9648,12 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>drafter (68M-0.6B) + KV; padding overhead not reported</t>
+          <t>drafter (68M or 0.6B) + its KV; padding overhead not reported</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>~95% exact output equivalence at greedy (residual attributed to FP nondeterminism)</t>
+          <t>90-97% exact output match vs AR at greedy (95-98% partial match); residual attributed to FP nondeterminism</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -9659,12 +9663,12 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>up to 3x throughput at bs8 vs bs1 (A100-80GB, greedy, 5 draft tokens)</t>
+          <t>EqSpec 2.4-2.6x at bs4, ExSpec 2.8-3.0x at bs8 throughput vs bs1 (A100-80GB, greedy, 5 draft tokens, HF Transformers 4.51.3)</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B/68M: 92.1% exact match at bs4 (EqSpec) vs 0.2% BSP, 0.0% DSD</t>
+          <t>Vicuna-7B/68M: 2.6x (EqSpec, bs4), 2.8x (ExSpec, bs8) vs bs1; baselines BSP 0.2-3.5%, DSD ~0% exact match</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -9679,7 +9683,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9730,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>self-spec: draft KV budget 128-4K tokens/seq, no extra weights; standalone drafter adds up to 38-140% memory</t>
+          <t>self-spec: draft KV budget 256-512 (StreamingLLM) or ~2K (SnapKV) tokens/seq, no extra weights; standalone drafter can take 38-140% of target memory (stated)</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -9736,22 +9740,22 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>expected tokens/step 2.31-8.21 across settings; acceptance up to ~90-95% (LLaMA-3.1 self-spec)</t>
+          <t>expected tokens/step 2.53-5.61 across configs (latest version); SnapKV drafts accept far more than StreamingLLM</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>up to 2.51x LLaMA-3.1-8B (100K ctx, 8x H100, greedy); 2.01x at bs256, 32K ctx</t>
+          <t>up to 2.51x LLaMA-3.1-8B (SnapKV self-spec, 100K ctx, bs41, 8x H100, greedy); 1.2-1.7x StreamingLLM self-spec at bs32-128, 8K-32K ctx (A100/H100/L40)</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3.1-8B up to 2.51x; LLaMA-2-7B-32K 1.75x at bs256; also LLaMA-3.1-70B, LLaMA-2-70B</t>
+          <t>LLaMA-3.1-8B up to 2.51x (SnapKV); LLaMA-2-7B-32K 1.27-1.69x (8x A100, v1), 1.68x bs64 8K ctx</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>PG-19, RULER (niah-multikeys-3, cwe, qa-1)</t>
+          <t>PG-19, RULER (QA-1, CWE, needle-in-haystack)</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
@@ -9761,7 +9765,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9823,27 +9827,27 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>1.1-1.8x vs AR across 15 setups; 6-55% over vanilla SD; abstract range 1.14-14.3x (L40, A800)</t>
+          <t>1.1-1.8x vs AR across 15 setups (1x L40, 1/2/4/8x A800, vLLM); 10-61% over other methods' speedup; abstract 1.14-14.3x is vs other speculative systems, not AR</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B + Llama-3.2-1B on 8x A800; Vicuna-7B/68M, Vicuna-33B/160M (per-model numbers not extracted)</t>
+          <t>Llama-3.1-70B + Llama-3.2-1B on 8x A800; Vicuna-7B/68M (L40, A800), Vicuna-33B/160M (2-4x A800); per-model numbers in figures</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Azure LLM inference traces, Mooncake trace, SpecBench mix</t>
+          <t>Azure LLM inference traces (code, conversation), Mooncake trace (v1); BurstGPT in v2</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>none found</t>
+          <t>https://github.com/cerebellumking/AdaSpec (per v2)</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9884,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>acceptance is an exogenous input, so tree or verifier choices cannot be modeled; valid only before saturation</t>
+          <t>acceptance is an exogenous constant per token (independent of earlier rejections), so tree or verifier choices cannot be modeled; models mean latency only, valid before saturation</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -9905,17 +9909,17 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>no new speedup; SD speedup diminishes with load (vLLM 0.13.0, A100)</t>
+          <t>no new speedup; SD speedup erodes with load when C2 ratio &gt;1, faster for longer drafts (vLLM 0.13.0, 1x A100; 4x A100 for 70B)</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-8B/70B with EAGLE-3-style drafter and Llama-3.1-8B drafter for 70B (numbers not extracted)</t>
+          <t>Llama-3.1-8B (1x A100) and 70B (4x A100) verifiers with EAGLE-3-style drafter, Llama-3.1-8B drafter for 70B; no speedup numbers; also Qwen3 8B-235B, gpt-oss-20b</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>synthetic prompts from Pride and Prejudice; prefill/decode 256-1024</t>
+          <t>synthetic prompts from Pride and Prejudice; prefill/decode 256-1024; GuideLLM load sweep</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
@@ -9925,7 +9929,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10081,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Separate drafter runs gamma sequential passes and keeps its own KV cache; drafter must share the target tokenizer; rejected tokens waste target FLOPs (more total arithmetic), which hurts once compute-bound</t>
+          <t>Separate drafter runs gamma sequential passes and keeps its own KV cache; drafter must share the target tokenizer; rejected tokens waste target FLOPs (more total arithmetic, stated), which hurts once compute-bound</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -10087,7 +10091,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Separate drafter (T5-small 77M to T5-large for T5-XXL) + its KV cache (unv.)</t>
+          <t>Separate drafter (T5-small 77M / base 250M / large 800M for T5-XXL 11B) + its KV cache</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -10097,12 +10101,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; acceptance rate alpha per pair/task (e.g. ~0.75 EnDe T5-small, unv.)</t>
+          <t>not reported as tau; alpha 0.75-0.82 (T=0) / 0.62-0.71 (T=1) EnDe T5-XXL by drafter; CNN/DM 0.53-0.74; LaMDA 137B 0.57-0.75</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2-3x vs T5X on T5-XXL 11B, TPU-v4, bs1 (unv.); ~3.4x EnDe T=0 with T5-small (unv.)</t>
+          <t>T5-XXL, 1 TPU-v4, bs1: EnDe 3.4x T=0 / 2.6x T=1 (T5-small, gamma 7); CNN/DM 3.1x / 2.3x (T5-small, gamma 5)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -10122,7 +10126,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10163,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Drafter is a separate 4B model trained for the target (same tokenizer), with its own weights and KV; drafting is sequential so drafter latency grows with K; speedup plateaus or regresses as K grows (stated)</t>
+          <t>Drafter is a separate 4B model (8 layers, d=6144) trained for the target with the same tokenizer, with its own weights and KV; drafting is sequential so drafter latency grows with K; efficiency per step drops as K grows (stated)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -10169,12 +10173,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>4B drafter (~8 GB bf16, est.) + its KV cache</t>
+          <t>4B drafter (~8 GB bf16, est.) + its KV cache; served on its own 16 TPU v4</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (within hardware numerics); XSum ROUGE-2 0.156 vs 0.157 greedy; HumanEval 47.0% vs 45.1% nucleus</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -10184,7 +10188,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2-2.5x on Chinchilla 70B, distributed TPU setup (abstract); per-task numbers not captured</t>
+          <t>Chinchilla 70B, 16 TPU v4, bs1, K=4: XSum 2.01x greedy, 1.92x nucleus; HumanEval 2.46x nucleus (14.1 -&gt; 5.73 ms/token)</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -10204,7 +10208,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10261,12 +10265,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; block efficiency figures only</t>
+          <t>block efficiency (T5-Small -&gt; T5-XL, greedy, gamma 7): XSum 2.68 -&gt; 3.31; GSM8K 3.27 -&gt; 4.14; CNN/DM 3.85 -&gt; 4.83</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>+10-45% over standard SD; lossy SD 6-10x latency cut; TPUv4, bs1</t>
+          <t>+10-45% over standard SD; e.g. CNN/DM greedy 2.07x -&gt; 2.53x vs AR (T5-Small/T5-XL, TPUv4, bs1); lossy SD 6-10x latency cut</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -10286,7 +10290,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10343,12 +10347,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; token acceptance rate +0.1 to +0.65</t>
+          <t>not reported as tau; token acceptance rate +0.1 to +0.65 (e.g. Spider 0.44 -&gt; 0.76 per overview)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1.22-3.06x latency reduction (README/abstract); hardware not captured</t>
+          <t>1.42-2.17x latency reduction (ICML/arXiv v4 abstract); hardware not captured</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10368,7 +10372,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -10405,7 +10409,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Drafter must be pretrained from scratch with target tokenizer (32 A100 pretraining) plus target-generated distillation data; separate model + KV; fine-tuned drafter can lose to base drafter on OOD tasks (stated)</t>
+          <t>Drafter must be pretrained from scratch with target tokenizer (600B tokens, 32 A100) plus target-generated distillation data; separate model + KV; fine-tuned drafter loses to base drafter on OOD tasks (WMT18 DeEn, stated)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -10450,7 +10454,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10516,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+6-27% tokens/s over DistillSpec (A100, greedy); e.g. MBPP 0.69 -&gt; 0.57 s/sentence</t>
+          <t>Pythia-31M-&gt;1.4B, A100, vLLM: MBPP 181.7 vs 149.2 tok/s (+22%), CNN/DM +14%, GSM8K +6% over DistillSpec</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -10532,7 +10536,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10589,17 +10593,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>tau 6.45 vs EAGLE-2 3.94 (Vicuna-7B, T=0); 5.22 vs 4.06 (Qwen2.5-7B, T=0)</t>
+          <t>mean tau 6.32 (MT-Bench 6.45) vs EAGLE-2 3.94 (Vicuna-7B, T=0); Qwen2.5-7B 5.28 vs 4.05 (T=0)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>~2x throughput over EAGLE-2 on Qwen2.5-72B, 4 GPUs, bs64 (2150 vs 980 tok/s)</t>
+          <t>Qwen2.5-72B, 4x H800: bs1 250 vs 200 tok/s EAGLE-2 (AR 60); bs64 2150 vs 980 tok/s (AR 1763)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>T=0 tau: Vicuna-7B 6.45; Llama2-Chat-70B 5.64 (EAGLE-2 4.26); Llama3-Instruct-8B 5.25 (EAGLE-2 4.19)</t>
+          <t>mean tau T=0: Vicuna-7B 6.32; Llama2-Chat-70B 5.60 (EAGLE-2 4.17); Llama3-Instruct-8B 5.36 (EAGLE-2 4.18); T=1: L2-70B 5.54, L3-8B 4.97</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10614,7 +10618,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10661,22 +10665,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>not reported; ~0.15B per head at 7B (d x d ResBlock + d x 32k head), ~0.74B for 5 heads (est.)</t>
+          <t>not reported; each head = d x d ResBlock + d x V head, ~0.15B per head at 7B, ~0.74B for 5 heads (est.)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>lossless for Medusa-1 greedy; typical acceptance lossy: MT-Bench score delta -0.14 to +0.05</t>
+          <t>lossless for Medusa-1 greedy; Medusa-2 / typical acceptance lossy: MT-Bench delta -0.14 (V13B) to +0.05 (V33B), Zephyr -0.07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>acceleration rate 3.47 (Vicuna-7B, Medusa-2); 3.51 (13B); 3.01 (33B)</t>
+          <t>acceleration rate 3.47 (Vicuna-7B), 3.51 (13B), 3.01 (33B), 3.14 (Zephyr-7B), Medusa-2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Medusa-1 2.18x, Medusa-2 2.83x (Vicuna-7B, A100, bs1, MT-Bench)</t>
+          <t>Medusa-1 2.18x, Medusa-2 2.83x (Vicuna-7B, A100-80GB, bs1, MT-Bench); Zephyr-7B M2 2.66x</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -10696,7 +10700,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10733,7 +10737,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Heads now run sequentially (one call per draft position), so drafting latency grows with depth; Hydra++ extra decoder layer adds its own KV cache; retrained per target</t>
+          <t>Heads run sequentially (one call per draft position; Hydra++ heads 0.6-1.4 ms each vs Medusa 0.3 ms), so drafting latency grows with depth; Hydra++ prefix attention layer adds its own KV cache; retrained per target</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10758,7 +10762,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Hydra++ 2.70x vs AR, 1.27x vs Medusa (Vicuna-7B, A100-40GB, bs1); 1.63x at bs8</t>
+          <t>Hydra++ 2.70x vs AR, 1.27x vs Medusa (Vicuna-7B, A100-40GB, bs1, MT-Bench); SpecBench avg 2.17x vs Medusa 1.75x; gap to Medusa shrinks at bs8 (fig.)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -10768,7 +10772,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench; summarization and RAG tasks (names not captured)</t>
+          <t>MT-Bench; SpecBench (MT chat, translation, summarization, QA, math, RAG)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -10778,7 +10782,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10825,7 +10829,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0.24B / 0.37B / 0.56B / 0.99B drafter for 7B/13B/33B/70B + 1-layer KV</t>
+          <t>0.24B / 0.37B / 0.56B / 0.99B drafter for 7B/13B/33B/70B (0.28B Mixtral) + 1-layer KV</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10835,17 +10839,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>tau 3.98 (Vicuna-13B, T=0, MT-Bench); 3.81 (LLaMA2-Chat-70B, T=0)</t>
+          <t>tau 3.98 (Vicuna-13B, T=0, MT-Bench), 3.20 at T=1; 3.81 (LLaMA2-Chat-70B, T=0)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3.03x (Vicuna-13B, bs1, T=0, MT-Bench); ~2x throughput at max batch</t>
+          <t>~2.8-3.0x MT-Bench T=0 bs1 (figure); HumanEval 3.33-3.76x; throughput 1.97x (Vicuna-7B, bs8, RTX 3090), 1.99x (L2-70B, bs5, 4x A100-40G)</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench T=0: Vicuna-7B 2.90x/tau 3.94, 13B 3.03x/3.98, 33B 2.97x/3.68; LLaMA2-Chat-70B 2.87x/3.81 (T=1 2.92x)</t>
+          <t>MT-Bench T=0 tau: V7B 3.94, V13B 3.98, V33B 3.68, L2-7B 3.62, L2-13B 3.90, L2-70B 3.81; HumanEval L2-70B 3.52x/4.42, L2-13B 3.76x/4.52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10860,7 +10864,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10907,7 +10911,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>same as EAGLE (0.24B for 7B) + 1-layer KV</t>
+          <t>same as EAGLE (reuses EAGLE drafter, 0.24B for 7B) + 1-layer KV</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10917,17 +10921,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>tau 4.83 (Vicuna-13B, T=0); 4.53 (LLaMA3-Instruct-8B, T=0); dataset column ambiguous in extraction</t>
+          <t>tau 4.83 MT-Bench, mean 4.65 (Vicuna-13B, T=0); mean 4.40 at T=1</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4.26x (Vicuna-13B, T=0, bs1); 3.80x at T=1</t>
+          <t>4.26x MT-Bench, 4.04x mean (Vicuna-13B, T=0, bs1); 3.80x mean at T=1; hardware not stated</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>T=0: Vicuna-13B 4.26x/tau 4.83; LLaMA2-Chat-70B 3.51x/4.48; LLaMA3-8B 3.46x/4.53; LLaMA3-70B 3.29x/4.16</t>
+          <t>T=0 MT-Bench: Vicuna-13B 4.26x/tau 4.83; L2-Chat-70B 3.51x/4.48; L3-8B 3.46x/4.53; L3-70B 3.29x/4.16; mean: L2-7B 3.43x/4.64, L2-13B 4.10x/4.68</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10942,7 +10946,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -10999,7 +11003,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>not captured from EAGLE-3 itself; GTO re-run: tau 6.07 (LLaMA-3.1-8B, T=0), 6.80 (Vicuna-13B)</t>
+          <t>tau 6.65 (Vicuna-13B), 6.13 (LLaMA-3.1-8B), 5.63 (L3.3-70B), T=0; mean 5.99 T=0, 4.90 T=1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -11014,7 +11018,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench, HumanEval, GSM8K, Alpaca, CNN/DM (unv.)</t>
+          <t>MT-Bench, HumanEval, GSM8K, Alpaca, CNN/DM</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -11061,7 +11065,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Multi-step (3-step) alignment multiplies training cost vs EAGLE; needs target top-K logits during training; inherits EAGLE-2 per-target drafter and target-feature dependency</t>
+          <t>Multi-step (n=3) alignment costs n times EAGLE training (stated); needs target top-K logits during training; inherits EAGLE-2 per-target drafter and target-feature dependency</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -11086,7 +11090,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4.05x (LLaMA3-Instruct-70B, H800, bs1, T=0)</t>
+          <t>4.05x (LLaMA3-Instruct-70B, H800, bs1, T=0, mean of 3 sets); T=1 3.85x</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11106,7 +11110,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11163,22 +11167,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>tau 5.44 (LLaMA3-Instruct-8B, T=0); 4.82 at T=1</t>
+          <t>tau 5.38 mean / 4.85 MT-Bench (LLaMA3-Instruct-8B, T=0); 5.20 mean at T=1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3.28x (LLaMA3-8B, A100 80G, bs1, T=0); README claims up to 4.2x</t>
+          <t>3.35x mean (LLaMA3-8B, A100 80G, bs1, T=0); vLLM chain-2: 1.52x bs2 -&gt; 1.25x bs16; README claims up to 4.2x</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>T=0: L3-8B 3.28x/tau 5.44; Vicuna-7B 4.03x/5.47; L2-Chat-7B 3.12x/5.11; L3-70B 3.99x/5.17 (EAGLE-2 4.01x/5.21)</t>
+          <t>T=0 mean: L2-7B 3.28x/tau 5.44; L2-13B 3.74x/5.70; L3-8B 3.35x/5.38; Vicuna-7B 4.23x/5.76 (HASS 4.03x/5.47); L3-70B 3.52x/4.66 (NeurIPS ver., 2 GPUs)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench, HumanEval, GSM8K</t>
+          <t>MT-Bench, HumanEval, GSM8K (also Qwen2-7B, Mixtral-8x7B in NeurIPS ver.)</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -11188,7 +11192,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11239,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>not reported; ~2 transformer-layer equivalent (LSTM + attention + MLP), ~0.4B for 7B (est.) + KV</t>
+          <t>not reported as count; drafter 'comparable to two Transformer layers' (2 LSTM + attention + MLP), ~0.4B for 7B (est.) + KV</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11245,17 +11249,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>not captured</t>
+          <t>tau 3.34 / 3.88 / 3.70 (Vicuna-7B, MT-Bench/HumanEval/GSM8K, T=0)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2.91-3.51x on Vicuna and LLaMA2-Chat (hardware/bs not captured)</t>
+          <t>2.91-3.51x (H800, bs1, T=0 only); 1.01-1.24x over EAGLE</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B/13B, LLaMA2-Chat-7B/13B: 2.91-3.51x (per-model split not captured)</t>
+          <t>T=0 MT-Bench: Vicuna-7B 3.10x/3.34; V13B 2.97x/3.37; L2-Chat-7B 2.94x/2.82; L2-13B 3.11x/2.95 (HumanEval up to 3.51x)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11270,7 +11274,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11317,12 +11321,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>not reported (lightweight RNN drafter + per-beam state)</t>
+          <t>not reported (one-layer RNN + few MLP layers drafter, + per-beam state)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>lossless at T=0; T&gt;0 implementation may not match distribution (README)</t>
+          <t>lossless (stated); README notes T&gt;0 implementation may not match distribution</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -11332,12 +11336,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2.80x (Vicuna-7B/13B, H100, PyTorch, bs1, greedy); MLX M2 Ultra 13B 1.94x (abstract: up to 2.3x)</t>
+          <t>2.80x (Vicuna-7B/13B, H100, PyTorch, bs1, greedy); MLX up to 2.3x M2 Ultra, 1.37x M1 Max; bs80 BW2 ~1636 tok/s total (H100, 7B)</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench: Vicuna-7B 2.80x/tau 4.20; 13B 2.80x/4.21; 33B 2.61x/3.87 (EAGLE 2.69/2.74/2.80x)</t>
+          <t>MT-Bench: Vicuna-7B 2.80x/tau 4.20; 13B 2.80x/4.21; 33B 2.61x/3.87 (EAGLE 2.69/2.74/2.80x); AlpacaEval 7B 2.69x/4.06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11352,7 +11356,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11418,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3.73x (LLaMA-3.1-8B, A100 80GB, bs1, T=0); +7.7% over EAGLE-3</t>
+          <t>3.73x (LLaMA-3.1-8B, A100 80GB, bs1, T=0) vs EAGLE-3 3.46x; T=1 2.89x</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -11434,7 +11438,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11496,12 +11500,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2.62x MT-Bench, 3.35x HumanEval (LLaMA-3.1-8B EAGLE-3, vLLM 0.11, bs1, T=0)</t>
+          <t>2.62x MT-Bench, 3.35x HumanEval (LLaMA-3.1-8B EAGLE-3, vLLM 0.11, bs1, T=0); hardware not stated</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3.1-8B EAGLE-3: tau 3.84 (T=0), speed 2.62x MT-Bench; LLaMA-3.3-70B also tested (numbers not captured)</t>
+          <t>LLaMA-3.1-8B EAGLE-3: tau 3.84 (T=0), 2.62x MT-Bench; MLP speculator HumanEval tau 2.42 -&gt; 2.83; LLaMA-3.3-70B EAGLE-3 mean tau 4.81 T=0 (+0.5%), 4.66 T=1 (+3.5%)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11516,7 +11520,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11557,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Training needs the target in the loop for rollouts (RL-style verl stack, teacher inference memory); per-target retraining; main recipe is on a DFlash block drafter, so inherits its target-feature dependency</t>
+          <t>Training needs the target in the loop for rollouts (verl RL stack, ~120 H200 GPU-h for Qwen3-4B); per-target retraining; main recipe is on a DFlash block drafter, so inherits its target-feature dependency</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -11563,7 +11567,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>not reported (DFlash b16 or EAGLE-3 drafter, same as base drafter)</t>
+          <t>not reported as count; 5-layer drafter for 4B/8B targets (8 layers for 30B), same as base drafter</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11578,7 +11582,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>mean 4.86x (Qwen3-4B, T=0 thinking), 4.89x (Qwen3-8B); hardware/bs not captured</t>
+          <t>mean 4.86x (Qwen3-4B, T=0 thinking), 4.89x (Qwen3-8B); H200, bs1</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11598,7 +11602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11639,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Each training step runs a simulated verification (target forward), raising training cost; verification head is training-only; drafter still per-target</t>
+          <t>Supervision comes from simulated verification against the target's outputs, so the drafter is tied to that target and acceptance rule and retrained per target; inherits base drafter's target-feature dependency</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -11660,12 +11664,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4.39x vs 4.07x (Qwen3-4B EAGLE-3, A100 80GB, bf16, HF, T=0)</t>
+          <t>4.39x vs 4.07x (Qwen3-4B EAGLE-3, A100 80GB, bf16, HF Transformers, T=0); DFlash 4.81x vs 4.54x</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3.1-8B: EAGLE-3 tau +2.5%, speed +3.8%; DFlash tau +3.8%, speed +3.4%</t>
+          <t>LLaMA-3.1-8B T=0: EAGLE-3 tau 5.66 -&gt; 5.81, 3.84x -&gt; 3.97x; DFlash tau 5.39 -&gt; 5.59, 4.19x -&gt; 4.34x</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11675,12 +11679,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/naver-ai/VAT (per paper; README not fetched)</t>
+          <t>https://github.com/naver-ai/VAT</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11717,7 +11721,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Ens-EAGLE keeps N=O(log T) drafter copies with different learning rates (memory xN); online updates use serving GPUs and drafter drifts; Online-LR variant is step-level and lossy</t>
+          <t>Ens-EAGLE keeps N drafter copies (N=3 in experiments) with different learning rates (memory xN); online updates need training compute and the drafter drifts during serving; Online-LR variant is step-level and lossy</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -11727,27 +11731,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Ens: N=O(log T) drafter copies + optimizer state (not quantified); Opt-Hydra: Hydra heads + momentum state</t>
+          <t>Ens: 3 drafter copies + optimizer state (not quantified); Opt-Hydra: Hydra heads + momentum state</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>lossless (token-level variants); Online-LR lossy (MMLU acc 84.52% reported)</t>
+          <t>lossless (token-level variants); Online-LR lossy (Qwen3-8B MMLU 84.52% vs target 83.81%)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>tau 2.70 (Opt-Hydra, Vicuna-7B, Alpaca-finance); 2.73 (Vicuna-13B); 2.01 (Ens-EAGLE, GSM8K)</t>
+          <t>tau 2.70 (Opt-Hydra, Vicuna-7B, Alpaca-finance); 2.94 (Llama-2-7B-Chat, GSM8K); 2.01 (Ens-EAGLE, Vicuna-7B, GSM8K)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1.55x (Opt-Hydra, Vicuna-7B); 1.84x (Vicuna-13B); 4x A800 80GB</t>
+          <t>vs vanilla SD (not AR): Opt-Hydra 1.18-1.55x (Vicuna-7B), 1.61-2.03x (Llama-2-7B-Chat); 4x A800 80GB</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B: Opt-Hydra 1.55x/tau 2.70, Ens-EAGLE 1.41x/2.01, Ens-EAGLE-3 1.26x/2.16; Vicuna-13B Opt-Hydra 1.84x/2.73</t>
+          <t>vs vanilla SD: Vicuna-7B Opt-Hydra 1.55x/2.70, Ens-EAGLE 1.41x/2.01, Ens-EAGLE-3 1.27x/2.07; Llama-2-7B-Chat Opt-Hydra 2.03x/3.28 (Spider), Ens-EAGLE 1.61x/1.82</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11762,7 +11766,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11793,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>venue? (not stated)</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -11809,7 +11813,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>~462 MB drafter, 127 MB trainable private part</t>
+          <t>~462 MB drafter params (full retrain), 127 MB trainable private part (27.5%)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11819,12 +11823,12 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>tau 4.79 vs 4.37 (Qwen2.5-Math-7B, T=0); 5.18 vs 4.59 (Coder-7B)</t>
+          <t>tau 5.19 vs 4.69 full FT (Qwen2.5-Math-7B, T=0); 5.18 vs 4.59 (Coder-7B); 4.21 vs 3.89 (Meditron3-Qwen2.5-7B)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3.06x vs ~2.88x (Math-7B, T=0, notes); PDF extract 3.27x, README 3.45x (inconsistent); 4x H200</t>
+          <t>3.27x vs 3.07x full FT (Math-7B, T=0); Coder 3.11x vs 2.76x; 4x H200 stated (other extract gave 3.06x; numbers conflict)</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -11996,7 +12000,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Draft still runs ~50% of target depth per token, capping speedup; skip set searched offline per model (2.5-6 h BO) and static, so it degrades under task shift</t>
+          <t>Draft still runs ~50% of target depth per token, capping speedup; skip set searched offline per model (BO, 1000 iters, ~2.5 h 13B, ~6 h 70B) and static, so it degrades under task shift</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -12011,17 +12015,17 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (ROUGE-2 0.108 vs 0.106 LLaMA-2-13B CNN/DM; Pass@1 0.317 vs 0.311 CodeLLaMA-13B)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>acceptance 0.85-0.92 (LLaMA-2, greedy); tau not reported</t>
+          <t>acceptance ~0.92 (LLaMA-2-13B CNN/DM, greedy), 0.85-0.92 across LLaMA-2; tau not reported</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>1.22-1.99x (A100, HF, bs1 implied); best 1.99x LLaMA-2-70B CNN/DM</t>
+          <t>1.22-1.99x (A100 40/80GB, HF transformers 4.33, bs1, greedy; T=0.2/0.6 sampling also tested); best 1.99x LLaMA-2-70B CNN/DM</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -12031,7 +12035,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>CNN/DM, XSum, HumanEval</t>
+          <t>CNN/DM, XSum, HumanEval (GSM8K, MT-Bench in later version)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -12041,7 +12045,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12088,32 +12092,32 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>none extra (single model, shared KV and exit head)</t>
+          <t>none extra (single model, shared exit LM head; draft KV and hidden states reused by verify)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>lossless vs the LayerSkip-trained model (which differs from original checkpoint)</t>
+          <t>lossless vs the LayerSkip-trained model; trained model has minimal last-layer accuracy drop vs original (continual pretraining)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>not reported in abstract (acceptance tracked in paper)</t>
+          <t>token acceptance 68.9% Llama2-7B / 74.5% 13B CNN/DM (E=8, d=12, continual PT); 77.8% 7B from scratch; 45% Llama1-7B HumanEval; tau not reported</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>up to 2.16x CNN/DM, 1.82x coding, 2.0x TOPv2 (hardware not recorded)</t>
+          <t>up to 2.16x CNN/DM (Llama2-7B, scratch PT), 1.82x HumanEval (A100), 2.0x TOPv2; H100, greedy, max 512 tokens, bs1</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Llama2-7B/13B, Llama 1.5B, Llama1-7B code (v1); later versions add Llama3 (unv.); up to 2.16x</t>
+          <t>Llama2-7B 1.86x / 13B 1.81x CNN/DM, 7B 1.54x XSum (continual PT); Llama2-7B 2.16x, 1.5B 1.76x CNN/DM (scratch); Llama1-7B 1.82x HumanEval; Llama 1.5B 2.0x TOPv2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>CNN/DM, HumanEval, TOPv2, MMLU, NaturalQuestions</t>
+          <t>CNN/DM, XSum, HumanEval, TOPv2 (+ MMLU, NaturalQuestions etc. for last-layer accuracy)</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -12123,7 +12127,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12174,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67M adapter (Vicuna-7B) + its 1-layer KV</t>
+          <t>67M adapter (Vicuna-7B; 88.7% fewer than Medusa 591M) + its 1-layer KV</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12180,17 +12184,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>compression rate 1.41-2.22 by Spec-Bench subtask (Vicuna-7B, per fetched table)</t>
+          <t>compression rate 1.41-2.22 by Spec-Bench subtask (Vicuna-7B)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>up to 1.68x Spec-Bench; avg 1.50x Vicuna-7B, 1.44x Vicuna-13B (V100, bs1 implied)</t>
+          <t>avg 1.50x Vicuna-7B (1.24x translation to 1.68x MT-Bench), 1.44x Vicuna-13B (V100; bs and temperature not stated; exit l=2/3, eta 0.6, gamma 6)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B avg 1.50x (up to 1.68x), Vicuna-13B 1.44x</t>
+          <t>Vicuna-7B avg 1.50x (up to 1.68x MT-Bench, 1.61x math), Vicuna-13B avg 1.44x (up to 1.66x MT-Bench)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12205,7 +12209,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12266,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>acceptance 98-100% greedy (LLaMA-2); tau not recorded</t>
+          <t>mean generated length M 4.34 CNN/DM, 3.13 GSM8K, 8.21 TinyStories (LLaMA-2-13B, greedy); 3.85/2.99/6.17 (LLaMA-2-70B); 4.75 CodeLLaMA-13B HumanEval</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -12344,7 +12348,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>tau 1.28-6.22 (LLaMA-3-8B, T=0), 2.57-5.81 (LLaMA-3-70B, T=0); T=1: 0.98-4.26 (8B), 1.53-5.38 (70B), by Spec-Bench task</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -12416,7 +12420,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0.52-2.26% memory overhead (LayerSkip 0.50-1.42%)</t>
+          <t>0.52-2.26% memory overhead (avg 1.54%)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12431,12 +12435,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2.16-2.62x vs AR (A100/H100, bs1, greedy and T=0.6)</t>
+          <t>1.98-2.84x vs AR by model and task (A100 40GB / H100 80GB, bs1, T=0.6 sampling, greedy for pass@1)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3-8B 2.62x; LLaMA-2-7B 2.50x; LLaMA-2-70B 2.84x (as summarized); CodeLLaMA-7B 2.26x; also Llama-3.2-1B, 13B, CodeLlama-34B</t>
+          <t>LLaMA-2-7B 2.12-2.75x, 13B 1.98-2.29x, 70B 2.12-2.84x by task; LLaMA-3-8B 2.62x; Llama-3.2-1B 2.36x; CodeLLaMA-7B/34B 2.26x/2.12x HumanEval</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12451,7 +12455,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12488,7 +12492,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Lossy early exit, output can differ from the full model; predictors trained per model and need an EAGLE draft model for features</t>
+          <t>Lossy early exit, output can differ from the full model; predictors trained per model and need an EAGLE draft model for features; predictors add ~5.6% latency</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -12513,12 +12517,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2.25x cloud (A100 80GB vs HF), 2.43x PC (RTX 4060 laptop vs llama.cpp)</t>
+          <t>2.25x cloud (Llama2-7B, A100 80GB vs HF, combined with other opts), 2.43x PC (RTX 4060 laptop vs llama.cpp); SpecEE alone 1.23-1.43x vs HF; 256 output tokens, bs not stated</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Llama2-7B 2.25x cloud / 2.43x PC; Llama2-13B/70B 1.14x/1.12x over HF baseline component</t>
+          <t>Llama2-7B 2.25x cloud / 2.43x PC; Llama2-13B 1.43x, 70B 1.23x vs HF (A100); with EAGLE 1.05x/1.06x over EAGLE (7B/13B)</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12533,7 +12537,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12672,32 +12676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>acceptance &gt;90% (91.16% LWM-Text-Chat-128K at 128K)</t>
+          <t>acceptance 89.9-94.3%: 91.16% Llama-2-7B-32K (Multi-LexSum 32K), 94.31% LWM-Text-Chat-128K (Multi-LexSum 128K)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>up to 2.49x (Llama-2-7B-32K-Instruct, 32K ctx, bs1, A6000)</t>
+          <t>up to 2.49x (LWM-Text-Chat-128K, 128K ctx, bs1, 2x A6000); 1.35x at 4K to 2.08x at 32K (Llama-2-7B-32K-Instruct)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Llama-2-7B-32K-Instruct up to 2.49x; LWM-Text-Chat-128K (Llama-2-based)</t>
+          <t>Llama-2-7B-32K-Instruct 1.35-2.08x (4K-32K); LWM-Text-Chat-128K (Llama-2-based) 1.78-2.49x (16K-128K)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>PG-19, Multi-LexSum, LWM long-context, 4K-128K</t>
+          <t>PG-19, Multi-LexSum, InfiniteBench Sum; contexts 4K-128K</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>none found (no link in paper)</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12749,22 +12753,22 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>lossless vs W4A16 (W4A4 alone loses e.g. 25-51% on GSM8K/MATH)</t>
+          <t>lossless vs W4A16 (W4A4 alone loses 25-51% relative, e.g. GSM8K 73.4 to 54.2, Llama-3-8B Atom)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>not recorded (gamma=3)</t>
+          <t>not reported as tau (gamma=3; &gt;80% W4A4/W4A16 token agreement)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>avg 1.38x, up to 1.64x throughput vs W4A16 (Llama-2-7B, bs32, L20 48GB)</t>
+          <t>avg 1.38x, up to 1.64x throughput vs W4A16 (Llama-2-7B, bs32; 4x L20 48GB, gamma 3, group size 128)</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Llama-2-7B up to 1.64x vs W4A16; Llama 3B/8B/13B tested</t>
+          <t>Llama-2-7B avg 1.58x (up to 1.64x), Llama-2-13B 1.47x, Llama-3.2-3B 1.25x vs W4A16; Llama-3-8B quality tests</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12779,7 +12783,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12836,7 +12840,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>acceptance ~0.92 (T=0), &gt;0.9 at T=1</t>
+          <t>acceptance &gt;0.9 across temperatures (Llama2-7B-128K, retrieval-cache draft)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -12861,7 +12865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12927,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>up to 2x LLaMA-2-7B-32K (32K, bs32), 1.84x LLaMA-3.1-8B (100K, bs32), 8x A100, greedy</t>
+          <t>up to 2x LLaMA-2-7B-32K (32K, bs32), 1.84x LLaMA-3.1-8B (100K, bs32) on 8x A100; 1.84x LLaMA-2-7B (8K, bs64) on 4x H100; greedy, 64 output tokens</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-2-7B-32K up to 2x; LLaMA-3.1-8B 1.84x; TinyLlama-1.1B draft variant</t>
+          <t>LLaMA-2-7B-32K up to 2x; LLaMA-3.1-8B 1.84x (100K), 1.43x (64K); TinyLlama-1.1B draft variant</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12943,7 +12947,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -12995,7 +12999,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>lossless (greedy)</t>
+          <t>lossless (identical BLEU to greedy)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -13005,7 +13009,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>up to 38% faster than AR; ~2x with parallel resources (MT models)</t>
+          <t>PGJ up to 38% faster on CPU (Opus); HGJ 1-8% faster on GPU (MBart50); ~2x bound with parallel resources</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -13015,7 +13019,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>machine translation benchmarks (not recorded)</t>
+          <t>WMT14, WMT16, WMT17, IWSLT15, IITB, FLORES</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -13025,7 +13029,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13066,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Spends 56-120x extra FLOPs per step, so it slows in compute-bound settings (large batch); Jacobi guesses from an untrained model have low hit rate</t>
+          <t>Spends 56-120x extra FLOPs per step (W=15,N=5 at 7B), so it slows in compute-bound settings (large batch) and weak GPUs (~30% on RTX 3090); Jacobi guesses from an untrained model have low hit rate</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -13082,7 +13086,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>step compression ~1.5-2.0</t>
+          <t>step compression ~1.6-2.05 (LLaMA-2-7B MT-Bench ~2.0; summarization 1.64-1.77)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -13107,7 +13111,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13148,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Modifies target weights, so output is not guaranteed equal to the original model; needs per-domain trajectory generation and training (2-30 A100 h)</t>
+          <t>Modifies target weights, so output is not equal to the original model; needs per-domain trajectory generation and training (2-30 h on 8x A100)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -13159,22 +13163,22 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>lossless vs CLLM; vs original: near-no accuracy loss reported</t>
+          <t>lossy vs original fine-tuned target: GSM8K 59.1 to 56.4, Spider 70.0 to 69.3, CSN 60.4 to 59.2, MT-Bench 6.5 to 6.4</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>not recorded (fast-forwarded tokens per iteration reported)</t>
+          <t>not reported as tau; fast-forwarded tokens per iteration 2.0-6.8x vs base model</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2.4-3.4x Jacobi, 2.5-3.6x with lookahead (A100, bs1)</t>
+          <t>Jacobi 2.4-3.4x, lookahead 2.5-3.6x (A100 40GB, bs1); e.g. GSM8K 43.5 to 132.4 tok/s</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-2-7B-based targets: 3.0x GSM8K, 2.4x ShareGPT/MT-Bench (Jacobi)</t>
+          <t>LLaMA2-7B-based targets: GSM8K 3.0x Jacobi / 2.9x lookahead; ShareGPT/MT-Bench 2.4x / 2.5x</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13189,7 +13193,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13250,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>mean generated length 1.77 Vicuna-7B/13B MT-Bench greedy (1.72 nucleus); 2.65/2.45 CodeLlama-7B/13B HumanEval greedy</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -13256,7 +13260,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B 1.69x, Vicuna-13B 1.77x (MT-Bench greedy); CodeLlama-7B 2.36x, 13B 2.27x (HumanEval)</t>
+          <t>Vicuna-7B 1.69x, 13B 1.77x MT-Bench greedy (1.62x/1.71x nucleus); CodeLlama-7B 2.36x, 13B 2.27x HumanEval greedy</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13323,7 +13327,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (HF transformers: works with greedy and sampling)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -13333,7 +13337,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>avg ~2.4x on summarization and context QA (Mistral-7B-Instruct, A100 40GB); smaller on MT-Bench</t>
+          <t>avg ~2.4x on summarization (CNN/DM) and context QA (HAGRID) (Mistral-7B-Instruct-v0.1, A100 40GB, greedy, max_ngram 3, 10 draft tokens); little gain on MT-Bench turn 1</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -13400,7 +13404,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>suffix trees in CPU RAM (~6.15 GB per 572M cached tokens)</t>
+          <t>suffix trees in CPU RAM (~6.15 GB per 572M cached tokens); ~20 us per draft token</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13410,12 +13414,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6.3 AgenticSQL, 7.8 SWE-Bench, 1.75 Spec-Bench (Llama-3.1-8B-Instruct)</t>
+          <t>6.3 AgenticSQL, 7.8 SWE-Bench, 1.75 Spec-Bench (Llama-3.1-8B-Instruct, greedy); hybrid with EAGLE-3 4.68 Spec-Bench</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5.3x AgenticSQL, 2.5x SWE-Bench, hybrid 2.5x Spec-Bench (H100, bs1, vLLM)</t>
+          <t>5.3x AgenticSQL, 2.5x SWE-Bench, 1.66x Spec-Bench alone, hybrid 2.46x Spec-Bench (H100, bs1, greedy); vLLM run with OpenHands-LM-32B, 8 concurrent, TP4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -13435,7 +13439,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -13492,7 +13496,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>MAT 3.03 (+Token Recycling), 3.77 (+EAGLE), 4.61 (+EAGLE-2) Spec-Bench; HumanEval 2.94/4.03/4.79 (Vicuna-7B, greedy)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -13512,7 +13516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>https://github.com/hyx1999/SAM-Decoding</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -13574,7 +13578,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>MAT 2.70 (Vicuna-7B), 2.72 (13B), 2.63 (33B), Spec-Bench, greedy</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -13728,7 +13732,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>n-1 extra transformer-layer heads (7B, n=4: ~0.6B, est.)</t>
+          <t>n-1 extra heads, one transformer layer each, shared unembedding (7B, n=4: ~0.6B, est.)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13753,7 +13757,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MBPP, HumanEval, APPS (unv.); NLP benchmarks</t>
+          <t>MBPP, HumanEval, APPS, CodeContests; ARC-C, COPA, HellaSwag, NQ, PIQA, SIQA, TriviaQA; CNN/DM, XSum and 5 other summarization sets; GSM8K</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -13795,7 +13799,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Sequential depth-1 MTP module trained with the model; reused as a 1-token speculative drafter</t>
+          <t>Sequential depth-1 (D=1) MTP module (1 transformer block, shared embedding and output head) trained with the model; reused as a 1-token speculative drafter</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -13810,7 +13814,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1 MTP module ~14B params on 671B model (unv.) + its KV</t>
+          <t>1 MTP module, 14B params (685B total = 671B main + 14B MTP) + its KV</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13820,12 +13824,12 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2nd-token acceptance 85-90% (unv.)</t>
+          <t>2nd-token acceptance 85-90% across generation topics</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>~1.8x TPS (unv.)</t>
+          <t>1.8x TPS (hardware, batch not stated)</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -13835,7 +13839,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>not recorded</t>
+          <t>various generation topics (not specified)</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -13845,7 +13849,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -13892,7 +13896,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1 MTP head (already in MiMo) + its KV; compressed draft vocab</t>
+          <t>1 MTP head (already in MiMo), 210.8M params fine-tuned (&lt;3% of backbone) + its KV; draft vocab 16K zh / 32K en</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13917,7 +13921,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7 benchmarks, general NLP, math, code (names not recorded)</t>
+          <t>MT-Bench, LiveCodeBench-v6, MATH-500, Natural Questions (QA, RAG), CNN/DM, C-Eval</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -13974,7 +13978,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>gated LoRA + 2-layer sampler (size not reported; small, est.)</t>
+          <t>rank-128 gated LoRA + 2-layer MLP sampler (counts not reported; small vs 8B, est.)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13984,7 +13988,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>up to ~5x tokens/step math and code, ~2.5x chat (Tulu3-8B, k=8)</t>
+          <t>tokens/step (k=8): 5.22 math, 5.35 code, 2.39-2.52 chat, 1.91-2.38 knowledge, 2.79-3.72 safety (Tulu3-8B)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -13999,7 +14003,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>math, code, chat, knowledge tasks of Tulu3 eval (names not recorded)</t>
+          <t>GSM8K, HumanEval, AlpacaEval, IFEval, MMLU, PopQA, TruthfulQA, safety (XSTest, HarmBench, etc.)</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -14161,7 +14165,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>each head predicts its offset independently, so later heads ignore earlier choices; heads share the base trunk, so proposal quality is capped by one hidden state</t>
+          <t>each head predicts its offset independently, so later heads ignore earlier choices; heads share one trunk hidden state; high acceptance needs fine-tuning the trunk, which changes the base model being decoded</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -14171,22 +14175,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) k-1 extra output heads on the base model, no extra KV</t>
+          <t>one extra FFN layer (hidden k x d_hidden, out k x d_model) on a transformer_base model; no extra KV</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>lossless (exact-match variant); lossy variants trade quality for up to 7x fewer iterations</t>
+          <t>lossless vs the (possibly fine-tuned) scoring model; dev BLEU 26.00 base vs 26.11 at k=8 (distill+FT); top-k approx lossy: 25.04 BLEU at k=10 top-2</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; up to 2x fewer decoding iterations lossless (MT)</t>
+          <t>mean accepted block (WMT dev, greedy): 1.76 regular k=8; 4.69 distill+FT k=8, 4.95 k=10; super-res 6.79 at k=10 (FT+approx)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>up to 4x wall-clock (MT and image super-resolution Transformers, greedy)</t>
+          <t>MT up to 3.3x wall-clock (k=8, block 4.7); test k=2 28.95 BLEU 1.72x, k=8 27.88 BLEU 3.31x; super-res 4.0x (k=6); greedy, hardware/bs not extracted</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -14196,7 +14200,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>WMT14 En-De MT (unv.), image super-resolution (unv.)</t>
+          <t>WMT 2014 En-De (newstest2013 dev, newstest2014 test), CelebA image super-resolution (8x8 to 32x32)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -14206,7 +14210,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14237,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR 2026</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -14253,7 +14257,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>separate small LM: Llama3.2-1B (for LLaMA3), Qwen2.5-0.5B, R1-Distill-Qwen-1.5B, plus its KV</t>
+          <t>separate small LM: Llama3.2-1B (LLaMA3 targets), Qwen2.5-0.5B, R1-Distill-Qwen-1.5B, plus its KV</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -14263,32 +14267,32 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>not reported as tau; LLaMA3.1-8B acceptance 1-alpha 0.93 / 4-alpha 0.90 HumanEval, 0.88/0.85 GSM8K (EAGLE-3 0.87/0.85); K_infer 12</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>LLaMA3.1-8B avg 3.57x / 274.4 tok/s, HumanEval 4.08x / 311.5 tok/s; Qwen2.5-7B 4.87x (A100-40GB, bs1, T=0, Transformers+); abstract v4: 3.67x / 264.88 tok/s (versions conflict)</t>
+          <t>vLLM, A100-40GB, bs1: LLaMA3.1-8B avg 3.00x / 219.15 tok/s; Qwen2.5-7B avg 3.18x, HE 3.76x; abstract 3.67x / 264.88 tok/s (earlier version: Transformers+ 3.57x)</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>LLaMA3.1-8B: HumanEval 4.08x, MATH500 3.35x, GSM8K 3.30x, avg 3.57x (Llama3.2-1B drafter)</t>
+          <t>vLLM A100 bs1: LLaMA3.1-8B HE 3.63x (264.88 tok/s), GSM8K 3.20x, SpecBench 2.17x, avg 3.00x; LLaMA3.3-70B HE 4.11x, GSM8K 3.94x, avg 3.49x (84.29 tok/s)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>HumanEval, GSM8K, MATH500</t>
+          <t>HumanEval, GSM8K, SpecBench, MATH500 (appendix)</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/AMD-AIG-AIMA/PARD</t>
+          <t>https://github.com/AMD-AGI/PARD</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14339,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Dream-7B drafter (~15 GB bf16, est.) plus its context processing</t>
+          <t>Dream-7B drafter (~15 GB bf16, est.) plus its context processing; no extra training</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -14345,12 +14349,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>MAT 6.99 across tasks (Qwen2.5-32B, T=0)</t>
+          <t>MAT mean 6.99 (Qwen2.5-32B, T=0): MT 7.02, Trans 7.35, Sum 6.25, QA 7.49, Math 7.61, RAG 8.04</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>up to 3x, mean 3.08x (Qwen2.5-32B, A100-80GB, T=0)</t>
+          <t>mean 3.08x, Math 4.02x, Sum 2.41x, RAG 2.38x (Qwen2.5-32B, 1x A100-80GB, bs1, T=0); path search ~1.1% overhead; draft len 20-30</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -14370,7 +14374,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14407,7 +14411,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>self-selection needs several drafter samples per round (extra drafter compute); block positions sampled from marginals, so drafts can be incoherent</t>
+          <t>self-selection needs several drafter samples per round (extra drafter compute); block positions sampled from marginals, so drafts can be incoherent; full 7B diffusion drafter tied to one tokenizer family</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -14417,7 +14421,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>not reported (diffusion LM drafter, size not extracted)</t>
+          <t>7B diffusion drafter (DiffuCoder-7B for Qwen, DiffuLLaMA-7B for Llama-2) plus its context processing (~14 GB bf16, est.)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -14427,22 +14431,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau; later positions get 3.2x higher acceptance than AR drafter</t>
+          <t>tokens/draft: Qwen2.5-14B Math500 6.20 (T=0); Qwen2.5-72B Math500 7.00 (T=1); EAGLE-2 4.25/4.63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>up to 5.5x avg over AR, +55% tok/s over prior baselines (Qwen2.5-14B/72B, Llama 13B/70B; hardware and T in appendix, not extracted)</t>
+          <t>up to 5.5x avg over AR, +55% tok/s over baselines; Qwen2.5-72B Math500 5.01x (T=1), Qwen2.5-14B 3.65x (T=0) (A100-80GB)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Llama 13B and 70B targets used; per-model numbers not extracted</t>
+          <t>LLaMA-2-70B-Chat HumanEval 5.28x, 7.40 tok/draft (T=1); LLaMA-2-13B-Chat Math500 3.61x, 6.31 (T=0); EAGLE-2 3.91x / 3.48x</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Math500, Alpaca, others not extracted</t>
+          <t>Math500, HumanEval, GPQA, GSM8K, LiveCodeBench, MT-Bench</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -14452,7 +14456,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14489,7 +14493,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>dLLM block positions independent given context; separate dLLM drafter retrained per target family</t>
+          <t>dLLM block positions independent given context; separate dLLM drafter retrained per target family (~240 GPU-h for Qwen3-8B); dLLM KV caching lacks support in vLLM/SGLang, hurting batched serving</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -14499,7 +14503,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>not reported (dLLM drafter, size not stated)</t>
+          <t>~0.5B (~470M) diffusion drafter (from open-dCoder or Qwen2.5-0.5B) plus its KV</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14509,12 +14513,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>~5 avg, max 32 (Qwen3-30B-A3B, T=0)</t>
+          <t>T=0 mean tau 4.61 (Qwen3-4B), 4.61 (8B), 4.82 (14B), 5.03 (30B-A3B); HumanEval 30B-A3B 6.58; max accepted 32 vs EAGLE-3 8</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-4B ~2.8-3.0x, 8B ~3.0x, 14B 3.1-3.7x, 30B-A3B up to 5.54x HumanEval (A100, T=0)</t>
+          <t>T=0, A100-80GB: 30B-A3B HumanEval 5.54x, MBPP 4.00x; 8B 2.35-3.30x; 14B 2.43-3.59x; bs16 HumanEval 175.66 vs AR 49.76 tok/s (no KV cache)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -14524,17 +14528,17 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>HumanEval, MBPP, CodeAlpaca (Python), LiveCodeBench</t>
+          <t>HumanEval, MBPP, CodeAlpacaPy, LiveCodeBench, GSM8K, Math500, Minerva Math</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/czc726/DEER</t>
+          <t>https://czc726.github.io/DEER/ (code announced)</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14571,7 +14575,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>parallel positions share one learned hidden state, so later positions do not see earlier drafted tokens; drafter tied to target features (retrained per target); EAGLE drafter KV grows with context</t>
+          <t>parallel positions use a shared hidden state and mask embedding, so later positions do not see earlier drafted tokens; drafter tied to target features (retrained per target); 4-layer drafter is costlier per pass than EAGLE-3 (slowdown at K=3 on MoE)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -14581,42 +14585,42 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) EAGLE-3-size single-layer drafter plus its KV</t>
+          <t>4-layer drafter, 2-5% of target params (paper), plus its KV</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (standard rejection sampling in vLLM)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>AL K=5: GPT-OSS-120B 2.9-3.5, GPT-OSS-20B 3.4-4.0, Qwen3-Coder-30B 3.0-4.5 (AR EAGLE-3 2.7-4.4); T not stated</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1.10-1.36x over AR EAGLE-3 (GPT-OSS 120B/20B, Qwen3-Coder-30B, vLLM; hardware/bs/T not extracted)</t>
+          <t>vs AR EAGLE-3, vLLM, 1x H200, C=2: GPT-OSS-20B 1.27-1.36x (1205 tok/s HumanEval, K=7); 120B 1.04-1.10x; Qwen3-Coder-30B 1.04-1.11x; no vanilla AR baseline</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ablations only, LLaMA 3.1 8B: 4-layer AL 3.92 HumanEval, 3.04 MT-Bench; 1-layer 2.69 / 2.41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>not extracted</t>
+          <t>HumanEval, MT-Bench, GSM8K (test); training on UltraChat, GSM8K train, OpenCodeInstruct</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>in vLLM; no standalone repo found</t>
+          <t>https://github.com/vllm-project/speculators (training); vLLM inference; no released checkpoints</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14653,7 +14657,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>positions conditionally independent within a block (product of marginals); needs fresh target features every round, so draft and verify serialize (ours: drafter ~16% of a round); block 16 caps accepted length at 16 per round</t>
+          <t>positions conditionally independent within a block (product of marginals); needs fresh target features every round, so draft and verify serialize (ours: drafter ~16% of a round); block 16 caps accepted length; drafter retrained per target</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -14663,32 +14667,32 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) ~1B drafter for Qwen3-8B (5 target-width layers + fc, shared embed/head) ~2 GB bf16; drafter KV ~5/36 of target KV, grows with context</t>
+          <t>1B drafter for Qwen3-8B and for LLaMA-3.1-8B (HF cards, ~2 GB bf16); drafter KV ~5/36 of target KV (est.), grows with context</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>lossless (not audited in bf16)</t>
+          <t>lossless</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>tau 6.49 T=0, 5.48 T=1 (Qwen3-8B avg); 8.01 SGLang Math500 (ours: tau 5.85, Qwen3-8B, A100, HF)</t>
+          <t>tau 6.49 T=0, 5.48 T=1 (Qwen3-8B avg, HF); MATH-500 7.87 T=0; SGLang Math500 8.01 (ours: tau 5.85, Qwen3-8B, A100, HF)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 4.86x T=0, 4.03x T=1 (H200, bs1, HF); SGLang B200 Math500 5.1x c=1 to 2.8x c=32 (ours: HF 4.37x; vLLM 4.84x, 2.69 ms/tok, A100 bs1)</t>
+          <t>Qwen3-8B 4.86x T=0, 4.03x T=1 (H200, bs1, HF); SGLang B200 Math500 5.1x (1175 tok/s) c=1 to 2.8x (16076 tok/s) c=32 (ours: HF 4.37x; vLLM 4.84x, A100 bs1)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3.1-8B-Instruct, block 10, SGLang B200: GSM8K 2.4x at c=1 to 1.6x at c=32 (EAGLE-3 0.6x at c=32)</t>
+          <t>LLaMA-3.1-8B-Instruct, block 10, SGLang B200, T=0: GSM8K 2.4x c=1 to 1.6x c=32, tau 4.32; HumanEval 2.8x, tau 4.91; Alpaca 2.2x, tau 3.73 (EAGLE-3(60) 0.6x at c=32)</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>GSM8K, MATH-500, AIME25, HumanEval, MBPP, LiveCodeBench, MT-Bench, Alpaca; GPQA (thinking); LongBench subsets</t>
+          <t>GSM8K, MATH-500, AIME24, AIME25, HumanEval, MBPP, LiveCodeBench, SWE-Bench, MT-Bench, Alpaca; thinking mode; LLaMA drafter trained on UltraChat+ShareGPT</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -14698,7 +14702,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14725,62 +14729,62 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>blog/code only</t>
+          <t>blog (Inco AI, 2026-08-18) + HF models</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>DFlash plus grouped causal convolution per layer and a candidate selector (first-order Markov rerank of top-k)</t>
+          <t>DFlash plus two-tap dynamic depthwise conv around attention/FFN sublayers and a path selector scoring adjacent token pairs over top-16 candidates per position</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>rerank is only first-order (predecessor/successor), so longer-range dependencies stay independent; still needs fresh target features each round</t>
+          <t>conv sees only the previous position and selector scores only adjacent pairs, so longer-range in-block dependencies stay independent; still needs fresh target features each round; drafter retrained per target</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>adds left-to-right information inside the block at small cost</t>
+          <t>adds left-to-right info inside the block for ~1.3% extra latency; selector picks a coherent path instead of per-position argmax</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) DFlash-size drafter plus conv and codebook params</t>
+          <t>2B drafter for Qwen3.8-27B (HF card); conv +16.5M params (3%), selector +2.0M; plus drafter KV (est.)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>lossless (assumed, standard verify)</t>
+          <t>lossless (rejection sampling, T=1)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>T=1 thinking: Qwen3.5-4B mean 5.97 vs DFlash 4.92; Qwen3.8-27B 4.80 (GSM8K 5.46, MT-Bench 4.10) vs MTP 4.28; Muse Glimmer 5.70 vs DFlash 4.44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>Qwen3.8-27B 2.7-3.4x bs1, GSM8K 236.1 tok/s 3.43x (1x H200, SGLang FA3, c=1, T=1, block 8); Muse Glimmer 3.1-4.6x (block 16)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>README lists Llama-3.1-8B as supported; no numbers found</t>
+          <t>none</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>GSM8K, MATH-500, HumanEval, MBPP, MT-Bench</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/z-lab/dflash</t>
+          <t>https://github.com/z-lab/dflash; HF incoai/Qwen3.8-27B-DFlash2, incoai/Muse-Glimmer-30B-DFlash2; SGLang, vLLM, llama.cpp, Ollama</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14837,12 +14841,12 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B MATH-500 tau 10.73 vs DFlash 7.79 (T=0) (ours: DDTree-128 tau 8.1, Qwen3-8B, A100)</t>
+          <t>Qwen3-8B MATH-500 tau 10.73 vs DFlash 7.79 (T=0), 9.54 vs 6.46 (T=1); Qwen3-4B 10.71 (ours: DDTree-128 tau 8.1, Qwen3-8B, A100)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B MATH-500 7.52x vs DFlash 5.56x (H200, bs1, T=0, HF/SDPA; budget picked per cell) (ours: DDTree-128 HF 5.90x, A100)</t>
+          <t>Qwen3-8B MATH-500 7.52x vs DFlash 5.56x T=0, 6.59x vs 4.56x T=1 (H200, HF/SDPA, budget picked per cell from 16-1024) (ours: DDTree-128 HF 5.90x, A100)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -14862,7 +14866,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14903,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>surrogate is a product of marginals, ignores dependencies; budget controller needs hardware-calibrated latency profiles; inherits DFlash block cap and fresh-feature dependency</t>
+          <t>surrogate is a product of marginals, ignores dependencies; budget controller needs per-(GPU, target) latency calibration and assumes bs1 cost profile; inherits DFlash block cap and fresh-feature dependency</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -14909,7 +14913,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>no extra params beyond DFlash; tree verify tokens per round; controller overhead negligible</t>
+          <t>no extra params beyond DFlash; tree verify tokens per round; controller overhead negligible (heap ops)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14919,17 +14923,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B tau 8.48 (T=0, A100); range 4.64-10.60</t>
+          <t>T=0 A100 avg tau: Qwen3-8B 8.48 (EAGLE-3 2.32), Qwen3-4B 8.56; range 4.64 (MT-Bench) to 10.60 (MATH500)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 6.61x over AR, DFlash 4.56x (A100, bs1, T=0); avg 1.39x over DFlash, 2.45x over EAGLE-3</t>
+          <t>T=0, A100, bs1: Qwen3-8B 6.61x avg (EAGLE-3 2.70x; DFlash GSM8K 4.56x); Qwen3-4B 6.93x; claims 1.39x over DFlash, 2.45x over EAGLE-3; also H100, RTX PRO 6000, A6000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-8B-Instruct: 4.46x, tau 6.00 vs DFlash 2.53x (A100, T=0)</t>
+          <t>Llama-3.1-8B-Instruct (DFlash block 10) evaluated on four GPUs; numbers only in Fig. 4, not extracted (earlier 4.46x/tau 6.00 unconfirmed)</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14939,12 +14943,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/kaist-ai-osi-lab/BASTION</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -15001,12 +15005,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>~3.1-10.4 by dataset (Qwen3-4B/8B, T=0); Qwen3-4B MATH-500 10.37 vs DDTree-oracle 10.35</t>
+          <t>T=0: Qwen3-4B MATH-500 tau 10.37 vs DDTree-oracle 10.35, DFlash 7.71; Qwen3-8B DFlash 7.91; ~8.9-10.4 on math/code sets</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-4B MATH-500 4.53 ms/tok (= DDTree oracle) vs DFlash 5.93 ms/tok (A800, T=0)</t>
+          <t>Qwen3-4B MATH-500 4.53 ms/tok (= DDTree-oracle, mean budget 221 vs oracle 256) vs DFlash 5.93, AR 30.65; Qwen3-8B 4.60 vs DFlash 5.83, AR 30.95 (A800, T=0)</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -15021,12 +15025,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/ZhangShuai1230/CaDDTree</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -15053,7 +15057,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>arXiv (AAAI template, unconfirmed)</t>
+          <t>arXiv (AAAI template)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -15073,22 +15077,22 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) small (two linear projections + depth embeddings) on top of DFlash</t>
+          <t>not reported; (est.) small (two linear projections + depth embeddings over frozen target embeddings) on top of DFlash; scorer 0.3 ms/round</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>lossless</t>
+          <t>lossless (standard target verification; not stated explicitly)</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B GSM8K MAT 8.06 vs DDTree 8.18, DFlash 5.82</t>
+          <t>Qwen3-8B MAT: GSM8K 8.06 vs DDTree 8.18, DFlash 5.82; Math500 9.36 vs 9.38, 7.02; Alpaca 4.26 vs 4.46, 2.83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2.13-6.36x over AR; Qwen3-8B up to 6.17x (A100-80GB, bs1)</t>
+          <t>2.13-6.36x over AR (A100-80GB, bs1, T not stated); Qwen3-8B Math500 6.17x vs DDTree 4.93x, DFlash 4.84x; Qwen3-4B 6.36x; Qwen3-Coder-30B 4.74x</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -15103,12 +15107,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>none found</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -15145,7 +15149,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>GRU runs sequentially over block positions, so a sequential step grows with block length; correction only helps when early positions are accepted; inherits fresh-feature dependency</t>
+          <t>Domino head updates its causal state token by token, so a sequential step grows with block length (1.20 ms/round after Triton+CUDA graphs); correction only pays off once early positions are accepted; inherits fresh-feature dependency</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -15155,7 +15159,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>+56M params (+5.3%) on DFlash drafter (GRU 1024-d, rank 256)</t>
+          <t>+56M params (+5.3%) on DFlash drafter (GRU 1024-d, rank-256 correction); no extra KV reported</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -15165,12 +15169,12 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B tau 7.08 vs DFlash 6.11 (T=0)</t>
+          <t>Qwen3-8B tau 7.17 vs DFlash 6.06 (T=0), 5.91 vs 5.18 (T=1); Qwen3-4B 7.08 vs 6.06 (T=0), 6.00 vs 5.33 (T=1)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 5.49x vs DFlash 4.70x (A100, T=0, HF); up to 5.8x throughput in SGLang</t>
+          <t>Qwen3-8B 5.49x vs DFlash 4.66x (T=0), 4.46x vs 3.96x (T=1) (A100-80GB, Transformers); SGLang Qwen3-8B GSM8K 5.1x at c=2, 3.0x at c=16; up to 5.8x</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -15190,7 +15194,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15231,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>only first-order conditioning (previous token); large trees conflict with production attention kernels (dense SDPA mask); inherits block cap</t>
+          <t>only first-order conditioning (previous token); trained teacher-forced, so conditioning on its own drafted tokens at inference gives exposure bias; large trees conflict with production attention kernels; inherits block cap</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -15247,12 +15251,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B B=64: 6.73 vs DDTree 6.15, DFlash 4.71 (T=0); 5.95 vs 5.39 (T=1)</t>
+          <t>Qwen3-8B B=64 T=1: 7.62 vs DDTree 6.76; T=0 B=64 ~8.84 vs DDTree ~7.8 (table parse ambiguous); +12.4% mean tau over DDTree</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>+9.1% over DDTree at B=64 (GH200, bs1, SDPA)</t>
+          <t>Qwen3-8B B=64 T=1: 5.50x vs DDTree 5.04x; +9.1% over DDTree at B=64 (GH200, bs1, PyTorch SDPA, bf16)</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -15262,7 +15266,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>MATH-500, GSM8K, HumanEval, MBPP, MT-Bench</t>
+          <t>MATH-500, GSM8K, HumanEval, MBPP, MT-Bench; targets Qwen3-4B/8B, Qwen3-Coder-30B-A3B</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -15309,7 +15313,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>two drafters run per round (second waits on the first); verify width grows with K branches; extra stages give diminishing returns (third stage -4% speed)</t>
+          <t>two drafters run per round (VP-drafter waits on drafter-1 confidences); verify width grows with K branches; more stages do not pay off (3rd stage: tau 7.62-&gt;8.24 but 5.35x-&gt;5.13x)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -15319,7 +15323,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) two DFlash-size drafters (~2x drafter weights and draft KV)</t>
+          <t>not reported; VP-drafter shares DFlash architecture, so ~2x drafter weights and draft KV (est.)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15329,12 +15333,12 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 7.05 vs DFlash 5.31 (T=0); 5.45 vs 4.33 (T=1)</t>
+          <t>Qwen3-8B 7.05 vs DFlash 5.31 (T=0), 5.45 vs 4.33 (T=1); GPT-OSS-20B 8.02 vs 4.13 (T=0), 2.35 vs 1.99 (T=1); gamma 16, K=4</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 4.98x vs 4.16x (T=0), 4.01x vs 3.43x (T=1); GPT-OSS-20B 6.15x vs 3.53x (H200, HF)</t>
+          <t>Qwen3-8B 4.98x vs 4.16x (T=0), 4.01x vs 3.43x (T=1); GPT-OSS-20B 6.15x vs 3.53x (T=0), 1.84x vs 1.71x (T=1) (H200, HF Transformers, FA2)</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -15354,7 +15358,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -15391,7 +15395,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>not extracted (abstract only); (likely) tree verify cost grows with branches x batch</t>
+          <t>draft head is a 5-layer decoder with its own KV fed by fused target features, so it is trained per target and needs fresh features each round; 256-node tree verify cost grows with batch, gains shrink at large batch</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -15401,7 +15405,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>not reported; (est.) ~1B draft head (5 layers, 4096 hidden, 12288 MLP for Qwen3-8B) + its KV cache</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15411,12 +15415,12 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>Qwen3-8B budget 256: MATH-500 10.76 (T=0), 9.01 (T=1); MT-Bench 5.94 (T=0); Qwen3-30B-A3B MATH-500 10.28 vs DDTree 9.71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>up to 9.64x MATH-500, 4.58x chat (H100, Qwen3 dense and MoE; bs/T not extracted)</t>
+          <t>Qwen3-8B budget 256 T=0: MATH-500 9.64x (DDTree 8.78x), MT-Bench 4.58x (H100); vLLM MATH-500 budget 128: 4.33x bs1, 3.26x bs8, 2.80x bs16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -15426,7 +15430,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>MATH-500, code, chat (names not extracted)</t>
+          <t>GSM8K, MATH-500, AIME25, HumanEval, MBPP, LiveCodeBench, MT-Bench</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -15436,7 +15440,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -15473,7 +15477,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>sequential module runs once per draft position; scheduler depends on throughput profiling; drafter KV over full prefix grows with context (~2.5 GiB at 128K, derived from LongSpark's 406x)</t>
+          <t>sequential head samples left to right per position (+0.2-1.3% round latency); fixed upfront gamma-token draft cost is wasted on low-acceptance queries; drafter KV over full prefix grows with context (2.5 GiB at 128K per LongSpark)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -15483,7 +15487,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>not reported; DFlash backbone + rank-256 head + linear confidence head; drafter state ~2.5 GiB at 128K (est.)</t>
+          <t>not reported; 5-layer DFlash-style backbone + rank-256 Markov/RNN head + linear confidence head; drafter state 2.5 GiB at 128K (LongSpark measurement)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15493,12 +15497,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>tau +16.3/18.4/18.3% vs DFlash on Qwen3-4B/8B/14B (absolute not extracted)</t>
+          <t>Qwen3-8B macro tau 4.87 vs DFlash 4.12, EAGLE-3 3.91 (T=1); +16.3/18.4/18.3% vs DFlash on Qwen3-4B/8B/14B</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek-V4 production: 60-85% per-user speedup at matched throughput</t>
+          <t>DeepSeek-V4-Flash 60-85%, V4-Pro 57-78% higher per-user speed vs MTP-1 at matched throughput (production); Qwen3 wall-clock not extracted</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -15508,7 +15512,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>math, code, chat (names not extracted)</t>
+          <t>GSM8K, MATH500, AIME25, MBPP, HumanEval, LiveCodeBench, MT-Bench, Alpaca, Arena-Hard</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -15555,7 +15559,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Jacobi iterations add K refiner passes to every round; refiner conditions on drafter candidates, so it cannot recover tokens outside them</t>
+          <t>Jacobi refinement adds K=4-7 batched refiner passes every round (K tuned per benchmark); refiner reranks drafter candidates, so it cannot recover tokens outside them</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -15565,7 +15569,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>not reported; (est.) small, rank-256 refiner on DFlash</t>
+          <t>not reported; rank-256 refiner (~16x lighter than full-width) on block-16 DFlash</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15575,12 +15579,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>+18-56% vs DFlash at T=0, +19-58% at T=1 (Qwen3-8B)</t>
+          <t>Qwen3-8B avg tau 8.02 (T=0), 6.97 (T=1) (README); +18-56% (T=0), +19-58% (T=1) vs DFlash</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>~1.3x (up to 1.7x) over DFlash T=0, ~1.46x T=1 (Qwen3-8B, H200)</t>
+          <t>6.2x (T=0), 5.3x (T=1) over AR; ~1.29x / 1.46x over DFlash, up to 1.7x (Qwen3-8B, H200, bs1, PyTorch, 2048 tokens)</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -15590,7 +15594,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7 math, code and chat benchmarks (not enumerated)</t>
+          <t>GSM8K, MATH-500, AIME25, HumanEval, MBPP, LiveCodeBench, MT-Bench</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -15637,7 +15641,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>only K=4 latent components, so dependence is coarse; trained with a biased surrogate objective and greedy-branch proposals that do not match stochastic inference</t>
+          <t>latent category sampled once per block from only K=4 components, so dependence is coarse; trained with a biased surrogate objective and proposals that do not match stochastic inference</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -15657,7 +15661,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>&gt;12% macro tau gain over DFlash, Qwen3-8B high-entropy (T 0.7-1.5, top-p 0.8/0.95)</t>
+          <t>&gt;12% macro tau gain over DFlash, Qwen3-8B high-entropy (T/top-p 0.7/0.8, 1.0/0.95, 1.5/0.95); absolute values not extracted</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -15677,7 +15681,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>none found</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -15719,7 +15723,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>one correction-head pass per tree depth, so sequential steps grow with depth; tree verify cost grows with nodes x batch</t>
+          <t>one correction-head pass per tree depth, so sequential steps grow with depth; fixed-width depth-wise schedule only approximates best-first search; tree verify cost grows with nodes x batch</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -15729,7 +15733,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>not reported; DFlash drafter + AR correction heads</t>
+          <t>not reported; DFlash drafter + pretrained AR correction module (Domino/DSpark-style)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15739,12 +15743,12 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>up to 12.97; Qwen3-8B avg 9.81 (T=0, extractor, check)</t>
+          <t>Qwen3-8B T=0 avg 9.81 vs DFlash 6.09, DDTree 7.59, Domino 7.11; max 12.97 (GSM8K)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>up to 9.73x; Qwen3-8B avg 6.99x (T=0; GPU not given)</t>
+          <t>Qwen3-8B T=0 avg 6.99x vs DFlash 4.43x, DDTree 5.63x, Domino 5.19x; up to 9.73x (GSM8K) (GPU/batch not extracted)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -15759,7 +15763,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/VILA-Lab/DARTree</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -15791,7 +15795,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>arXiv; COLM'26 workshop (per README)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -15821,12 +15825,12 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>DFlash baseline tau 7.09 at c=1 (Qwen3-8B); AdaFlash not extracted</t>
+          <t>AdaFlash not extracted; DFlash baseline tau 7.09-7.11 at c=1-128 (Qwen3-8B)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>up to 5.3x over AR; +66% throughput over prior SOTA at c=128 (SGLang); DFlash 0.90x at c=128</t>
+          <t>up to ~5.3x over AR; up to ~66% higher avg throughput than prior SOTA at high concurrency (SGLang); DFlash drops 4.38x (c=1) to 0.90x (c=128) on Qwen3-8B</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -15836,12 +15840,12 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>MathQA, GSM8K, OpenCodeInstruct, CodeAlpaca, ShareGPT, Blend, 2 long reasoning sets</t>
+          <t>MathQA, GSM8K, OpenCodeInstruct, CodeAlpaca, ShareGPT, Blend (+2, 8 total); targets Qwen3-8B, Qwen3-Coder-30B-A3B + 1</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/ZinYY/AdaFlash</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -15883,7 +15887,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>block fixed at 16 (accepted length capped); still needs fresh target features each round; training mismatch when combined with Domino</t>
+          <t>relay must be trained on its own rejected rollouts (teacher-forced relay training drops tau to 2.22 with Domino); block fixed at 16; still needs fresh target features each round</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -15893,7 +15897,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>not reported; small MLP relay on DFlash</t>
+          <t>not reported; small MLP relay on DFlash (0.51 ms, 1.2% latency)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15903,12 +15907,12 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 4.15 vs DFlash 3.66 (T=0), 3.45 vs 3.10 (T=1)</t>
+          <t>Qwen3-8B 4.15 vs DFlash 3.66 (T=0), 3.45 vs 3.10 (T=1); Qwen3-4B 4.20 vs 3.71 (T=0); with Domino 4.50 vs 4.02 (Qwen3-1.7B)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2.65x at c=1 down to 1.35x at c=32 (Qwen3-8B, SGLang, A800)</t>
+          <t>Qwen3-8B GSM8K: 3.08x vs DFlash 2.83x at c=1, 1.89x vs 1.71x at c=16, 1.35x vs 1.16x at c=32 (A800, SGLang)</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -15923,12 +15927,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>not found</t>
+          <t>https://github.com/pekpuch/dflow</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -15975,7 +15979,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>no new params (fine-tuned DSpark checkpoint); extra drafting GPU; ~8x per-round draft activations (est.)</t>
+          <t>no new params (backbone fine-tuned from DSpark ckpt); one dedicated drafting GPU; 8 anchors per round (d=7) so ~8x draft activations (est.)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15985,12 +15989,12 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>not extracted (+30.7% tau from multi-anchor fine-tuning)</t>
+          <t>not extracted (backbone fine-tuning raises avg tau +30.7%)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3.21x Qwen3-8B, 3.52x 14B; +11.1%/5.1% vs DSpark (H800, bs1-16, greedy)</t>
+          <t>avg 3.21x Qwen3-8B, 3.52x Qwen3-14B, max 4.53x; +11.1%/5.1% vs DSpark (H800, bs1-16, greedy)</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -16057,7 +16061,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>drafter state 6.3 MiB at 128K (406x smaller than DSpark); one extra drafter GPU</t>
+          <t>drafter state 6.3 MiB at 128K vs DSpark 2.5 GiB (406x smaller); one dedicated drafter GPU; params not reported</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16072,7 +16076,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1.88-2.13x over AR at 1K-128K; 128K TPOT 74.3 vs 97.2 ms DSpark; +6-12% vs DSpark at c=128</t>
+          <t>avg 1.88x/1.99x/2.13x over AR (Qwen3-4B/8B/14B); 128K TPOT 74.3 vs DSpark 97.2 ms; +12.0/7.8/6.0% vs DSpark at c=128 (target TP4 + 1 drafter GPU, SGLang)</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -16139,7 +16143,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>not reported; separate small drafter (PARD-style, size not extracted) plus its KV</t>
+          <t>not reported; separate small AR draft model (sizes not named) plus its KV</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16149,17 +16153,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 6.98; LLaMA3.1-8B 9.19 (T=0, K=16)</t>
+          <t>Qwen3-8B avg 6.98 (DFlash 5.58); LLaMA3.1-8B avg 6.95 (T=0, K=16, target-dependent)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Qwen3-8B 5.81x vs DFlash 4.61x, PARD 4.39x, EAGLE-3 1.93x (A100-40GB, vLLM, T=0)</t>
+          <t>Qwen3-8B avg 5.81x vs DFlash 4.61x, PARD 4.39x, EAGLE-3 1.93x (A100-40GB, vLLM, T=0); target-independent 4.82x/4.79x/4.68x on Qwen3-8B/14B/32B</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>LLaMA3.1-8B 6.94x / tau 9.19 (vLLM, T=0); notes also cite 5.19x (conflict, check table)</t>
+          <t>LLaMA3.1-8B avg 5.19x / tau 6.95 vs PARD 4.00x, EAGLE-3 2.76x; 6.94x / tau 9.19 is HumanEval only (abstract 'up to') (vLLM, A100-40GB, T=0, K=16)</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16174,7 +16178,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16225,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>LoRA adapter only; reuses target weights (draft pass costs a full forward)</t>
+          <t>LoRA r=16, 10.1M params (1.67% of 0.6B); reuses target weights, draft pass is a full forward (50.3 ms vs verify 50.6 ms)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16231,12 +16235,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>tau 2.88 (Qwen3-0.6B, T=0)</t>
+          <t>2.88 vs FastMTP 1.51 (Qwen3-0.6B, T=0, D=16)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>34.05 tok/s vs FastMTP 188.01 tok/s (Qwen3-0.6B, bf16, T=0, 256 tokens)</t>
+          <t>34.05 tok/s vs FastMTP 188.01, greedy AR 431.36 (slower than AR) (Qwen3-0.6B, SGLang, T=0, 256 tokens)</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -16246,17 +16250,17 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>TULU-3 (training); eval set not extracted</t>
+          <t>TULU-3 50k (training); eval prompt set not named</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none found</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16418,22 +16422,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>separate Transformer-base-size drafter; paper reports ~245-555 MB extra at test time</t>
+          <t>Spec-Drafter (12+2 layers) weights; extra peak GPU memory ~245-288 MB (WMT14 En-De, P100, bs 1-32)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>lossy, no drop measured: BLEU 28.93 vs 28.73 AR greedy (WMT14 En-De); ROUGE +0.03 (CNN/DM, BART-base)</t>
+          <t>lossy by rule, no measured drop: BLEU 28.93 vs 28.89 AR (WMT14 En-De, Transformer-base); En-Ro 35.45 vs 34.96; CNN/DM ROUGE-1 43.11 vs 43.08 (BART-base)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>8.23 tokens/iter (k=25) vs 2.32 for blockwise decoding</t>
+          <t>8.23 tokens/iter (k=25, WMT14 En-De, greedy)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>5.1-5.5x (Transformer-base, P100, bs1); 3.0-3.3x (12+2 target); 5.1x (BART-base)</t>
+          <t>Transformer-base: 5.1x En-De, 5.5x De-En, 4.6x En-Ro, 4.8x Ro-En; 12+2 target: 2.5-3.3x; BART-base CNN/DM 5.1x (P100, bs1, fairseq)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -16453,7 +16457,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16494,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>lossy: tokens the large model would not pick are kept; fallback and rollback thresholds must be tuned; small and large models must be aligned (README advises fine-tuning the small model)</t>
+          <t>lossy: tokens the large model would not pick are kept; fallback/rollback thresholds tuned per task; best results need the small model fine-tuned on large-model outputs (alignment); rollback discards small-model work</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -16500,12 +16504,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>not reported; small model (T5/mT5-small class) + its KV (est.)</t>
+          <t>small model (paper: 25M vs 409M/402M large, ~1/20) + its KV; ~5x fewer memory ops than vanilla</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>lossy: 'minimal' quality degradation at up to 2.12x; exact BLEU/ROUGE drop not seen</t>
+          <t>lossy: matched-quality IWSLT 40.24 vs 40.32 BLEU, WMT 31.26 vs 31.38, XSum 35.05 vs 35.08 R-L, CNN/DM 41.52 vs 41.54; max-speed setting ~1 pt drop (CNN/DM 40.96)</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -16515,12 +16519,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>up to 2.12x (T4 GPU)</t>
+          <t>aligned, matched quality: 1.62x IWSLT, 1.47x WMT, 1.50x XSum, 1.85x CNN/DM; ~1 pt drop: up to 2.12x (T4, bs1, greedy); unaligned 1.43-1.71x</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>none (T5/mT5 encoder-decoders)</t>
+          <t>none (mT5/T5 encoder-decoders only)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -16535,7 +16539,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16582,32 +16586,32 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Medusa heads: ResBlock + own vocab projection each, ~0.15B per head on 7B, ~0.7B for 5 heads (est.); no extra KV</t>
+          <t>per head W1 (d x d) + W2 (d x V): ~0.15B/head on 7B, ~0.74B for 5 heads (est., not reported); no extra KV</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>lossy at T&gt;0: MT-Bench quality roughly unchanged (unv.)</t>
+          <t>lossy at T&gt;0: Fig. 5 (Medusa-2 Vicuna-7B, T=0.7, MT-Bench writing/roleplay) shows GPT-4 score similar to random sampling; exact drop not tabulated</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>not reported for typical acceptance alone</t>
+          <t>acceleration rate (Medusa-2): 3.47 Vicuna-7B, 3.51 Vicuna-13B, 3.01 Vicuna-33B, 3.14 Zephyr-7B; typical-acceptance alone only in Fig. 5</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>~2x wall-time (Vicuna-7B/13B/33B, A100, bs1, MT-Bench, Medusa-1); +10% over greedy on creative tasks with typical acceptance; Medusa-2 2.3-3.6x (unv.)</t>
+          <t>Medusa-1 2.18x (Vicuna-7B), 2.33x (13B); Medusa-2 2.83x (7B/13B), 2.35x (33B), 2.66x (Zephyr-7B) (A100, bs1, MT-Bench); typical acceptance: higher accel. than RS at T=0.7</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B/13B/33B ~2x (Medusa-1); Medusa-2 2.3-3.6x (unv.)</t>
+          <t>Vicuna-7B 2.18x/2.83x, Vicuna-13B 2.33x/2.83x (Medusa-1/-2), Vicuna-33B 2.35x (Medusa-2); MT-Bench score change -0.14 to +0.05</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench</t>
+          <t>MT-Bench, AlpacaEval; training on ShareGPT/UltraChat</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -16617,7 +16621,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16664,42 +16668,42 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>none beyond the drafter (est.); per-step sort over the vocabulary</t>
+          <t>none beyond the drafter (est.); O(n) data structure, O(sort(n)) build per step (n = vocab or top-k)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>lossy with bounded per-token divergence; measured drop not reported in material seen</t>
+          <t>lossy with bounded per-token f-divergence; theory paper, no measured drop (toy simulation only); claims proxy can beat target</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>not reported (theory paper)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>not reported (full text not read)</t>
+          <t>not reported (theory paper, no benchmarks)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>none seen</t>
+          <t>none (no experiments)</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>not reported</t>
+          <t>none (toy simulation only)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/vivien000/mentored_decoding</t>
+          <t>none found in paper</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16736,7 +16740,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>lossy: no guarantee of target distribution; judge needs hand-labeled error annotations and new domains need new labels (OOD drop); needs a strong drafter (Medusa/EAGLE heads unsuitable) and a large target</t>
+          <t>lossy: no guarantee of target distribution; judge trained on ~500 hand-annotated examples and OOD domains drop; needs a long-drafting drafter (Medusa/EAGLE-2 draft &lt;=6 tokens) and a large target</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -16746,12 +16750,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>judge head 16,384 params (405B) / 8,192 (70B), negligible; plus separate Llama-3.1-8B drafter + its KV</t>
+          <t>judge head ~16.4k params (linear on target last-layer embeddings), negligible; plus separate Llama-3.1-8B drafter + its KV</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>lossy: GSM8K ~90% and HumanEval 86.6% ~ target 405B; OOD (code removed from judge data) HumanEval 86.6% -&gt; 80.4%</t>
+          <t>lossy: target accuracy 'almost exactly preserved' (GSM8K ~91%, HumanEval 86.6% on 405B, figure); OOD (no code in judge data) HumanEval 86.6% -&gt; 80.4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -16761,7 +16765,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8B/405B: 9.7x HF, 3.9x gpt-fast, 129.3 tok/s; 8B/70B: 2x HF, 3x gpt-fast, 141.8 tok/s (H100, 8-bit, bs1)</t>
+          <t>8B/405B: 9.7x HF, 3.9x gpt-fast, 129.3 tok/s (8xH100); 8B/70B: 2x HF, 3x gpt-fast, 141.8 tok/s (2xH100); gpt-fast 8-bit, bs1</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -16781,7 +16785,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16818,7 +16822,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>lossy: target distribution not preserved; labels need verifiable tasks (final-answer change) and classifier degrades OOD, so mining is redone per domain; offline mining needs many sequential target passes</t>
+          <t>lossy: target distribution not preserved; labels need verifiable tasks and classifier is task-specific (GSM8K&lt;-&gt;LCB transfer much worse); mining needs many sequential target passes (~706 s/sample for 8B/70B)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -16828,27 +16832,27 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>logistic regression on concatenated hidden states (~6k params, est.) + Llama-3.2-1B drafter + KV</t>
+          <t>logistic regression on concat draft+target hidden states (6144-d for 1B/8B, ~6k params, est.) + Llama drafter + KV</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>lossy: ≤1% accuracy drop on GSM8K at ~1.5x more accepted tokens; ~1% drop on LiveCodeBench at ~2x</t>
+          <t>lossy: GSM8K 8B/70B 92.0 -&gt; 89.9% at 1.49x, 91.9% at 1.11x; 1B/8B 83.1 -&gt; 80.2% at 1.14x; LiveCodeBench ~2% Pass@1 drop at &gt;22 tokens/cycle</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15+ (GSM8K), 20+ (LiveCodeBench) per cycle, window W=64 (Llama 1B/8B, greedy on GSM8K)</t>
+          <t>&gt;40 tokens/forward (8B/70B, GSM8K), &gt;22 (8B/70B, LiveCodeBench); 1B/8B ~1.5x more than SD at &lt;=1% drop (greedy)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>~2x over standard SD (GSM8K/LiveCodeBench); hardware and batch not specified</t>
+          <t>vs SD in vLLM (A100-80GB, bs1, bf16): 8B/70B GSM8K 72.3 -&gt; 107.4 tok/s (1.49x); 1B/8B 147.7 -&gt; 169.2 tok/s (1.14x)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.2-1B -&gt; Llama-3.1-8B: up to 1.5x more accepted tokens at ≤1% GSM8K drop</t>
+          <t>Llama-3.1-8B -&gt; 70B: 1.49x over SD at -2.1 pts GSM8K; Llama-3.2-1B -&gt; 3.1-8B: 1.14x at -2.9 pts</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -16863,7 +16867,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16900,7 +16904,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>lossy: target distribution not preserved; label threshold τ calibrated on annotated math examples; label creation needs pre-generated target responses and extra scoring passes</t>
+          <t>lossy: target distribution not preserved; label threshold calibrated on GSM8K (AutoJudge labels); labeling needs target responses plus suffix rescoring passes (N=20 tokens) per mismatch</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -16910,27 +16914,27 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>logistic regression on target hidden states (~4k params, est.) + 1B/0.5B drafter + KV</t>
+          <t>logistic regression on target hidden states (~4k params for 8B, est.) + 1B/8B/0.5B drafter + KV; judge 0.26% of verify time</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>lossy: -1.0% average task accuracy (vs -2.7% for AutoJudge)</t>
+          <t>lossy (Llama 8B/1B, T=0): GSM8K 80.5 vs 80.7 SD, MMLU 62.7 vs 65.0, MATH-500 42.2 vs 45.4, CNN/DM 63.9 vs 64.6, LCB 10.0 vs 8.6</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>+2.06 accepted tokens/cycle over standard SD (vs +1.96 AutoJudge)</t>
+          <t>Llama 8B/1B: GSM8K 11.29 vs 9.14 SD, MMLU 6.38 vs 4.36, CNN/DM 6.05 vs 4.35, MATH-500 12.78 vs 9.98</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>not reported as wall-clock in material seen (V100, T=0)</t>
+          <t>A100, T=0: 8B/1B GSM8K 137.4 vs 111.2 tok/s SD (+23.5%), MMLU 89.5 vs 61.1 (+46.3%); 70B/8B (4xA100) +22.4% GSM8K, +22.7% MMLU</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.2-1B -&gt; Llama-3.1-8B (included in averages above)</t>
+          <t>Llama-3.1-8B/3.2-1B and Llama-3.1-70B/8B: +22-46% tok/s over SD (above)</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -16945,7 +16949,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -16992,22 +16996,22 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>none beyond the drafter (Llama-3.1-8B + KV for 70B target)</t>
+          <t>none beyond the drafter (Llama-3.1-8B, Gemma2-2B or Qwen2.5-7B + KV)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>lossy: ~2% absolute accuracy drop at &gt;5 tok/s over SD (GSM8K, CSQA); ~0% on HumanEval</t>
+          <t>lossy: Llama 8B/70B GSM8K 93.1 vs 95.1% SD at 22.0 tok/s; CSQA 82.1 vs 84.1; HumanEval 77.4 = SD; low threshold matches SD accuracy</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>CSQA 1.96 -&gt; 3.32 at SD-matched accuracy (Llama 8B/70B)</t>
+          <t>Llama 8B/70B: GSM8K 9.7 SD -&gt; 11.8-13.5; CSQA 1.96 -&gt; 3.32-8.14; HumanEval 7.6 -&gt; 8.5-8.9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Llama 8B/70B, 2xA100, bs1: GSM8K 16.8 (SD) -&gt; 19.5 (matched acc.) / 22.0 tok/s; HumanEval 20.5 -&gt; 22.3 / 23.6</t>
+          <t>Llama 8B/70B, 2xA100, bs1: GSM8K 16.8 SD -&gt; 19.5-22.0 tok/s (AR 8.5); HumanEval 20.5 -&gt; 22.3-23.6; CSQA 13.5 -&gt; 14.4-19.5; Gemma2/Qwen2.5 on 2xA6000</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -17017,7 +17021,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>GSM8K, CSQA, HumanEval</t>
+          <t>GSM8K, CSQA, HumanEval, MMLU; pairs Llama-3.1 8B/70B, Gemma2 2B/27B, Qwen2.5 7B/32B</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -17027,7 +17031,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -17054,7 +17058,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>AISTATS 2026 or NeurIPS 2025 (conflict)</t>
+          <t>AISTATS 2026 (earlier NeurIPS 2025 Efficient Reasoning workshop)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -17074,32 +17078,32 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>small FFN weight network (size not reported) + Llama-3.2-1B drafter + KV</t>
+          <t>weight net: 1 FC layer + sigmoid on concat draft+target hidden states (params not reported, small vs drafter, est.) + 1B drafter + KV</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>lossy: 'comparable quality' (ROUGE, accuracy, perplexity); exact drop not seen</t>
+          <t>lossy, no drop seen (Llama 8B/1B, T=1): GSM8K 67% = AR; MBPP 53% = AR; CNN/DM R-2 12.11 vs 9.86 AR; XSum R-2 7.23 vs 7.03</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>not reported in material seen (figures only)</t>
+          <t>acceptance rate (N=5, T=1), Llama 8B/1B: GSM8K 72.6% vs 44.6% SD, CNN/DM 70.0 vs 21.6, XSum 70.5 vs 20.4, MBPP 85.0 vs 26.3</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>not reported in material seen (T=0, 128 tokens on CNN/DM)</t>
+          <t>wall-clock only as normalized time in figures (8xA100-40GB); no speedup numbers tabulated</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.2-1B -&gt; Llama-3.1-8B (main pair); numbers not seen</t>
+          <t>Llama-3.1-8B/3.2-1B: acceptance 70-85% vs 20-45% SD at AR-level quality (T=1, N=5)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>GSM8K, CNN/DM, XSum, MBPP</t>
+          <t>GSM8K, CNN/DM, XSum, MBPP; pairs Llama-3.1-8B/3.2-1B, Qwen3-8B/0.6B, Gemma-3-12B/4B</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -17109,7 +17113,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -17161,22 +17165,22 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>lossy: &gt;99% accuracy retention (GSM8K, HumanEval, MBPP)</t>
+          <t>lossy: &gt;99% accuracy recovery; e.g. GSM8K 94.69 vs 95.45% (Llama-3.1-70B)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>~11-12 (70B), ~15-18 (405B) vs 1-4 standard SD</t>
+          <t>tau 12.67 in-dist / 11.35 OOD (70B, T=0); 17.14 / 17.13 (405B) vs ~2-3 standard SD</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70B: in-dist 2.88x T=0 / 2.59x T=1, OOD 2.53x / 2.56x; 405B: 4.80x / 5.21x (MI355X, bs1); README avg 2.81x / 5.07x</t>
+          <t>T=0: 70B 2.88x in-dist / 2.53x OOD; 405B 5.34x / 4.80x; T=1: 70B 2.59x / 2.56x, 405B 5.31x / 5.21x (MI355X, 1 GPU 70B, 4 GPUs 405B, bs1)</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B 2.5-2.9x; Llama-3.1-405B 4.8-5.2x; OOD 1.62x over EAGLE-3 (Llama-3.3-70B)</t>
+          <t>Llama-3.1-70B 2.5-2.9x, tau ~11-13; Llama-3.1-405B 4.8-5.3x, tau ~17; OOD 1.62x over EAGLE-3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -17191,7 +17195,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17240,11 @@
           <t>single harness and taxonomy for lossy rules; names failure modes</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>EAGLE-3 draft head + its KV (est.); lossy rules themselves add no memory</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>truncation (SpecCascade) gap to true truncation sampling grows with difficulty: 0.38 pp (GSM8K) to 6.67 pp (AIME)</t>
@@ -17244,17 +17252,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>reported as block efficiency; numbers not seen</t>
+          <t>block efficiency in App. C; numbers not extracted</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>reported as decoding speed; numbers not seen</t>
+          <t>tokens/s in App. C; numbers not extracted (A100, bs1, T=0 per App. G)</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Llama-based models (versions not seen)</t>
+          <t>EAGLE-3 on Llama-3.1-8B-Instruct (plus Qwen) per App. G; numbers not extracted</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -17316,27 +17324,27 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>small model + its KV (T5-small 77M; Gemma 2B/9B for 27B)</t>
+          <t>small model + its KV (T5-small 77M for T5-large 800M / T5-XL 3B; Gemma 2B drafter for 9B/27B)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>lossy by design: matches large-model quality at 1.85x (WMT), 1.89x (CNN/DM), 1.18x (XSum); can exceed it</t>
+          <t>lossy by design: matches large-model quality at the speedups below; can exceed it</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>not reported in material seen</t>
+          <t>not reported (rejection rates only)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1.85x WMT, 1.89x CNN/DM, 1.18x XSum latency reduction at large-model quality (T5, T=1, γ=5, bs1)</t>
+          <t>at large-model quality, SpecCascade [Token]: small-&gt;large 1.85x WMT, 1.89x CNN/DM, 1.18x XSum; small-&gt;XL 2.50x, 1.89x, 1.40x (T5, T=1, gamma=5, bs1)</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>none (T5, Gemma)</t>
+          <t>none (T5, Gemma 2B/9B/27B)</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -17351,7 +17359,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -17403,7 +17411,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>lossy (gain): +1.1 avg accuracy vs target over 6 benchmarks; GPQA-Diamond 38.4 vs 32.8</t>
+          <t>lossy (gain): Qwen2.5-Math 1.5B/7B: avg 66.1 vs 65.3 target (6 tasks); GPQA up to 38.4 vs 32.8; 7B/72B: MATH500 88.0 vs 85.6</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -17413,17 +17421,17 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>up to 4.4x fewer FLOPs vs target-only; wall-clock not reported (A100, vLLM)</t>
+          <t>up to 4.4x fewer FLOPs vs target-only (7B/72B, MATH500); wall-clock not reported (A100, vLLM, T=0.7)</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-8B target with ~1B Llama draft tested; numbers not seen</t>
+          <t>Llama-3.2-1B/3.1-8B, PRM 7B: avg 41.9 vs 41.4 target, 41.1 SD (MATH500 50.4 vs 49.4, GSM8K 85.4 vs 83.9)</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MATH500, GSM8K, GPQA-Diamond, Olympiad-level math</t>
+          <t>MATH500, GSM8K, GaoKao-2023-En, OlympiadBench, GPQA-Diamond, MMLU-STEM</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -17433,7 +17441,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17493,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>lossy (gain, v1): +1.0 MATH500, +3.1 AIME, +9.9 GPQA vs QwQ-32B</t>
+          <t>lossy (gain): QwQ-32B +1.3-3.6 AIME, +4.0-9.0 MATH500, +0.4-1.7 GPQA; Skywork-OR1-32B +1.4-5.0 (pass@1, k=16)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -17495,12 +17503,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>v1: 2.5x MATH500, 1.9x AIME, 1.5x GPQA (QwQ-32B, 2xA6000, vLLM 0.8.2, T=0.6); +19.4-44.2% latency cut over SD alone</t>
+          <t>QwQ-32B: 2.5x MATH500, 1.5x AIME, 1.4x GPQA; Skywork-OR1-32B: 3.0x, 1.6x, 1.7x (2xA6000, vLLM 0.8.2, T=0.6); +SD: 19.4-58.0% lower latency than SD alone</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>R1-Distill-Llama-70B as base (§5.4); numbers not seen</t>
+          <t>R1-Distill-Llama-70B as base (App. A.1); numbers not extracted</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -17552,7 +17560,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>lossy vs large model: output mostly small-model text; cue words are model-family heuristics; both models must share a family/tokenizer</t>
+          <t>lossy vs large model: output mostly small-model text; cue words are hand-picked heuristics; each switch hands text across, so the other model must prefill the new tokens (est.)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -17567,22 +17575,22 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>lossy vs 32B (accuracy vs 32B alone not seen); small model gains: MATH500 83.2 -&gt; 89.4, GPQA 33.8 -&gt; 41.9</t>
+          <t>lossy vs 32B alone: MATH500 89.4 vs 93.8, GPQA 41.9 vs 61.6, AIME 32.2 vs 60.0, AMC23 80.0 vs 95.0 (1.5B+32B); vs 1.5B alone +5 to +8 pts</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>not applicable</t>
+          <t>not applicable (~18-21% of output tokens from the large model)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>est. 96.6 vs 32.2 tok/s for 32B alone (FLOP-based estimate, A100-class, not measured)</t>
+          <t>FLOP-based estimate, not measured: 96.6 vs 32.2 tok/s for 32B alone (MATH500, A100-class)</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>LLaMA3-8B small + Qwen-32B large: +3.4% accuracy, +44.4% est. speed vs small alone</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -17597,7 +17605,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17642,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>lossy: output is a draft CoT, not the target's; LoRA tuning of both models (math only); 'all wrong' detected only 52% of the time, wasted drafts when rejected</t>
+          <t>lossy: output is a draft CoT, not the target's; LoRA tuning of both models on GSM8K data; 'all drafts wrong' detected only 52% of the time, and rejected rounds waste 5 drafts</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -17649,7 +17657,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>lossy: 'near-target' accuracy, exact drop not seen; CollegeMath above target</t>
+          <t>lossy: Qwen-32B -0.4 to -1.0 pts (CollegeMath +0.4); Llama-70B -1.4 to -2.4 pts (GSM8K 86.8 vs 88.2, MATH 90.4 vs 92.0)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -17659,12 +17667,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2.26-2.92x (R1-Distill-Qwen-32B, A100-40GB); 1.26-1.96x (R1-Distill-Llama-70B, H800)</t>
+          <t>R1-Distill-Qwen 1.5B/32B: 1.90-2.92x (A100-40GB); R1-Distill-Llama 8B/70B: 1.26-1.96x (H800)</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>R1-Distill-Llama-8B -&gt; R1-Distill-Llama-70B: 1.26-1.96x</t>
+          <t>R1-Distill-Llama-8B -&gt; 70B: 1.26-1.96x at -1.4 to -2.4 pts</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -17679,7 +17687,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -17736,12 +17744,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>step acceptance 0.35-0.63</t>
+          <t>step acceptance 0.35-0.63 (R1-Distill), 0.30-0.53 (Qwen3)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>LR+SD 1.49-2.11x, LR alone 1.04-1.71x, n-gram SD 1.32-1.53x (32B targets, 8xH100, vLLM 0.8.3, T=0.6)</t>
+          <t>LR+SD 1.51-2.11x (R1-Distill-32B), 1.32-1.68x (Qwen3-32B); LR alone 1.04-1.71x; SD alone 1.25-1.53x (8xH100, vLLM 0.8.3, T=0.6)</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -17761,7 +17769,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17821,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>lossy (gain): +3.6% accuracy vs standard SD (target-only MATH500 83.0)</t>
+          <t>lossy (gain): Qwen2.5-Math 7B/1.5B MATH500 85.4 vs 83.0 target, GSM8K 95.8 vs 94.7; 'accuracy +3.6%' vs SD/RSD</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -17823,17 +17831,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>~11% lower latency vs standard SD (hardware not seen)</t>
+          <t>~11% lower latency vs RSD (A100, vLLM); per-method latency only in figure</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Llama-3 8B/1B: MATH500 51.6 vs 48.2 target, GSM8K 85.1 vs 83.9, Olympiad 17.2 vs 14.5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MATH500, GSM8K, GaoKao-2023-En, OlympiadBench</t>
+          <t>MATH500, GSM8K, GaoKao-2023-En, OlympiadBench; Qwen2.5-Math, Qwen2.5, Llama-3 pairs</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -17843,7 +17851,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18013,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>not reported; K=8 draft sequences x L=8 tokens of draft KV plus 64 verify positions (est.)</t>
+          <t>not reported; K=8 draft sequences x L=8 tokens of draft KV plus up to 64 verify positions in the target pass (est.)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -18015,12 +18023,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>block efficiency 4.0 vs 2.9 for SD (PaLM-2 Gecko/Bison, K=8, L=8, T=1)</t>
+          <t>block efficiency 4.0 vs 2.9 SD (K=8 vs 1, L=8) and 3.1 vs 2.4 (L=4) (PaLM-2 Gecko-&gt;Bison, LM1B, T=1); 3.27 vs 2.33 (6M/97M LM1B models)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2.13x vs AR, 1.37x vs SD (PaLM-2 Gecko-&gt;Bison, K=8, L=8, T=1; hardware not stated)</t>
+          <t>2.13x vs AR, 1.37x vs SD (K=8, L=8); 2.08x vs 1.67x SD at L=4 (PaLM-2 Gecko-&gt;Bison, T=1); hardware not stated</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -18030,7 +18038,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>LM1B (plus small FLAX LM1B ablations)</t>
+          <t>LM1B (1000 prompts, 3 seeds; plus 6M/97M LM1B transformers)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -18040,7 +18048,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18097,17 +18105,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>acceptance rate 90.7% greedy draft vs 89.9% optimal w/o replacement (OPT-125M/6.7B, Alpaca, T=0.7); existing verifiers 0.1-3.3 pts below optimum</t>
+          <t>single-step acceptance, Alpaca, T=0.7, w/o replacement: optimal 89.9% vs RRS 88.9%, greedy 90.7% (OPT-125M/6.7B); 76.5/75.7/78.4% (LLaMA-68M/7B); 71.5/70.9/72.6% (EAGLE/Vicuna-7B)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>1.17x (multi-step MT-Bench, T=0.1, 4 drafts x 3 steps; baseline per paper table, check); RTX A6000</t>
+          <t>multi-step MT-Bench Vicuna-7B+EAGLE, T=0.1: greedy draft 1.17x (4 drafts x 3 steps), 1.13x vs RRS 1.04x (2 x 4); RTX A6000; reference baseline of the x not stated in extract</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-68M/LLaMA-7B and Eagle-0.24B/Vicuna-7B pairs used; per-model numbers not extracted</t>
+          <t>LLaMA-68M/LLaMA-7B: optimal 73.0% w/ repl. (K-SEQ 71.9%, RRS 71.6%), 76.5% w/o repl.; EAGLE-0.24B/Vicuna-7B: 64.4% / 71.5%; Vicuna-7B multi-step up to 1.17x</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -18122,7 +18130,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18167,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>token-level selection only, no tree-wide joint acceptance; each draft needs its own draft pass/model; gain only at T&gt;0</t>
+          <t>token-level selection only, no tree-wide joint acceptance; practical scheme needs a truncated LP (s=5) and truncated alphabet (40 tokens), so it only approximates the optimum; gain only at T&gt;0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -18169,7 +18177,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>not reported; one extra draft sequence (and KV) per draft (est.)</t>
+          <t>not reported; K=2 draft sequences of 5 tokens (+ draft KV) from OPT-125M (est.)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -18179,22 +18187,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>not read (abstract: improved block efficiency over baselines)</t>
+          <t>not reported numerically (block efficiency in Fig. 3 plots only; OPT-125M-&gt;OPT-13B, K=2, 5 tokens/call, target T=1, top-p 0.95)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>not read (abstract: improved token rates over baselines)</t>
+          <t>token-rate % gain over SpecInfer and single-draft SD shown in plots only; 1x A100-80GB</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>not read</t>
+          <t>none (OPT-125M/OPT-13B only)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>not read</t>
+          <t>XSum, Databricks-Dolly-15k, WMT18</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -18204,7 +18212,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18241,7 +18249,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>solver costs up to ~100 ms/token, far above a 20-50 ms decode step; optimal only for i.i.d. drafts; truncation set can be too large, forcing early termination (small deviation from target)</t>
+          <t>solver runs per token (5-47 ms/token on Llama-3), comparable to a decode step; success rate falls to 15% at k=1000, n=2, forcing early termination/fallback; optimal only for i.i.d. drafts</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -18256,27 +18264,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>lossless in exact solve; truncated solve gives 'negligible deviation' from target</t>
+          <t>lossless in exact solve; early-terminated solve deviates at most 15*tau in L1 from target (tau=1e-3 setting)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>~90% per-token acceptance (Llama-3 70B/8B, Gemma-2 27B/2B, n&lt;=10, T=1); +1.03%/+0.47% acceptance vs other solvers at 100 ms budget</t>
+          <t>Llama-3 70B/8B: 90.04% vs 89.01% max-flow at 100 ms/token, 85.65% vs 83.94% at 10 ms; Gemma-2 27B/2B: 86.60% vs 85.83%; T not extracted</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>nearly 2x wall time in multi-step SpecTr setting; per-token overhead &lt;100 ms; hardware not extracted</t>
+          <t>solver 5.27-47.46 ms/token (Llama-3); ~2x wall-clock vs SpecTr baseline in multi-step setting (App. R); hardware in App. M not extracted</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Llama-3-70B target / Llama-3-8B draft: ~90% acceptance, +1.03% over other solvers under 100 ms/token</t>
+          <t>Llama-3-70B target / Llama-3-8B draft: 90.04% acceptance vs 89.01% max-flow solver (100 ms/token budget)</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40 random prompts per dataset (dataset names not extracted)</t>
+          <t>40 random prompts per dataset (names in App. M, not extracted)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -18343,12 +18351,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>+8.30% block efficiency avg (7.00-10.06%) vs token-wise (PaLM-2-S + XXS, gamma=8, sampling)</t>
+          <t>+8.30% block efficiency avg (7.00-10.06% across 8 datasets) vs token-wise (PaLM-2-S + PaLM-2-XXS, gamma=8, sampling)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>+6.49% wall-clock avg (5.36-8.14%) vs token-wise SD (PaLM-2-S, gamma=8); hardware not stated</t>
+          <t>+6.49% wall-clock avg (5.36-8.14%) vs token-wise SD (PaLM-2-S + XXS, gamma=8, T&gt;0); hardware not stated</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -18368,7 +18376,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18425,22 +18433,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>not reported numerically in extract (figures only)</t>
+          <t>not reported numerically (block efficiency in Figs. 4-5 only)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>RSD-S beats SD and SpecTr on block efficiency and token rate in most budgets (A100); exact values in figures</t>
+          <t>RSD-S beats SD and SpecTr on block efficiency, MBSU and token rate at fixed draft length (A100; values in figures only)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Llama 2 / Llama 2-Chat 7B,13B,70B targets: RSD-S strictly outperforms SD and SpecTr at fixed draft length (values in figures)</t>
+          <t>Llama 2 / Llama 2-Chat 7B, 13B, 70B targets (also OPT 13B/30B/66B): RSD-S strictly outperforms SD and SpecTr at fixed draft length (figures only)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>WMT18 De-En, XSum, Databricks-Dolly-15k</t>
+          <t>WMT18 De-En (T=0.3), XSum (T=0.3), Databricks-Dolly-15k (T=1, top-p 0.95)</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -18450,7 +18458,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18495,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>bottom-up traversal over the whole tree adds overhead that eats part of the gain; gain shrinks as T falls and is zero at T=0</t>
+          <t>bottom-up traversal over the whole tree adds overhead that eats part of the gain; gain shrinks as T falls (1.0% at T=0.2 vs 2.8% at T=1) and is zero at T=0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -18507,17 +18515,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>tau 4.09 vs 3.95 token-level (Llama3.1-8B / 3.2-1B, chain d5, MT, T=1); 2.59 vs 2.47 (Llama2-7B / 68M, binary tree, T=1)</t>
+          <t>tau 4.09 vs 3.95 token-level (Llama3.1-8B / 3.2-1B, chain d5); 4.76 vs 4.64 binary tree; 4.67 vs 4.53 EAGLE sparse tree; 2.59 vs 2.47 (Llama2-7B / 68M, binary d5)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58.5 tok/s sparse tree vs 34.5 AR (~1.7x) on Llama3.1-8B; +1.7-2.5% tok/s vs token-level (RTX A6000, bs1, T=1, PyTorch)</t>
+          <t>58.5 tok/s EAGLE sparse tree vs 57.3 token-level vs 34.5 AR (~1.7x) on Llama3.1-8B; +1.7-2.5% tok/s vs token-level; RTX A6000, bs1</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Llama3.1-8B: tau 4.09, 52.5-58.5 tok/s vs 34.5 AR; Llama2-7B: 72.5 tok/s vs 37.3 AR</t>
+          <t>Llama3.1-8B: tau 4.09-4.76, 52.5-58.5 tok/s vs 34.5 AR; Llama2-7B/68M: tau 2.16 chain, 2.59 binary (+4.7-5.5%), AR 37.3 tok/s</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -18532,7 +18540,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18589,32 +18597,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>tau 3.29 vs 3.06 RRSw (Vicuna-7B + EAGLE, binary d5, T=1); 2.95 vs 2.72 (Llama3.1-8B, T=1)</t>
+          <t>tau 3.29 vs 3.06 RRSw, 3.13 traversal (Vicuna-7B + EAGLE, binary 2x5, T=1); 2.95 vs 2.72 (Llama3.1-8B, T=1); equal to traversal at T=0.3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72.2 tok/s vs 35.9 AR (~2.0x), ~7% over RRSw (Vicuna-7B, RTX A6000, bs1, T=1)</t>
+          <t>72.2 tok/s vs 67.5 RRSw vs 35.9 AR (~2.0x) (Vicuna-7B + EAGLE, RTX A6000 48G, bs1, T=1)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B tau 3.29 (+7.5%); Llama3.1-8B tau 2.95 (+8.5%); also Vicuna-13B/33B, Llama2-7B+68M</t>
+          <t>Vicuna-7B tau 3.29 (+7.5%); Vicuna-13B 3.35, 45.3 tok/s (AR 22.3); Vicuna-33B 3.21, 21.4 tok/s (AR 9.2); Llama3.1-8B 2.95, 51.1 tok/s (AR 34.5); Llama2-7B+68M 2.65, 62.5 tok/s</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Spec-Bench (MT-Bench, WMT14 De-En, CNN/DM, Natural Questions, GSM8K, DPR)</t>
+          <t>Spec-Bench (6 domains, 80 samples each)</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>none found</t>
+          <t>none found (built on EAGLE repo)</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18649,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>ICLR 2026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -18651,7 +18659,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>no gain at T=0; with EAGLE-3 top-K drafting draft probs are near one-hot, so the joint-probability gain is muddied (authors flag stochasticity/precision); needs full draft+target probs for all gamma positions</t>
+          <t>no gain at T=0; needs full draft and target probability vectors for all gamma positions; gain shrinks for the largest target (+3.3% BE on Qwen2.5-72B GSM8K)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -18661,7 +18669,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>none beyond drafter; verify &lt;1% of decode time; stores gamma x V probs (est.)</t>
+          <t>none beyond drafter; stores gamma x V probabilities (est.); verify &lt;1% of decode time (stated)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -18671,17 +18679,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>BE 6.30 / 6.47 / 6.65 vs 5.99 / 6.14 / 6.44 token-wise (Qwen2.5-0.5B -&gt; 14B/32B/72B, GSM8K, gamma=10, T=1)</t>
+          <t>BE 6.30 / 6.47 / 6.65 vs 5.99 / 6.14 / 6.44 token-wise (Qwen2.5-0.5B -&gt; 14B/32B/72B, GSM8K, gamma=10, T=1); HumanEval 5.29-5.49; CNN/DM 2.45-2.59</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>+6.7% avg speed vs token-wise; 91.05 tok/s (+10.7%) Qwen2.5-14B GSM8K (1x H20, T=1); EAGLE-3 80.49 vs 71.59 tok/s</t>
+          <t>+6.7% avg speed vs token-wise; 91.05 vs 82.28 tok/s Qwen2.5-14B GSM8K (1x H20, T=1); EAGLE-3 integration 80.49 vs 71.59 tok/s (+12.4%)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B/8B: +8.8% BE, +9.2% speed (8x H20); EAGLE-3 Llama3.1-8B: &gt;12% speed</t>
+          <t>Llama-3.1-70B/8B: BE 7.43 vs 6.83 (+8.8%), 9.18 vs 8.41 tok/s (+9.2%) (H20)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -18696,7 +18704,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18728,7 +18736,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Generic tree construction principle (title only)</t>
+          <t>Generic tree construction principle aimed at maximizing speedup (title only; OpenReview page blocked by bot check)</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -18825,7 +18833,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>SSMs LLaMA-68M / OPT-125M (+ their KV) and target KV for tree nodes</t>
+          <t>SSMs LLaMA-68M / OPT-125M add &lt;1% memory; token-tree overhead negligible vs KV cache (stated)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -18835,32 +18843,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2.18-3.91 tokens/step greedy, 1.64-2.38 stochastic (tree width 1-5)</t>
+          <t>verified tokens/step greedy 2.18-2.95 (width 1) to 3.07-3.69 (width 5); stochastic 2.21-2.38 (width 5) (LLaMA-7B + LLaMA-68M, range over datasets)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1.5-2.5x single-node, 2.4-2.8x multi-node vs incremental; 2.6-3.5x offloading vs FlexGen (A10 24GB, bs 1-16)</t>
+          <t>1.5-2.5x single-node (LLaMA-7B 1 GPU, OPT-30B 4 GPUs), 2.4-2.8x multi-node (LLaMA-65B, 2 nodes) vs vLLM/HF TGI/FasterTransformer; 2.6-3.5x offloading vs FlexGen (OPT-13B/30B); A10 24GB, bs1-16</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-7B and LLaMA-65B targets with LLaMA-68M SSM (within the 1.5-2.8x distributed range)</t>
+          <t>LLaMA-7B + LLaMA-68M: 1.5-2.5x single GPU; LLaMA-65B multi-node: 2.4-2.8x</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Instruction Prompts, ChatGPT Prompts, WebQA, Alpaca, PIQA</t>
+          <t>Alpaca, ChatGPT Prompts, WebQA, Chatbot Instruction Prompts (CIP), PIQA</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/flexflow/flexflow-serve</t>
+          <t>https://github.com/flexflow/FlexFlow (paper link; now flexflow-serve)</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18907,7 +18915,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68M drafter + KV; up to 128-node (768 offloaded) verify tree per step</t>
+          <t>JF68M drafter + KV, 128-node verify tree (A100); offload: Llama2-7B/Llama3-8B drafter + 768-node tree</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -18917,17 +18925,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5.08 tokens/step (Llama2-7B + 68M, C4, T=0); 3.92 at T=0.6; 11.68 (Llama3-70B offload, T=0)</t>
+          <t>5.08 tokens/step (Llama2-7B + JF68M, C4, T=0, tree 128); 3.92 at T=0.6; 4.98 MT-Bench T=0; offload 10.30 (Llama2-70B/7B), 11.68 (Llama3-70B/8B, T=0)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4.04x (Llama2-7B, A100, bs1, T=0); 3.73x Llama2-13B; 9.5x Llama3-70B offloaded on L40 (0.60 s/token)</t>
+          <t>4.04x (Llama2-7B, A100, bs1, T=0, C4) vs SpecInfer 3.45x; up to 3.73x Llama2-13B, 2.27x Vicuna-33B; offload on L40: 9.5x Llama3-70B (0.60 s/token), 8.6x Llama2-70B (0.66 s/token)</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Llama2-7B 4.04x (T=0), 3.18x (T=0.6); Llama2-13B 3.73x; Vicuna-33B; Llama3-70B offload 9.5x</t>
+          <t>Llama2-7B 4.04x (T=0), 3.18x (T=0.6); Llama2-13B up to 3.73x; Vicuna-33B 2.27x; offload Llama2-70B 8.6x, Llama3-70B 9.5x</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -18942,7 +18950,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -18979,7 +18987,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>deeper trees mean more sequential drafter passes; draft probability is used as acceptance proxy, which weakens under sampling; per-step tree rebuild gives dynamic shapes</t>
+          <t>deeper trees mean more sequential drafter passes, so a strong large drafter can raise MAL yet give ~1x (Llama-2-7B + 1B draft: MAL 4.88, 1.01x); draft probability as acceptance proxy weakens under sampling; per-step tree rebuild gives dynamic shapes</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -18989,7 +18997,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>drafter (68M-7B, or EAGLE head) + its KV; 25-60 node verify tree</t>
+          <t>drafter (68M, 1B, 7B or EAGLE head) + its KV; 25-60 node verify tree</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -18999,22 +19007,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MAL 4.06 (Llama-2-70B + EAGLE, MT-Bench, T=0); 7.74 with Llama-2-7B draft; 4.55 GSM8K</t>
+          <t>MAL 4.06 (Llama-2-70B + EAGLE, MT-Bench, T=0); 7.74 with Llama-2-7B draft (50 nodes); ~10 with 500 nodes; 4.09 at T=1</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3.21x (Llama-2-70B + EAGLE, GSM8K, 4x A100-40GB, T=0); 3.01x at T=1</t>
+          <t>3.05x (Llama-2-70B + EAGLE, MT-Bench, 4x A100-PCIE-40GB, T=0), ~3.2x GSM8K; 3.01x at T=1; Llama-2-7B + EAGLE 2.56x (RTX 4090)</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Llama-2-7B/13B/70B and Vicuna-33B; best 3.21x Llama-2-70B + EAGLE</t>
+          <t>Llama-2-7B: 1.69x (68M), 2.56x (EAGLE); Llama-2-13B 1.80x (68M, L20); Llama-2-70B 1.85x (7B draft), 3.05x (EAGLE); Vicuna-33B 2.24x (EAGLE)</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MT-Bench, GSM8K (C4 for Sequoia trees)</t>
+          <t>MT-Bench, GSM8K</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -19024,7 +19032,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19079,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>EAGLE head ~0.24B for Vicuna-7B (per Hu et al.) + its KV; ~1 decoder layer for larger targets (est.)</t>
+          <t>EAGLE head ~0.24B for Vicuna-7B (per Hu et al.) + its KV; draft tree 60 tokens (7B/8B), 50 (13B), 48 (70B) verified per step</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -19081,17 +19089,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>tau 4.98 (Vicuna-7B, MT-bench, T=0); 4.83 Vicuna-13B; 4.28 Vicuna-7B at T=1</t>
+          <t>tau 4.98 (Vicuna-7B, MT-bench, T=0); 4.83 Vicuna-13B; 4.28 Vicuna-7B at T=1; up to 5.52 (LLaMA2-Chat-13B, HumanEval, T=0)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3.62x Vicuna-7B, 4.26x Vicuna-13B (MT-bench, T=0, bs1); 3.05x Vicuna-7B at T=1</t>
+          <t>3.62x Vicuna-7B, 4.26x Vicuna-13B (MT-bench, T=0); 3.05x Vicuna-7B at T=1; up to 5.00x LLaMA2-Chat-13B HumanEval; hardware not stated in extract</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B 3.62x/tau 4.98; LLaMA2-Chat-7B 3.43x/tau 4.70; LLaMA2-Chat-13B 4.21x; also LLaMA2-70B, LLaMA3-8B/70B</t>
+          <t>Vicuna-7B 3.62x/tau 4.98; LLaMA2-Chat-7B 3.43x/4.70; LLaMA2-Chat-13B 4.21x/4.75; LLaMA2-Chat-70B 3.51x/4.48; LLaMA3-8B 3.46x/4.53; LLaMA3-70B 3.29x/4.16 (MT-bench, T=0)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -19106,7 +19114,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19143,7 +19151,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>pays off only with long shared prefixes or large trees; requires a custom attention kernel inside the serving engine</t>
+          <t>pays off only with large token trees or long shared prefixes (stated); gain small where attention is a minor share of latency (~30% in multi-step reasoning: 1.03-1.10x); requires a custom Triton attention kernel in the engine</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -19153,7 +19161,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>none extra (kernel metadata only)</t>
+          <t>none extra (kernel metadata only; paged and unpaged KV supported)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -19168,17 +19176,17 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>up to 2.23x end-to-end, 3.59x attention latency vs SOTA attention kernels (tree-based workloads incl. SD)</t>
+          <t>SD trees 32/64/128/256 nodes: 1.43x/1.70x/2.22x/2.52x e2e vs Radix Attention, 3.82x attention (Llama3-8B, A100-80GB, v2); latest abstract: up to 2.23x e2e / 3.59x attention</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Llama-3-8B / Llama-3.1-8B used in examples; per-model numbers not extracted</t>
+          <t>Llama3-8B: SD workload 1.43-2.52x e2e vs Radix Attention (A100-80GB, v2); few-shot 1.24-1.33x</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>APPS (SD trees, 64 tokens), few-shot prompting and multi-step reasoning tree workloads</t>
+          <t>few-shot prompting (4k prompt), multi-step reasoning (sorting, doc merging, keyword counting, set intersection), speculative decoding token trees</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -19188,7 +19196,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19243,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68M/160M drafter + KV and tree (not reported)</t>
+          <t>not reported; Llama-68M/160M drafter + KV and verify tree (est.)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -19250,12 +19258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>up to 3.98x (A100-80GB), 2.76x on A40 vs SpecInfer/Sequoia/vLLM-Spec; bs1</t>
+          <t>up to 3.98x (A100-80GB), 2.76x (A40) vs SpecInfer baseline; 1.49x over Sequoia; bs1 (single request), T=0; PyTorch TorchInductor + CUDA Graphs</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Llama-2-7B/13B targets with Llama-68M/160M drafters: up to 3.98x</t>
+          <t>Llama-2-7B + Llama-68M and Llama-2-13B + Llama-160M: up to 3.98x (A100)</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -19270,7 +19278,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19307,7 +19315,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>needs drafter on separate GPU(s) or they contend on one GPU; post-verify drafts are wasted on rejection and target runs 1.29-1.42x more forward passes</t>
+          <t>needs drafter on separate GPU(s) or they contend for one GPU (stated); post-verify drafts are wasted on rejection, so draft and target run +29-42% more forward passes than SD</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -19317,7 +19325,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>full separate drafter (e.g. 7B for 70B) + its KV on extra GPU</t>
+          <t>full separate drafter (e.g. 7B for 70B) + its KV on its own GPU (draft 1 GPU, 70B target 3 GPUs)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -19327,17 +19335,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>MAT 26.53 (CodeLlama 7B/70B, HumanEval); 39.90 DeepSeek 6.7B/33B (PEARL's MAT definition)</t>
+          <t>MAT (PEARL's definition) 26.53 vs 8.32 SD (CodeLlama 7B/70B, HumanEval); 27.95 (7B/34B); 39.90 vs 5.69 (DeepSeek 6.7B/33B)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4.43x (CodeLlama 7B-&gt;70B, HumanEval, A100-80G, bs1, bf16); README headline 3.87x HumanEval on H100</t>
+          <t>4.43x vs AR, 1.46x vs SD (CodeLlama 7B-&gt;70B, HumanEval, A100-SXM4-80G, bs1, bf16)</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Llama 2 7B/70B: 3.82x GSM8K, 2.64x MT-Bench, 3.95x MGSM; Llama 3.1 8B/70B: 3.95x MGSM, 3.59x MT-Bench</t>
+          <t>Llama2 7B/70B: 3.29x HumanEval, 3.82x GSM8K, 2.64x MT-Bench avg; Llama3.1 8B/70B: 3.87x HumanEval</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -19352,7 +19360,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19379,7 +19387,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ICLR 2026</t>
+          <t>arXiv 2026 (v3 May 2026; earlier ICLR 2026 note not confirmed)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -19389,7 +19397,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>needs a dedicated draft GPU; speculations for missed outcomes are wasted compute; hit rate drops with batch size and temperature</t>
+          <t>needs a dedicated draft GPU; speculations for missed outcomes are wasted compute; cache misses rise with batch size (at bs16 a fast backup speculator beats the neural one)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -19399,7 +19407,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1B drafter on separate H100 + speculation cache 'hundreds of MB'</t>
+          <t>1B drafter on separate H100 + speculation cache O(BFK(K+1)(V+1)) bits, 'hundreds of MB' (stated)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -19409,17 +19417,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>not reported as tau</t>
+          <t>not reported as tau (cache hit rate ~80-90% at fan-out 128, T=0)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4.8x avg vs AR (Llama-3.1-70B on 4x H100 + 1B draft on 1x H100, bs1, T=0); 255.8 vs 161.8 SD vs 54.7 AR tok/s; ~30% over best SD baseline</t>
+          <t>4.68x avg vs AR, 1.58x vs SD (Llama-3.1-70B on 4x H100 + 1B draft on 1x H100, bs1, T=0): 255.8 vs 161.8 SD vs 54.7 AR tok/s; Qwen3-32B 2.29x</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B + Llama-3.2-1B: 5.3x HumanEval, 5.6x GSM8K, 4.8x avg vs AR</t>
+          <t>Llama-3.1-70B + Llama-3.2-1B: 5.17x HumanEval, 5.50x GSM8K, 4.10x Alpaca, 3.93x UltraFeedback, 4.68x avg vs AR</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -19434,7 +19442,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19471,7 +19479,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>3 models resident with 3 KV caches; theory conditions hard to meet beyond 3 models (stated); extra verification stage to schedule</t>
+          <t>3 models resident with 3 KV caches whose footprint grows with length, lowering gains on summarization/RAG (stated); conditions for &gt;3 models hard to meet with off-the-shelf models (stated)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -19481,7 +19489,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>full 4-bit quantized copy of target + EAGLE head + their KV (est.)</t>
+          <t>not reported; full 4-bit (group 128) copy of target + EAGLE-2 head + their KV (est.)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -19491,32 +19499,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9.1-10 tokens avg (secondary review)</t>
+          <t>9.88 (Vicuna-7B), 9.84 (LLaMA2-7B), 9.44 (LLaMA3-8B), 9.32 (Qwen2-7B) tokens per target pass, Spec-Bench overall; 7.48 LLaMA2-70B; T not stated</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>up to 4.43x Vicuna-7B; hardware/T not extracted</t>
+          <t>3.48x Vicuna-7B overall (up to 4.43x Math); 3.66x LLaMA2-7B; A800-80G; T not stated</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>LLaMA2-Chat-7B 3.31-4.01x; LLaMA3-8B up to 3.87x; Vicuna-7B up to 4.43x; Vicuna-13B 2.69x; LLaMA-70B 2.92x</t>
+          <t>LLaMA2-7B 3.31-4.10x (3.66x overall); LLaMA3-8B 2.71-3.87x (3.31x); Vicuna-7B 3.48x; Vicuna-13B 2.69x; LLaMA2-70B 2.92x</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Spec-Bench tasks (MT-Bench, translation, summarization, QA, math, RAG)</t>
+          <t>Spec-Bench (MT, translation, summarization, QA, math, RAG)</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>promised, not found</t>
+          <t>release promised, not found</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19553,7 +19561,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>unpad-realign-repad overhead grows superlinearly (~40% of compute at bs8, 46.7% at bs16); static batching only, no continuous batching</t>
+          <t>unpad-realign-repad overhead grows superlinearly (39.4% of compute at bs8, 46.7% at bs16); beyond bs8 cross-batch grouping fails more often and falls back to realignment; static batching only</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -19563,12 +19571,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>drafter (68M-0.6B) + KV; padding overhead not reported</t>
+          <t>drafter (68M or 0.6B) + its KV; padding overhead not reported</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>~95% exact output equivalence at greedy (residual attributed to FP nondeterminism)</t>
+          <t>90-97% exact output match vs AR at greedy (95-98% partial match); residual attributed to FP nondeterminism</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -19578,12 +19586,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>up to 3x throughput at bs8 vs bs1 (A100-80GB, greedy, 5 draft tokens)</t>
+          <t>EqSpec 2.4-2.6x at bs4, ExSpec 2.8-3.0x at bs8 throughput vs bs1 (A100-80GB, greedy, 5 draft tokens, HF Transformers 4.51.3)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B/68M: 92.1% exact match at bs4 (EqSpec) vs 0.2% BSP, 0.0% DSD</t>
+          <t>Vicuna-7B/68M: 2.6x (EqSpec, bs4), 2.8x (ExSpec, bs8) vs bs1; baselines BSP 0.2-3.5%, DSD ~0% exact match</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -19598,7 +19606,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19645,7 +19653,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>self-spec: draft KV budget 128-4K tokens/seq, no extra weights; standalone drafter adds up to 38-140% memory</t>
+          <t>self-spec: draft KV budget 256-512 (StreamingLLM) or ~2K (SnapKV) tokens/seq, no extra weights; standalone drafter can take 38-140% of target memory (stated)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -19655,22 +19663,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>expected tokens/step 2.31-8.21 across settings; acceptance up to ~90-95% (LLaMA-3.1 self-spec)</t>
+          <t>expected tokens/step 2.53-5.61 across configs (latest version); SnapKV drafts accept far more than StreamingLLM</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>up to 2.51x LLaMA-3.1-8B (100K ctx, 8x H100, greedy); 2.01x at bs256, 32K ctx</t>
+          <t>up to 2.51x LLaMA-3.1-8B (SnapKV self-spec, 100K ctx, bs41, 8x H100, greedy); 1.2-1.7x StreamingLLM self-spec at bs32-128, 8K-32K ctx (A100/H100/L40)</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>LLaMA-3.1-8B up to 2.51x; LLaMA-2-7B-32K 1.75x at bs256; also LLaMA-3.1-70B, LLaMA-2-70B</t>
+          <t>LLaMA-3.1-8B up to 2.51x (SnapKV); LLaMA-2-7B-32K 1.27-1.69x (8x A100, v1), 1.68x bs64 8K ctx</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>PG-19, RULER (niah-multikeys-3, cwe, qa-1)</t>
+          <t>PG-19, RULER (QA-1, CWE, needle-in-haystack)</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -19680,7 +19688,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19742,27 +19750,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1.1-1.8x vs AR across 15 setups; 6-55% over vanilla SD; abstract range 1.14-14.3x (L40, A800)</t>
+          <t>1.1-1.8x vs AR across 15 setups (1x L40, 1/2/4/8x A800, vLLM); 10-61% over other methods' speedup; abstract 1.14-14.3x is vs other speculative systems, not AR</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B + Llama-3.2-1B on 8x A800; Vicuna-7B/68M, Vicuna-33B/160M (per-model numbers not extracted)</t>
+          <t>Llama-3.1-70B + Llama-3.2-1B on 8x A800; Vicuna-7B/68M (L40, A800), Vicuna-33B/160M (2-4x A800); per-model numbers in figures</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Azure LLM inference traces, Mooncake trace, SpecBench mix</t>
+          <t>Azure LLM inference traces (code, conversation), Mooncake trace (v1); BurstGPT in v2</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>none found</t>
+          <t>https://github.com/cerebellumking/AdaSpec (per v2)</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19799,7 +19807,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>acceptance is an exogenous input, so tree or verifier choices cannot be modeled; valid only before saturation</t>
+          <t>acceptance is an exogenous constant per token (independent of earlier rejections), so tree or verifier choices cannot be modeled; models mean latency only, valid before saturation</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -19824,17 +19832,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>no new speedup; SD speedup diminishes with load (vLLM 0.13.0, A100)</t>
+          <t>no new speedup; SD speedup erodes with load when C2 ratio &gt;1, faster for longer drafts (vLLM 0.13.0, 1x A100; 4x A100 for 70B)</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Llama-3.1-8B/70B with EAGLE-3-style drafter and Llama-3.1-8B drafter for 70B (numbers not extracted)</t>
+          <t>Llama-3.1-8B (1x A100) and 70B (4x A100) verifiers with EAGLE-3-style drafter, Llama-3.1-8B drafter for 70B; no speedup numbers; also Qwen3 8B-235B, gpt-oss-20b</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>synthetic prompts from Pride and Prejudice; prefill/decode 256-1024</t>
+          <t>synthetic prompts from Pride and Prejudice; prefill/decode 256-1024; GuideLLM load sweep</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -19844,7 +19852,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -19860,7 +19868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -20211,19 +20219,43 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>'not reported' where the paper gives nothing. Counts: memory 34, accepted tokens 28, LLaMA 32 with none.</t>
+          <t>'not reported' where the paper gives nothing. Counts: memory 31, accepted tokens 29, LLaMA 30 with none.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Known conflicts</t>
+          <t>Resolved conflicts</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Draft-OPD 5.96/5.73 are tau, not speedup; PARD-2 LLaMA speedup differs by source (6.94x vs 5.19x); EDA speedup varies by source.</t>
+          <t>PARD-2: 5.19x / tau 6.95 is the LLaMA3.1-8B average, 6.94x / tau 9.19 is HumanEval only. Draft-OPD 5.96/5.73 are tau. Several earlier recalled numbers were corrected after full-text reads (see changes_round2.md in the repo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Check by eye</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Numbers read from figures or where two extractions disagreed are flagged in the cell (EAGLE, EAGLE-2 L3 rows, EDA, MagicDec, TreeFlash, DeFT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Not read</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Max-Speedup Speculative Sampling (OpenReview blocked); Prompt Lookup Decoding has no paper.</t>
         </is>
       </c>
     </row>
